--- a/naver-place-crawler/results_nail/남구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/남구_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>미라클뷰티&amp;네일</t>
+          <t>에스네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ssoyoung0318@naver.com</t>
+          <t>snail4324@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-3178</t>
+          <t>0507-1406-3132</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 12층1호</t>
+          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miraclebeauty_nail?igsh=MW5nN3NoOHd0OG51dg==</t>
+          <t>https://www.instagram.com/snail0070</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="Q2" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="R2" t="n">
-        <v>266</v>
+        <v>146</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2040709432</t>
+          <t>38286683</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040709432</t>
+          <t>https://m.place.naver.com/place/38286683</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,30 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>젤리네일</t>
+          <t>미라클뷰티&amp;네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mi2013@naver.com</t>
+          <t>alsdudvvv3@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1330-3178</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
+          <t>인천광역시 미추홀구 매소홀로 262 12층1호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1SGa70g</t>
+          <t>https://www.instagram.com/miraclebeauty_nail?igsh=MW5nN3NoOHd0OG51dg==</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -702,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>390</v>
+        <v>194</v>
       </c>
       <c r="Q3" t="n">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="R3" t="n">
-        <v>497</v>
+        <v>274</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1140244485</t>
+          <t>2040709432</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140244485</t>
+          <t>https://m.place.naver.com/place/2040709432</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -748,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>수앙뷰티</t>
+          <t>인블리네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>m_s_y_0219@naver.com</t>
+          <t>bbobbolee2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1431-2153</t>
+          <t>070-7643-2243</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 남주길 150 근린생활시설 2동 210호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soins_beauty_n</t>
+          <t>https://pf.kakao.com/_xhUIxmC</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -796,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>207</v>
+        <v>416</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>1221</v>
       </c>
       <c r="R4" t="n">
-        <v>221</v>
+        <v>1637</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2042315946</t>
+          <t>63265483</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042315946</t>
+          <t>https://m.place.naver.com/place/63265483</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일피컨트</t>
+          <t>에이풋케어 내성발톱 발톱무좀 발각질 문제성발</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>edenia_@naver.com</t>
+          <t>illbwidu@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1368-8328</t>
+          <t>0507-1378-4114</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2099호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 시티필드 6층 6013호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailpiquant</t>
+          <t>https://blog.naver.com/illbwidu</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -879,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>485</v>
       </c>
       <c r="R5" t="n">
-        <v>118</v>
+        <v>588</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1998009537</t>
+          <t>1319855180</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1998009537</t>
+          <t>https://m.place.naver.com/place/1319855180</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -936,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>채움네일</t>
+          <t>네일 해봄</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rhdwnsla5656@naver.com</t>
+          <t>eruriee@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1326-3123</t>
+          <t>0507-1303-4226</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로228번길 11 1층</t>
+          <t>인천광역시 미추홀구 토금중로30번길 9 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaeum_nail_</t>
+          <t>https://www.instagram.com/nail_haebom/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>222</v>
+        <v>876</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="R6" t="n">
-        <v>261</v>
+        <v>1056</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1824103581</t>
+          <t>38301920</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824103581</t>
+          <t>https://m.place.naver.com/place/38301920</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오래도록예쁘게 인하대역본점</t>
+          <t>네일에보</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oye_beauty@naver.com</t>
+          <t>daniya1210@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1348-5330</t>
+          <t>0507-1311-6332</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용정공원로83번길 43 e편한세상시티 2층 217호</t>
+          <t>인천광역시 미추홀구 경인로 372 201동 B2층 2055호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/o.ye_beauty/</t>
+          <t>https://www.instagram.com/_nailevo_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1078,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>153</v>
+        <v>343</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="R7" t="n">
-        <v>172</v>
+        <v>421</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1200197583</t>
+          <t>1252060771</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200197583</t>
+          <t>https://m.place.naver.com/place/1252060771</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>라 폴리쉬드</t>
+          <t>채움네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kimhaha1103@naver.com</t>
+          <t>rhdwnsla5656@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1354-5656</t>
+          <t>0507-1326-3123</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 승학길 28 105호 1층상가 라 폴리쉬드</t>
+          <t>인천광역시 미추홀구 소성로228번길 11 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/la_polished?igsh=djk3a2lwb3ppdDRk</t>
+          <t>https://www.instagram.com/chaeum_nail_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>55</v>
+        <v>223</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="R8" t="n">
-        <v>62</v>
+        <v>262</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2080412833</t>
+          <t>1824103581</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080412833</t>
+          <t>https://m.place.naver.com/place/1824103581</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1218,34 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>걸스네일</t>
+          <t>네일그리움 주안점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ymj11969@naver.com</t>
+          <t>cherryjoa_v@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1410-0304</t>
+          <t>0507-1443-5044</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 133 걸스네일</t>
+          <t>인천광역시 미추홀구 미추홀대로614번길 42 101호 네일그리움</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://link.thinkofyou.kr/girls_nail</t>
+          <t>https://www.instagram.com/nail_geurium</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1266,7 +1270,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1275,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>158</v>
+        <v>255</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37257261</t>
+          <t>1994727673</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37257261</t>
+          <t>https://m.place.naver.com/place/1994727673</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1312,34 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일언니</t>
+          <t>쿄우네일 석바위점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pjh48886@naver.com</t>
+          <t>dlthwjd7530@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1360-4886</t>
+          <t>0507-1394-6274</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 97 102 호 네일언니</t>
+          <t>인천광역시 미추홀구 경원대로 858 3층 일부호 쿄우네일</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_unni_</t>
+          <t>http://pf.kakao.com/_xdlxjBn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1360,7 +1364,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>496</v>
+        <v>180</v>
       </c>
       <c r="Q10" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R10" t="n">
-        <v>537</v>
+        <v>218</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36184234</t>
+          <t>2023963502</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36184234</t>
+          <t>https://m.place.naver.com/place/2023963502</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1410,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>뷰티컴트루</t>
+          <t>네일오숑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wlsk4075@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1372-5309</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬서로18번길 27-20 1층</t>
+          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_cometrue</t>
+          <t>https://www.instagram.com/nail_osyong/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1454,7 +1454,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R11" t="n">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2001250057</t>
+          <t>1518702391</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001250057</t>
+          <t>https://m.place.naver.com/place/1518702391</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1500,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>도화네일</t>
+          <t>아르떼네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>gsqnls2u@naver.com</t>
+          <t>arte__nail_@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1373-9131</t>
+          <t>0507-1323-0926</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
+          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dohwa_nail_</t>
+          <t>https://blog.naver.com/arte__nail_</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1548,7 +1548,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>691</v>
+        <v>391</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="R12" t="n">
-        <v>693</v>
+        <v>450</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1155887763</t>
+          <t>1775601804</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155887763</t>
+          <t>https://m.place.naver.com/place/1775601804</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일링</t>
+          <t>뾰로롱네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gulgomi@naver.com</t>
+          <t>mjy22977@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1346-3521</t>
+          <t>0507-1302-6657</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 학익로80번길 11 시티오씨엘3단지 메가박스 상가 2층 B-224호</t>
+          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nailing</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1647,17 +1647,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="Q13" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>259</v>
+        <v>83</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1351774557</t>
+          <t>2058778627</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1351774557</t>
+          <t>https://m.place.naver.com/place/2058778627</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1688,34 +1688,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
+          <t>네일인더문</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dritn-nail_a_o@naver.com</t>
+          <t>beauty_n_nail@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1325-1015</t>
+          <t>0507-1436-0467</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 장천로 57 1층</t>
+          <t>인천광역시 미추홀구 소성로 237 1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://m.themosttimes.co.kr/39655</t>
+          <t>https://www.instagram.com/nail_inthemoon</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="Q14" t="n">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="R14" t="n">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1166150967</t>
+          <t>1204881858</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166150967</t>
+          <t>https://m.place.naver.com/place/1204881858</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1782,29 +1782,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>제로네일</t>
+          <t>네일플래닛</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>seeat_f@naver.com</t>
+          <t>znzltkfkd123@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1359-4583</t>
+          <t>0507-1470-6637</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
+          <t>인천광역시 미추홀구 경인로 372 포레나 201동(아인여성병원건물) 지상2층 2017호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zeronail_art</t>
+          <t>https://blog.naver.com/znzltkfkd123</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="R15" t="n">
-        <v>336</v>
+        <v>443</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1613054835</t>
+          <t>1077662255</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613054835</t>
+          <t>https://m.place.naver.com/place/1077662255</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1876,29 +1876,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>우니네일</t>
+          <t>제로네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sseonni51@naver.com</t>
+          <t>seeat_f@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1390-7191</t>
+          <t>0507-1359-4583</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 2층 2057호</t>
+          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ooninail_?igsh=YXc5aDlrOHZoeDh1&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/zeronail_art</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>92</v>
+        <v>333</v>
       </c>
       <c r="Q16" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>110</v>
+        <v>338</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1013712359</t>
+          <t>1613054835</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013712359</t>
+          <t>https://m.place.naver.com/place/1613054835</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1970,29 +1970,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>쿄우네일 석바위점</t>
+          <t>네일 품은 손</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dlthwjd7530@naver.com</t>
+          <t>sssh200118@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1394-6274</t>
+          <t>0507-1360-1453</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로 858 3층 일부호 쿄우네일</t>
+          <t>인천광역시 미추홀구 한나루로357번길 5-58 1층 네일품은손</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdlxjBn</t>
+          <t>http://pf.kakao.com/_eQCrb</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="Q17" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="R17" t="n">
-        <v>216</v>
+        <v>122</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2023963502</t>
+          <t>1680001412</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023963502</t>
+          <t>https://m.place.naver.com/place/1680001412</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2064,29 +2064,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일에보</t>
+          <t>라 폴리쉬드</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>daniya1210@naver.com</t>
+          <t>khw23540@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1311-6332</t>
+          <t>0507-1354-5656</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 201동 B2층 2055호</t>
+          <t>인천광역시 미추홀구 승학길 28 105호 1층상가 라 폴리쉬드</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailevo_</t>
+          <t>https://www.instagram.com/la_polished?igsh=djk3a2lwb3ppdDRk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2112,7 +2112,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>338</v>
+        <v>85</v>
       </c>
       <c r="Q18" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="R18" t="n">
-        <v>416</v>
+        <v>93</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1252060771</t>
+          <t>2080412833</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252060771</t>
+          <t>https://m.place.naver.com/place/2080412833</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2158,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네일팔레트</t>
+          <t>루미랑네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nail4season@naver.com</t>
+          <t>jine_blog@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1334-0294</t>
+          <t>0507-1371-1706</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palette_nailll</t>
+          <t>https://www.instagram.com/rumirang_nail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="R19" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,17 +2230,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1167629339</t>
+          <t>1156304078</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167629339</t>
+          <t>https://m.place.naver.com/place/1156304078</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2252,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에스네일</t>
+          <t>디어마인샵</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>snail4324@naver.com</t>
+          <t>unthsu@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1406-3132</t>
+          <t>0507-1403-2780</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
+          <t>인천광역시 미추홀구 경인남길30번길 94 1층 디어마인샵</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snail0070</t>
+          <t>http://instagram.com/dear_mine91</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>74</v>
+        <v>1300</v>
       </c>
       <c r="Q20" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="R20" t="n">
-        <v>146</v>
+        <v>1353</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,17 +2324,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>38286683</t>
+          <t>1144594831</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38286683</t>
+          <t>https://m.place.naver.com/place/1144594831</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2346,29 +2346,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>메이에르 네일</t>
+          <t>디몽드네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tlsdmsal1910@naver.com</t>
+          <t>eautorride2@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1472-1341</t>
+          <t>0507-1392-5341</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로330번길 23 1층 메이에르네일</t>
+          <t>인천광역시 미추홀구 수봉남로 1 (용현동)2층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/meyere_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2394,22 +2394,22 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R21" t="n">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2090344240</t>
+          <t>1670918594</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090344240</t>
+          <t>https://m.place.naver.com/place/1670918594</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2440,29 +2440,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>디몽드네일</t>
+          <t>네일미니</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>eautorride2@naver.com</t>
+          <t>snow1blossom@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1392-5341</t>
+          <t>0507-1379-4411</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 수봉남로 1 (용현동)2층</t>
+          <t>인천광역시 미추홀구 한나루로489번길 107 1층 102호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_mi_ni</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>133</v>
+        <v>414</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="R22" t="n">
-        <v>144</v>
+        <v>468</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,17 +2512,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1670918594</t>
+          <t>1633509740</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1670918594</t>
+          <t>https://m.place.naver.com/place/1633509740</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2534,34 +2534,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일,포슬</t>
+          <t>네일핏</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kirari__@naver.com</t>
+          <t>nailfitsl@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0507-1386-5035</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
+          <t>인천광역시 미추홀구 독배로 311 비젼프라자 2층 206호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_poseul_</t>
+          <t>http://pf.kakao.com/_FxiNCG</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2582,7 +2578,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2591,13 +2587,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>405</v>
+        <v>932</v>
       </c>
       <c r="Q23" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="R23" t="n">
-        <v>444</v>
+        <v>944</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2606,17 +2602,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1050625355</t>
+          <t>718951949</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050625355</t>
+          <t>https://m.place.naver.com/place/718951949</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2628,30 +2624,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>주주네일</t>
+          <t>로이네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>cafri4030@naver.com</t>
+          <t>wlgus1647@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1350-5396</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주승로 51 주안에듀서밋아파트 상가 2동 106호</t>
+          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/juju___nail</t>
+          <t>http://pf.kakao.com/_vxkKMs/chat</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2672,7 +2672,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="R24" t="n">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2696,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1451330914</t>
+          <t>1765283529</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1451330914</t>
+          <t>https://m.place.naver.com/place/1765283529</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2718,29 +2718,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>모도리 네일</t>
+          <t>제리네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dbsalwjd88@naver.com</t>
+          <t>wjdsla91777@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1330-1268</t>
+          <t>0507-1479-5891</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로382번길 12 1층 모도리네일</t>
+          <t>인천광역시 미추홀구 매소홀로 262 1층 1055호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/j7n._s?igsh=N2UybHpmZjRnbWJz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>313</v>
+        <v>262</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="R25" t="n">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1752538431</t>
+          <t>1744004614</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1752538431</t>
+          <t>https://m.place.naver.com/place/1744004614</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2812,29 +2812,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일스튜디오 매료</t>
+          <t>홀리네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>lnj7205@naver.com</t>
+          <t>ko3hi@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1440-3488</t>
+          <t>0507-1409-1716</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인에비뉴 2층 2098호 (투썸플레이스 위)</t>
+          <t>인천광역시 미추홀구 매소홀로446번길 7 1층 홀리뷰티</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailstudiomeryo/</t>
+          <t>https://www.instagram.com/_holly_nail_0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2869,13 +2869,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>249</v>
+        <v>33</v>
       </c>
       <c r="Q26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R26" t="n">
-        <v>263</v>
+        <v>43</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1152584583</t>
+          <t>1681381393</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1152584583</t>
+          <t>https://m.place.naver.com/place/1681381393</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2906,34 +2906,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일,꽃이피다</t>
+          <t>마이린 네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nail910401@naver.com</t>
+          <t>myrin_nail@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1311-6628</t>
+          <t>0507-1364-9606</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 시티필드 7층 7012호 네일꽃이피다</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.bloom__</t>
+          <t>http://pf.kakao.com/_kqfkxj</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2954,7 +2954,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,17 +2978,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1271233277</t>
+          <t>1373786401</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1271233277</t>
+          <t>https://m.place.naver.com/place/1373786401</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3000,25 +3000,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>예뻐지는네일</t>
+          <t>드림드로잉</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jisoo851208@naver.com</t>
+          <t>powerkorea0505@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1365-9785</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로578번길 9 1층(주안동)</t>
+          <t>인천광역시 미추홀구 매소홀로 262 7층 7001호 드림드로잉</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautynail_0901</t>
+          <t>https://www.instagram.com/d_dnail0818</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3053,13 +3057,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="Q28" t="n">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="R28" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,17 +3072,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1148534617</t>
+          <t>1887397016</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1148534617</t>
+          <t>https://m.place.naver.com/place/1887397016</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3090,29 +3094,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일 해봄</t>
+          <t>반디인하우스 도화앨리웨이점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>eruriee@naver.com</t>
+          <t>bandinhouse_dohwa@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1303-4226</t>
+          <t>0507-1392-8241</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 토금중로30번길 9 1층</t>
+          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_haebom/</t>
+          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3147,13 +3151,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>867</v>
+        <v>341</v>
       </c>
       <c r="Q29" t="n">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="R29" t="n">
-        <v>1045</v>
+        <v>420</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3166,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>38301920</t>
+          <t>1485881474</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38301920</t>
+          <t>https://m.place.naver.com/place/1485881474</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3184,29 +3188,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>블루진네일</t>
+          <t>네일로</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>whole4ni@naver.com</t>
+          <t>kongdw@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1407-5343</t>
+          <t>0507-1378-2633</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로897번길 40 상가 1층 101호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 4층 4013호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bluejin_nail</t>
+          <t>https://www.instagram.com/nailo.nailstudio?igsh=bnB4MXhpNzF4MjU%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3232,7 +3236,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3241,13 +3245,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="Q30" t="n">
-        <v>173</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>308</v>
+        <v>86</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3260,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1920868303</t>
+          <t>2019386343</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920868303</t>
+          <t>https://m.place.naver.com/place/2019386343</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3278,34 +3282,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>예뻐진</t>
+          <t>네일도 희</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>tlsguswls81@naver.com</t>
+          <t>kimmihee4@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1334-0060</t>
+          <t>0507-1304-7934</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 301-2 2층</t>
+          <t>인천광역시 미추홀구 소성로 321-1 1층 101호 네일도, 희</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gFGxbb</t>
+          <t>https://www.instagram.com/naildo_hee</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3326,7 +3330,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3335,13 +3339,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>96</v>
+        <v>296</v>
       </c>
       <c r="Q31" t="n">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,17 +3354,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1366454286</t>
+          <t>1208564106</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1366454286</t>
+          <t>https://m.place.naver.com/place/1208564106</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3372,34 +3376,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>모드니에네일 인천용현점</t>
+          <t>걸스네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>wlsk4075@naver.com</t>
+          <t>ymj11969@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>032-888-2430</t>
+          <t>0507-1410-0304</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 61 1층 101호,102호</t>
+          <t>인천광역시 미추홀구 소성로 133 걸스네일</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://instagram.com/modnie_nail</t>
+          <t>https://link.thinkofyou.kr/girls_nail</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3420,7 +3424,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3429,13 +3433,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>758</v>
+        <v>158</v>
       </c>
       <c r="Q32" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="R32" t="n">
-        <v>858</v>
+        <v>212</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,17 +3448,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1031233548</t>
+          <t>37257261</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031233548</t>
+          <t>https://m.place.naver.com/place/37257261</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3466,29 +3470,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>문제성 손,발 오감네일 도화점</t>
+          <t>우니네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ogam_foot_nail@naver.com</t>
+          <t>sseonni51@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1388-5117</t>
+          <t>0507-1390-7191</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
+          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 2층 2057호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ogam_foot_nail</t>
+          <t>https://www.instagram.com/ooninail_?igsh=YXc5aDlrOHZoeDh1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3503,7 +3507,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3523,13 +3527,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>660</v>
+        <v>92</v>
       </c>
       <c r="Q33" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="R33" t="n">
-        <v>726</v>
+        <v>110</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,17 +3542,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1716147754</t>
+          <t>1013712359</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716147754</t>
+          <t>https://m.place.naver.com/place/1013712359</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3560,34 +3564,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일맑음</t>
+          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>s1514@naver.com</t>
+          <t>dritn-nail_a_o@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1489-0530</t>
+          <t>0507-1325-1015</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
+          <t>인천광역시 미추홀구 장천로 57 1층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuneungyeong4</t>
+          <t>https://m.themosttimes.co.kr/39655</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3617,13 +3621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="Q34" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="R34" t="n">
-        <v>304</v>
+        <v>204</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3632,17 +3636,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1539397163</t>
+          <t>1166150967</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539397163</t>
+          <t>https://m.place.naver.com/place/1166150967</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3654,34 +3658,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>루미랑네일</t>
+          <t>하이스타네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jine_blog@naver.com</t>
+          <t>mumu800@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1371-1706</t>
+          <t>0507-1377-6082</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
+          <t>인천광역시 미추홀구 경인로 372 201동 2030호 하이스타네일</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rumirang_nail</t>
+          <t>http://pf.kakao.com/_Qxexiqn</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3702,7 +3706,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3711,13 +3715,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>249</v>
+        <v>14</v>
       </c>
       <c r="Q35" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="R35" t="n">
-        <v>303</v>
+        <v>57</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3726,17 +3730,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1156304078</t>
+          <t>1591639462</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156304078</t>
+          <t>https://m.place.naver.com/place/1591639462</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3748,29 +3752,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>아르떼네일</t>
+          <t>뷰티컴트루</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>arte__nail_@naver.com</t>
+          <t>wlsk4075@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1323-0926</t>
+          <t>0507-1372-5309</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
+          <t>인천광역시 미추홀구 낙섬서로18번길 27-20 1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/arte__nail_</t>
+          <t>https://www.instagram.com/beauty_cometrue</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3785,7 +3789,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3805,13 +3809,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>392</v>
+        <v>246</v>
       </c>
       <c r="Q36" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="R36" t="n">
-        <v>451</v>
+        <v>259</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3820,17 +3824,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1775601804</t>
+          <t>2001250057</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1775601804</t>
+          <t>https://m.place.naver.com/place/2001250057</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3842,29 +3846,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일언니</t>
+          <t>수앙뷰티</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>555__555@naver.com</t>
+          <t>m_s_y_0219@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1315-4886</t>
+          <t>0507-1431-2153</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 305 102호 네일언니2</t>
+          <t>인천광역시 미추홀구 남주길 150 근린생활시설 2동 210호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailunni_</t>
+          <t>https://www.instagram.com/soins_beauty_n</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3899,13 +3903,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>825</v>
+        <v>222</v>
       </c>
       <c r="Q37" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="R37" t="n">
-        <v>881</v>
+        <v>240</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3914,17 +3918,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1277528071</t>
+          <t>2042315946</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1277528071</t>
+          <t>https://m.place.naver.com/place/2042315946</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3936,29 +3940,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>하이스타네일</t>
+          <t>소이네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sssong8759@naver.com</t>
+          <t>bin1549@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0507-1377-6082</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 201동 2030호 하이스타네일</t>
+          <t>인천광역시 미추홀구 경인로 372 201동 지하1층 B1008호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Qxexiqn</t>
+          <t>http://pf.kakao.com/_mxnTtn/chat</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3993,13 +3993,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="Q38" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="R38" t="n">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1591639462</t>
+          <t>2033157749</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591639462</t>
+          <t>https://m.place.naver.com/place/2033157749</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4030,34 +4030,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일로</t>
+          <t>네일구뜨</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kongdw@naver.com</t>
+          <t>kry198@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1378-2633</t>
+          <t>0507-1376-0963</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 4층 4013호</t>
+          <t>인천광역시 미추홀구 미추홀대로578번길 20 1층 네일구뜨</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailo.nailstudio?igsh=bnB4MXhpNzF4MjU%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_xdxgAXb/chat</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="R39" t="n">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,17 +4102,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2019386343</t>
+          <t>1674534211</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019386343</t>
+          <t>https://m.place.naver.com/place/1674534211</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4124,34 +4124,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>디두네일 D.do nail studio</t>
+          <t>네일스튜디오 매료</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ddonail12@naver.com</t>
+          <t>lnj7205@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1423-8033</t>
+          <t>0507-1440-3488</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
+          <t>인천광역시 미추홀구 경인로 372 아인에비뉴 2층 2098호 (투썸플레이스 위)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Ukxhxmn</t>
+          <t>https://www.instagram.com/nailstudiomeryo/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4172,7 +4172,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4181,13 +4181,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>62</v>
+        <v>249</v>
       </c>
       <c r="Q40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R40" t="n">
-        <v>75</v>
+        <v>263</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,17 +4196,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2003325308</t>
+          <t>1152584583</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003325308</t>
+          <t>https://m.place.naver.com/place/1152584583</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4218,29 +4218,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일미니</t>
+          <t>네일링</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>gold77com@naver.com</t>
+          <t>hans6758724@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1379-4411</t>
+          <t>0507-1346-3521</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로489번길 107 1층 102호</t>
+          <t>인천광역시 미추홀구 학익로80번길 11 시티오씨엘3단지 메가박스 상가 2층 B-224호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mi_ni</t>
+          <t>https://www.instagram.com/__nailing</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4275,13 +4275,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>414</v>
+        <v>229</v>
       </c>
       <c r="Q41" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="R41" t="n">
-        <v>468</v>
+        <v>264</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,17 +4290,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1633509740</t>
+          <t>1351774557</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633509740</t>
+          <t>https://m.place.naver.com/place/1351774557</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4312,29 +4312,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>반디인하우스 도화앨리웨이점</t>
+          <t>용쥬르샵 인천본점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>bandinhouse_dohwa@naver.com</t>
+          <t>iiidydwn@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1392-8241</t>
+          <t>032-423-2963</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
+          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
+          <t>https://blog.naver.com/iiidydwn</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4369,13 +4369,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>340</v>
+        <v>662</v>
       </c>
       <c r="Q42" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="R42" t="n">
-        <v>419</v>
+        <v>717</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,17 +4384,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1485881474</t>
+          <t>1845960167</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485881474</t>
+          <t>https://m.place.naver.com/place/1845960167</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4406,29 +4406,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>제리네일</t>
+          <t>란또 네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>wjdsla91777@naver.com</t>
+          <t>wealth_8674@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1479-5891</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 1층 1055호</t>
+          <t>인천광역시 미추홀구 매소홀로 407 예지빌딩 3층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j7n._s?igsh=N2UybHpmZjRnbWJz&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/randdo24.nail_beauty</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4463,13 +4459,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>260</v>
+        <v>216</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="R43" t="n">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4478,17 +4474,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1744004614</t>
+          <t>1119025988</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1744004614</t>
+          <t>https://m.place.naver.com/place/1119025988</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4500,25 +4496,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일을 띠다</t>
+          <t>도화네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nail_ddida@naver.com</t>
+          <t>gsqnls2u@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1373-9131</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 13층 13016호</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_ddida</t>
+          <t>https://www.instagram.com/dohwa_nail_</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4553,13 +4553,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>131</v>
+        <v>693</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>149</v>
+        <v>695</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4568,17 +4568,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1370791561</t>
+          <t>1155887763</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370791561</t>
+          <t>https://m.place.naver.com/place/1155887763</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4590,30 +4590,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일핏</t>
+          <t>네일언니</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>nailfitsl@naver.com</t>
+          <t>pjh48886@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1360-4886</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 311 비젼프라자 2층 206호</t>
+          <t>인천광역시 미추홀구 인하로 97 102 호 네일언니</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FxiNCG</t>
+          <t>https://www.instagram.com/nail_unni_</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4634,7 +4638,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4643,13 +4647,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>932</v>
+        <v>499</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="R45" t="n">
-        <v>944</v>
+        <v>540</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4658,17 +4662,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>718951949</t>
+          <t>36184234</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/718951949</t>
+          <t>https://m.place.naver.com/place/36184234</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4680,29 +4684,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일스프링</t>
+          <t>효즈네일&amp;속눈썹&amp;왁싱</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>witty_luna@naver.com</t>
+          <t>kwoun0303@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1465-2797</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
+          <t>인천광역시 미추홀구 인하로 67</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___spring</t>
+          <t>http://instagram.com/hyoz_official</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4737,13 +4737,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>117</v>
+        <v>1148</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="R46" t="n">
-        <v>127</v>
+        <v>1254</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4752,17 +4752,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2098983836</t>
+          <t>1543447735</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098983836</t>
+          <t>https://m.place.naver.com/place/1543447735</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4774,34 +4774,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일혜 도화점</t>
+          <t>끌림네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>nailhye_@naver.com</t>
+          <t>cclimnail@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1487-9095</t>
+          <t>032-872-9118</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
+          <t>인천광역시 미추홀구 소성로 16 1층 110-2호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.hye/</t>
+          <t>http://pf.kakao.com/_iBxexon</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4822,7 +4822,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>316</v>
+        <v>122</v>
       </c>
       <c r="Q47" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>333</v>
+        <v>125</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4846,17 +4846,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1396481559</t>
+          <t>2064653044</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396481559</t>
+          <t>https://m.place.naver.com/place/2064653044</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4868,29 +4868,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일파인</t>
+          <t>메이에르 네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>milkysuk@naver.com</t>
+          <t>dmsal6910@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1490-7041</t>
+          <t>0507-1472-1341</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로224번길 14 1층 네일파인</t>
+          <t>인천광역시 미추홀구 인주대로330번길 23 1층 메이에르네일</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_pine</t>
+          <t>https://www.instagram.com/meyere_nail</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4925,13 +4925,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="Q48" t="n">
-        <v>212</v>
+        <v>13</v>
       </c>
       <c r="R48" t="n">
-        <v>340</v>
+        <v>90</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1679016661</t>
+          <t>2090344240</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679016661</t>
+          <t>https://m.place.naver.com/place/2090344240</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4962,29 +4962,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일도 희</t>
+          <t>아무아네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sunjoy0902@naver.com</t>
+          <t>zld9142@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1304-7934</t>
+          <t>0507-1365-1547</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 321-1 1층 101호 네일도, 희</t>
+          <t>인천광역시 미추홀구 주안동로 39 1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildo_hee</t>
+          <t>https://youtube.com/@amouanail_diary?si=mNU7eI9gjC1L4C3W</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5010,7 +5010,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5019,13 +5019,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>295</v>
+        <v>211</v>
       </c>
       <c r="Q49" t="n">
-        <v>7</v>
+        <v>490</v>
       </c>
       <c r="R49" t="n">
-        <v>302</v>
+        <v>701</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5034,17 +5034,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1208564106</t>
+          <t>2098522217</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208564106</t>
+          <t>https://m.place.naver.com/place/2098522217</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5056,29 +5056,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일진</t>
+          <t>네일혜 도화점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kng026@naver.com</t>
+          <t>nailhye_@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1343-3705</t>
+          <t>0507-1487-9095</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로32번길 22 1층 104호 네일진</t>
+          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___jin_?igsh=ZHIxemZmNXcxNWtq&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/_nail.hye/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>68</v>
+        <v>323</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R50" t="n">
-        <v>78</v>
+        <v>340</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5128,17 +5128,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1343927659</t>
+          <t>1396481559</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1343927659</t>
+          <t>https://m.place.naver.com/place/1396481559</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5150,34 +5150,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일플래닛</t>
+          <t>디두네일 D.do nail studio</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>znzltkfkd123@naver.com</t>
+          <t>ddonail12@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1470-6637</t>
+          <t>0507-1423-8033</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 포레나 201동(아인여성병원건물) 지상2층 2017호</t>
+          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/znzltkfkd123</t>
+          <t>http://pf.kakao.com/_Ukxhxmn</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5198,22 +5198,22 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>346</v>
+        <v>66</v>
       </c>
       <c r="Q51" t="n">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="R51" t="n">
-        <v>443</v>
+        <v>80</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5222,17 +5222,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1077662255</t>
+          <t>2003325308</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077662255</t>
+          <t>https://m.place.naver.com/place/2003325308</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5244,34 +5244,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>레푸스 인하대역점 내성발톱 무좀발톱 발각질 문제성발</t>
+          <t>예뻐진</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>hhs3556@naver.com</t>
+          <t>tlsguswls81@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1314-9364</t>
+          <t>0507-1334-0060</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 309 노블레스 빌딩 10층 1004호</t>
+          <t>인천광역시 미추홀구 인하로 301-2 2층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
+          <t>http://pf.kakao.com/_gFGxbb</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5292,7 +5292,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="Q52" t="n">
-        <v>441</v>
+        <v>91</v>
       </c>
       <c r="R52" t="n">
-        <v>578</v>
+        <v>187</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5316,17 +5316,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1027018171</t>
+          <t>1366454286</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027018171</t>
+          <t>https://m.place.naver.com/place/1366454286</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5338,29 +5338,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>에이풋케어 내성발톱 발톱무좀 발각질 문제성발</t>
+          <t>모드니에네일 인천용현점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>illbwidu@naver.com</t>
+          <t>wlsk4075@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1378-4114</t>
+          <t>032-888-2430</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 시티필드 6층 6013호</t>
+          <t>인천광역시 미추홀구 낙섬중로 61 1층 101호,102호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/illbwidu</t>
+          <t>http://instagram.com/modnie_nail</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5395,13 +5395,13 @@
         </is>
       </c>
       <c r="P53" t="n">
+        <v>773</v>
+      </c>
+      <c r="Q53" t="n">
         <v>101</v>
       </c>
-      <c r="Q53" t="n">
-        <v>483</v>
-      </c>
       <c r="R53" t="n">
-        <v>584</v>
+        <v>874</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5410,17 +5410,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1319855180</t>
+          <t>1031233548</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1319855180</t>
+          <t>https://m.place.naver.com/place/1031233548</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5432,34 +5432,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>아무아네일</t>
+          <t>고운손</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jujuhehe6466@naver.com</t>
+          <t>ghghrjftm@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1365-1547</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안동로 39 1층</t>
+          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://youtube.com/@amouanail_diary?si=mNU7eI9gjC1L4C3W</t>
+          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5480,7 +5476,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5489,13 +5485,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="Q54" t="n">
-        <v>267</v>
+        <v>2</v>
       </c>
       <c r="R54" t="n">
-        <v>467</v>
+        <v>166</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5504,17 +5500,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2098522217</t>
+          <t>1926481487</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098522217</t>
+          <t>https://m.place.naver.com/place/1926481487</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5526,29 +5522,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일또방</t>
+          <t>네일스프링</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>wldus318@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1378-8088</t>
+          <t>0507-1465-2797</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 665 1층</t>
+          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ddobang/</t>
+          <t>https://www.instagram.com/nail___spring</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5583,13 +5579,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>632</v>
+        <v>123</v>
       </c>
       <c r="Q55" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="R55" t="n">
-        <v>654</v>
+        <v>133</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5598,17 +5594,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1177770049</t>
+          <t>2098983836</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1177770049</t>
+          <t>https://m.place.naver.com/place/2098983836</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5620,29 +5616,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일그리움 주안점</t>
+          <t>네일맑음</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>cherryjoa_v@naver.com</t>
+          <t>s1514@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1443-5044</t>
+          <t>0507-1489-0530</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로614번길 42 101호 네일그리움</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_geurium</t>
+          <t>https://www.instagram.com/yuneungyeong4</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5677,13 +5673,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="Q56" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="R56" t="n">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5692,17 +5688,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1994727673</t>
+          <t>1539397163</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994727673</t>
+          <t>https://m.place.naver.com/place/1539397163</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5714,34 +5710,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일스하리</t>
+          <t>네일파인</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>yoollina_@naver.com</t>
+          <t>milkysuk@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1447-1684</t>
+          <t>0507-1490-7041</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로864번길 24 여성복지관 내 407호</t>
+          <t>인천광역시 미추홀구 인주대로224번길 14 1층 네일파인</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rdvxgn</t>
+          <t>https://www.instagram.com/nail_pine</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5771,13 +5767,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="Q57" t="n">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="R57" t="n">
-        <v>109</v>
+        <v>340</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5786,17 +5782,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2056712513</t>
+          <t>1679016661</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056712513</t>
+          <t>https://m.place.naver.com/place/1679016661</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5808,30 +5804,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>소이네일</t>
+          <t>부티스튜디오</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bin1549@naver.com</t>
+          <t>avecbeaute_@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1371-2954</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 201동 지하1층 B1008호</t>
+          <t>인천광역시 미추홀구 인하로91번길 71 1층일부호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_mxnTtn/chat</t>
+          <t>https://www.instagram.com/buti_studio?igsh=MWJsdzcyNDNobGc0aw==</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5852,7 +5852,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R58" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2033157749</t>
+          <t>2061859427</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033157749</t>
+          <t>https://m.place.naver.com/place/2061859427</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5898,29 +5898,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>미다움네일</t>
+          <t>착한언니피부네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>dksdidwhdk@naver.com</t>
+          <t>u4melive@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1442-0506</t>
+          <t>0507-1368-0680</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
+          <t>인천광역시 미추홀구 낙섬중로 73 1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://instagram.com/me_daoom</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>22</v>
+        <v>383</v>
       </c>
       <c r="Q59" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>81</v>
+        <v>385</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5970,17 +5970,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1835371224</t>
+          <t>2096439755</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835371224</t>
+          <t>https://m.place.naver.com/place/2096439755</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5992,34 +5992,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>끌림네일</t>
+          <t>문제성 손,발 오감네일 도화점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>cclimnail@naver.com</t>
+          <t>ogam_foot_nail@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>032-872-9118</t>
+          <t>0507-1388-5117</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 16 1층 110-2호</t>
+          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_iBxexon</t>
+          <t>https://blog.naver.com/ogam_foot_nail</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6040,7 +6040,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6049,13 +6049,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>109</v>
+        <v>663</v>
       </c>
       <c r="Q60" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="R60" t="n">
-        <v>112</v>
+        <v>732</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2064653044</t>
+          <t>1716147754</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064653044</t>
+          <t>https://m.place.naver.com/place/1716147754</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6086,30 +6086,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>디에즈네일</t>
+          <t>네일스하리</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>tombo613@naver.com</t>
+          <t>yoollina_@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1447-1684</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 52 104호 디에즈네일</t>
+          <t>인천광역시 미추홀구 경원대로864번길 24 여성복지관 내 407호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://instagram.com/dieznail</t>
+          <t>http://pf.kakao.com/_rdvxgn</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6130,7 +6134,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6139,13 +6143,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="Q61" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="R61" t="n">
-        <v>250</v>
+        <v>111</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6154,17 +6158,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1520395186</t>
+          <t>2056712513</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520395186</t>
+          <t>https://m.place.naver.com/place/2056712513</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6176,29 +6180,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>오드리뷰티</t>
+          <t>네일진</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>saerom66@naver.com</t>
+          <t>kng026@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1367-2646</t>
+          <t>0507-1343-3705</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 102 오드리뷰티 3층</t>
+          <t>인천광역시 미추홀구 낙섬중로32번길 22 1층 104호 네일진</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreybeauty._1</t>
+          <t>https://www.instagram.com/nail___jin_?igsh=ZHIxemZmNXcxNWtq&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6224,7 +6228,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6233,13 +6237,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="Q62" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="R62" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6248,17 +6252,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1722511887</t>
+          <t>1343927659</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722511887</t>
+          <t>https://m.place.naver.com/place/1343927659</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6270,29 +6274,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>드림드로잉</t>
+          <t>네일,포슬</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>powerkorea0505@naver.com</t>
+          <t>r__r_b@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1365-9785</t>
+          <t>0507-1386-5035</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 7층 7001호 드림드로잉</t>
+          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d_dnail0818</t>
+          <t>https://www.instagram.com/nail_poseul_</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6327,13 +6331,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>91</v>
+        <v>407</v>
       </c>
       <c r="Q63" t="n">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="R63" t="n">
-        <v>244</v>
+        <v>448</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6342,17 +6346,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1887397016</t>
+          <t>1050625355</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1887397016</t>
+          <t>https://m.place.naver.com/place/1050625355</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6364,29 +6368,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>디어마인샵</t>
+          <t>모도리 네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>unthsu@naver.com</t>
+          <t>dbsalwjd88@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1403-2780</t>
+          <t>0507-1330-1268</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인남길30번길 94 1층 디어마인샵</t>
+          <t>인천광역시 미추홀구 독배로382번길 12 1층 모도리네일</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://instagram.com/dear_mine91</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6396,7 +6400,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6417,17 +6421,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1291</v>
+        <v>319</v>
       </c>
       <c r="Q64" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>1344</v>
+        <v>321</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6436,17 +6440,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1144594831</t>
+          <t>1752538431</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1144594831</t>
+          <t>https://m.place.naver.com/place/1752538431</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6458,29 +6462,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>홀리네일</t>
+          <t>레푸스 인하대역점 내성발톱 무좀발톱 발각질 문제성발</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>miho6677@naver.com</t>
+          <t>hhs3556@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1409-1716</t>
+          <t>0507-1314-9364</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로446번길 7 1층 홀리뷰티</t>
+          <t>인천광역시 미추홀구 독배로 309 노블레스 빌딩 10층 1004호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_holly_nail_0</t>
+          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6515,13 +6519,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>436</v>
       </c>
       <c r="R65" t="n">
-        <v>43</v>
+        <v>574</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6530,17 +6534,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1681381393</t>
+          <t>1027018171</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681381393</t>
+          <t>https://m.place.naver.com/place/1027018171</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6552,25 +6556,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일오숑</t>
+          <t>아무르네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>nailon22@naver.com</t>
+          <t>07alsrud@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1360-5941</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
+          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2103호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_osyong/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6580,7 +6588,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6601,17 +6609,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>258</v>
+        <v>102</v>
       </c>
       <c r="Q66" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="R66" t="n">
-        <v>277</v>
+        <v>110</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6620,17 +6628,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1518702391</t>
+          <t>1701492501</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1518702391</t>
+          <t>https://m.place.naver.com/place/1701492501</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6642,34 +6650,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>인블리네일</t>
+          <t>하드킴네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bbobbolee2@naver.com</t>
+          <t>hardkim_nail@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>070-7643-2243</t>
+          <t>0507-1386-0240</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
+          <t>인천광역시 미추홀구 학익로80번길 11 312동 2층 B-221호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xhUIxmC</t>
+          <t>https://blog.naver.com/hardkim_nail</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6679,7 +6687,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6690,7 +6698,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6699,13 +6707,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>409</v>
+        <v>73</v>
       </c>
       <c r="Q67" t="n">
-        <v>1219</v>
+        <v>42</v>
       </c>
       <c r="R67" t="n">
-        <v>1628</v>
+        <v>115</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6714,17 +6722,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>63265483</t>
+          <t>2095090349</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/63265483</t>
+          <t>https://m.place.naver.com/place/2095090349</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6736,12 +6744,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>효즈네일&amp;속눈썹&amp;왁싱</t>
+          <t>예뻐지는네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kwoun0303@naver.com</t>
+          <t>jisoo851208@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -6749,12 +6757,12 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 67</t>
+          <t>인천광역시 미추홀구 미추홀대로578번길 9 1층(주안동)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://instagram.com/hyoz_official</t>
+          <t>https://www.instagram.com/beautynail_0901</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6789,13 +6797,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1140</v>
+        <v>113</v>
       </c>
       <c r="Q68" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="R68" t="n">
-        <v>1246</v>
+        <v>242</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6804,17 +6812,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1543447735</t>
+          <t>1148534617</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543447735</t>
+          <t>https://m.place.naver.com/place/1148534617</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6826,29 +6834,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>봉구네일</t>
+          <t>네일데이원</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>94rnrdudal@naver.com</t>
+          <t>lisianthus0330@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1320-0380</t>
+          <t>0507-1337-2867</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86</t>
+          <t>인천광역시 미추홀구 경원대로834번길 27-12 NS빌딩 2층 203호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bonggu_nail</t>
+          <t>https://www.instagram.com/nail_dayone</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6883,13 +6891,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>100</v>
+        <v>237</v>
       </c>
       <c r="Q69" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="R69" t="n">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6898,17 +6906,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1965492062</t>
+          <t>1689139269</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965492062</t>
+          <t>https://m.place.naver.com/place/1689139269</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6920,25 +6928,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>라보떼 뷰티</t>
+          <t>네일,꽃이피다</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>skgus7415@naver.com</t>
+          <t>nail910401@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1311-6628</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
+          <t>인천광역시 미추홀구 매소홀로 262 시티필드 7층 7012호 네일꽃이피다</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/labeaute7027__</t>
+          <t>https://www.instagram.com/nail.bloom__</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6973,13 +6985,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>262</v>
+        <v>172</v>
       </c>
       <c r="Q70" t="n">
-        <v>252</v>
+        <v>35</v>
       </c>
       <c r="R70" t="n">
-        <v>514</v>
+        <v>207</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6988,17 +7000,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1828605681</t>
+          <t>1271233277</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828605681</t>
+          <t>https://m.place.naver.com/place/1271233277</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7010,29 +7022,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>주엘로</t>
+          <t>젤리네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jew_ell@naver.com</t>
+          <t>mi2013@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1431-9930</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로112번길 2 2층 203호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_jooello</t>
+          <t>https://open.kakao.com/o/s1SGa70g</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7058,7 +7066,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7067,13 +7075,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>230</v>
+        <v>391</v>
       </c>
       <c r="Q71" t="n">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="R71" t="n">
-        <v>250</v>
+        <v>498</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7082,17 +7090,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1125345899</t>
+          <t>1140244485</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125345899</t>
+          <t>https://m.place.naver.com/place/1140244485</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7104,29 +7112,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>하드킴네일</t>
+          <t>네일언니</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>hardkim_nail@naver.com</t>
+          <t>555__555@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1386-0240</t>
+          <t>0507-1315-4886</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 학익로80번길 11 312동 2층 B-221호</t>
+          <t>인천광역시 미추홀구 독배로 305 102호 네일언니2</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hardkim_nail</t>
+          <t>https://www.instagram.com/nailunni_</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7141,7 +7149,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7161,13 +7169,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>72</v>
+        <v>831</v>
       </c>
       <c r="Q72" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="R72" t="n">
-        <v>114</v>
+        <v>887</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7176,17 +7184,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2095090349</t>
+          <t>1277528071</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095090349</t>
+          <t>https://m.place.naver.com/place/1277528071</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7198,25 +7206,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>란또 네일&amp;뷰티</t>
+          <t>네일팔레트</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>wealth_8674@naver.com</t>
+          <t>nail4season@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1334-0294</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 407 예지빌딩 3층</t>
+          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/randdo24.nail_beauty</t>
+          <t>https://www.instagram.com/palette_nailll</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7251,13 +7263,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="Q73" t="n">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="R73" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7266,17 +7278,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1119025988</t>
+          <t>1167629339</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1119025988</t>
+          <t>https://m.place.naver.com/place/1167629339</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7288,34 +7300,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일구뜨</t>
+          <t>라보떼 뷰티</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kry198@naver.com</t>
+          <t>dlatmfrl5824@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1376-0963</t>
+          <t>0507-1377-9030</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로578번길 20 1층 네일구뜨</t>
+          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdxgAXb/chat</t>
+          <t>https://www.instagram.com/labeaute7027__</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7336,7 +7348,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7345,13 +7357,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>93</v>
+        <v>267</v>
       </c>
       <c r="Q74" t="n">
-        <v>31</v>
+        <v>249</v>
       </c>
       <c r="R74" t="n">
-        <v>124</v>
+        <v>516</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7360,17 +7372,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1674534211</t>
+          <t>1828605681</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674534211</t>
+          <t>https://m.place.naver.com/place/1828605681</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7382,29 +7394,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>용쥬르샵 인천본점</t>
+          <t>네일또방</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>iiidydwn@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>032-423-2963</t>
+          <t>0507-1378-8088</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
+          <t>인천광역시 미추홀구 미추홀대로 665 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iiidydwn</t>
+          <t>https://www.instagram.com/nail_ddobang/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7419,7 +7431,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7439,13 +7451,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>660</v>
+        <v>634</v>
       </c>
       <c r="Q75" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="R75" t="n">
-        <v>715</v>
+        <v>656</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7454,17 +7466,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1845960167</t>
+          <t>1177770049</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845960167</t>
+          <t>https://m.place.naver.com/place/1177770049</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7476,29 +7488,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일고운</t>
+          <t>블루진네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>won_jieun@naver.com</t>
+          <t>whole4ni@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1301-1928</t>
+          <t>0507-1407-5343</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86 주안역 지하도 상가 109호</t>
+          <t>인천광역시 미추홀구 경원대로897번길 40 상가 1층 101호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_goeun</t>
+          <t>https://www.instagram.com/bluejin_nail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7533,13 +7545,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="Q76" t="n">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="R76" t="n">
-        <v>41</v>
+        <v>311</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7548,17 +7560,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1691519525</t>
+          <t>1920868303</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1691519525</t>
+          <t>https://m.place.naver.com/place/1920868303</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/남구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/남구_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에스네일</t>
+          <t>뷰티컴트루</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>snail4324@naver.com</t>
+          <t>wlsk4075@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1406-3132</t>
+          <t>0507-1372-5309</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
+          <t>인천광역시 미추홀구 낙섬서로18번길 27-20 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snail0070</t>
+          <t>https://www.instagram.com/beauty_cometrue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="Q2" t="n">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>146</v>
+        <v>260</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>38286683</t>
+          <t>2001250057</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38286683</t>
+          <t>https://m.place.naver.com/place/2001250057</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미라클뷰티&amp;네일</t>
+          <t>네일또방</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>alsdudvvv3@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1330-3178</t>
+          <t>0507-1378-8088</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 12층1호</t>
+          <t>인천광역시 미추홀구 미추홀대로 665 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miraclebeauty_nail?igsh=MW5nN3NoOHd0OG51dg==</t>
+          <t>https://www.instagram.com/nail_ddobang/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>194</v>
+        <v>634</v>
       </c>
       <c r="Q3" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="R3" t="n">
-        <v>274</v>
+        <v>656</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2040709432</t>
+          <t>1177770049</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040709432</t>
+          <t>https://m.place.naver.com/place/1177770049</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>인블리네일</t>
+          <t>하이스타네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bbobbolee2@naver.com</t>
+          <t>mumu800@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>070-7643-2243</t>
+          <t>0507-1377-6082</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
+          <t>인천광역시 미추홀구 경인로 372 201동 2030호 하이스타네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xhUIxmC</t>
+          <t>http://pf.kakao.com/_Qxexiqn</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>416</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1221</v>
+        <v>43</v>
       </c>
       <c r="R4" t="n">
-        <v>1637</v>
+        <v>57</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>63265483</t>
+          <t>1591639462</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/63265483</t>
+          <t>https://m.place.naver.com/place/1591639462</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에이풋케어 내성발톱 발톱무좀 발각질 문제성발</t>
+          <t>반디인하우스 도화앨리웨이점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>illbwidu@naver.com</t>
+          <t>bandinhouse_dohwa@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1378-4114</t>
+          <t>0507-1392-8241</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 시티필드 6층 6013호</t>
+          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/illbwidu</t>
+          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>103</v>
+        <v>341</v>
       </c>
       <c r="Q5" t="n">
-        <v>485</v>
+        <v>79</v>
       </c>
       <c r="R5" t="n">
-        <v>588</v>
+        <v>420</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1319855180</t>
+          <t>1485881474</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1319855180</t>
+          <t>https://m.place.naver.com/place/1485881474</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일 해봄</t>
+          <t>네일,꽃이피다</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eruriee@naver.com</t>
+          <t>nail910401@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1303-4226</t>
+          <t>0507-1311-6628</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 토금중로30번길 9 1층</t>
+          <t>인천광역시 미추홀구 매소홀로 262 시티필드 7층 7012호 네일꽃이피다</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_haebom/</t>
+          <t>https://www.instagram.com/nail.bloom__</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>876</v>
+        <v>172</v>
       </c>
       <c r="Q6" t="n">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="R6" t="n">
-        <v>1056</v>
+        <v>207</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>38301920</t>
+          <t>1271233277</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38301920</t>
+          <t>https://m.place.naver.com/place/1271233277</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일에보</t>
+          <t>우니네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>daniya1210@naver.com</t>
+          <t>sseonni51@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1311-6332</t>
+          <t>0507-1390-7191</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 201동 B2층 2055호</t>
+          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 2층 2057호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailevo_</t>
+          <t>https://www.instagram.com/ooninail_?igsh=YXc5aDlrOHZoeDh1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>343</v>
+        <v>93</v>
       </c>
       <c r="Q7" t="n">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="R7" t="n">
-        <v>421</v>
+        <v>111</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1252060771</t>
+          <t>1013712359</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252060771</t>
+          <t>https://m.place.naver.com/place/1013712359</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>채움네일</t>
+          <t>네일오숑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rhdwnsla5656@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1326-3123</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로228번길 11 1층</t>
+          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaeum_nail_</t>
+          <t>https://www.instagram.com/nail_osyong/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="R8" t="n">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1824103581</t>
+          <t>1518702391</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824103581</t>
+          <t>https://m.place.naver.com/place/1518702391</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일그리움 주안점</t>
+          <t>네일스프링</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cherryjoa_v@naver.com</t>
+          <t>wldus318@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1443-5044</t>
+          <t>0507-1465-2797</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로614번길 42 101호 네일그리움</t>
+          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_geurium</t>
+          <t>https://www.instagram.com/nail___spring</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>255</v>
+        <v>125</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>276</v>
+        <v>135</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1994727673</t>
+          <t>2098983836</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994727673</t>
+          <t>https://m.place.naver.com/place/2098983836</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1316,34 +1312,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>쿄우네일 석바위점</t>
+          <t>네일로</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dlthwjd7530@naver.com</t>
+          <t>loosetime@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1394-6274</t>
+          <t>0507-1378-2633</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로 858 3층 일부호 쿄우네일</t>
+          <t>인천광역시 미추홀구 매소홀로 262 4층 4013호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdlxjBn</t>
+          <t>https://www.instagram.com/nailo.nailstudio?igsh=bnB4MXhpNzF4MjU%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2023963502</t>
+          <t>2019386343</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023963502</t>
+          <t>https://m.place.naver.com/place/2019386343</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1410,25 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일오숑</t>
+          <t>미라클뷰티&amp;네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>ssoyoung0318@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1330-3178</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 12층1호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_osyong/</t>
+          <t>https://www.instagram.com/miraclebeauty_nail?igsh=MW5nN3NoOHd0OG51dg==</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="R11" t="n">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1518702391</t>
+          <t>2040709432</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1518702391</t>
+          <t>https://m.place.naver.com/place/2040709432</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1500,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아르떼네일</t>
+          <t>라 폴리쉬드</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>arte__nail_@naver.com</t>
+          <t>khw23540@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1323-0926</t>
+          <t>0507-1354-5656</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
+          <t>인천광역시 미추홀구 승학길 28 105호 1층상가 라 폴리쉬드</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/arte__nail_</t>
+          <t>https://www.instagram.com/la_polished?igsh=djk3a2lwb3ppdDRk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1548,7 +1548,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>391</v>
+        <v>77</v>
       </c>
       <c r="Q12" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>450</v>
+        <v>85</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1775601804</t>
+          <t>2080412833</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1775601804</t>
+          <t>https://m.place.naver.com/place/2080412833</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>뾰로롱네일</t>
+          <t>네일링</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mjy22977@naver.com</t>
+          <t>gulgomi@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1302-6657</t>
+          <t>0507-1346-3521</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
+          <t>인천광역시 미추홀구 학익로80번길 11 시티오씨엘3단지 메가박스 상가 2층 B-224호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/__nailing</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1647,17 +1647,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R13" t="n">
-        <v>83</v>
+        <v>264</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2058778627</t>
+          <t>1351774557</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058778627</t>
+          <t>https://m.place.naver.com/place/1351774557</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1688,29 +1688,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일인더문</t>
+          <t>아무르네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>beauty_n_nail@naver.com</t>
+          <t>07alsrud@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1436-0467</t>
+          <t>0507-1360-5941</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 237 1층</t>
+          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2103호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_inthemoon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1741,18 +1741,18 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8</v>
+      </c>
+      <c r="R14" t="n">
         <v>110</v>
       </c>
-      <c r="Q14" t="n">
-        <v>52</v>
-      </c>
-      <c r="R14" t="n">
-        <v>162</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1204881858</t>
+          <t>1701492501</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204881858</t>
+          <t>https://m.place.naver.com/place/1701492501</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1782,29 +1782,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일플래닛</t>
+          <t>제리네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>znzltkfkd123@naver.com</t>
+          <t>wjdsla91777@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1470-6637</t>
+          <t>0507-1479-5891</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 포레나 201동(아인여성병원건물) 지상2층 2017호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 1층 1055호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/znzltkfkd123</t>
+          <t>https://www.instagram.com/j7n._s?igsh=N2UybHpmZjRnbWJz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>346</v>
+        <v>263</v>
       </c>
       <c r="Q15" t="n">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
-        <v>443</v>
+        <v>278</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1077662255</t>
+          <t>1744004614</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077662255</t>
+          <t>https://m.place.naver.com/place/1744004614</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1876,34 +1876,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>제로네일</t>
+          <t>걸스네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>seeat_f@naver.com</t>
+          <t>ymj11969@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1359-4583</t>
+          <t>0507-1410-0304</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
+          <t>인천광역시 미추홀구 소성로 133 걸스네일</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zeronail_art</t>
+          <t>https://link.thinkofyou.kr/girls_nail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1924,7 +1924,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>333</v>
+        <v>158</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="R16" t="n">
-        <v>338</v>
+        <v>212</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1613054835</t>
+          <t>37257261</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613054835</t>
+          <t>https://m.place.naver.com/place/37257261</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1970,34 +1970,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일 품은 손</t>
+          <t>용쥬르샵 인천본점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sssh200118@naver.com</t>
+          <t>iiidydwn@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1360-1453</t>
+          <t>032-423-2963</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로357번길 5-58 1층 네일품은손</t>
+          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_eQCrb</t>
+          <t>https://blog.naver.com/iiidydwn</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2018,7 +2018,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>98</v>
+        <v>662</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="R17" t="n">
-        <v>122</v>
+        <v>717</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1680001412</t>
+          <t>1845960167</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1680001412</t>
+          <t>https://m.place.naver.com/place/1845960167</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2064,34 +2064,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>라 폴리쉬드</t>
+          <t>아무아네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>khw23540@naver.com</t>
+          <t>zld9142@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1354-5656</t>
+          <t>0507-1365-1547</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 승학길 28 105호 1층상가 라 폴리쉬드</t>
+          <t>인천광역시 미추홀구 주안동로 39 1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/la_polished?igsh=djk3a2lwb3ppdDRk</t>
+          <t>https://youtube.com/@amouanail_diary?si=mNU7eI9gjC1L4C3W</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2112,7 +2112,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>533</v>
       </c>
       <c r="R18" t="n">
-        <v>93</v>
+        <v>743</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2080412833</t>
+          <t>2098522217</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080412833</t>
+          <t>https://m.place.naver.com/place/2098522217</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2158,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>루미랑네일</t>
+          <t>하드킴네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jine_blog@naver.com</t>
+          <t>hardkim_nail@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1371-1706</t>
+          <t>0507-1386-0240</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
+          <t>인천광역시 미추홀구 학익로80번길 11 312동 2층 B-221호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rumirang_nail</t>
+          <t>https://blog.naver.com/hardkim_nail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>255</v>
+        <v>74</v>
       </c>
       <c r="Q19" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="R19" t="n">
-        <v>309</v>
+        <v>116</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,17 +2230,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1156304078</t>
+          <t>2095090349</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156304078</t>
+          <t>https://m.place.naver.com/place/2095090349</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2252,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>디어마인샵</t>
+          <t>네일데이원</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unthsu@naver.com</t>
+          <t>aar422@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1403-2780</t>
+          <t>0507-1337-2867</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인남길30번길 94 1층 디어마인샵</t>
+          <t>인천광역시 미추홀구 경원대로834번길 27-12 NS빌딩 2층 203호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://instagram.com/dear_mine91</t>
+          <t>https://www.instagram.com/nail_dayone</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1300</v>
+        <v>237</v>
       </c>
       <c r="Q20" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1353</v>
+        <v>240</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,17 +2324,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1144594831</t>
+          <t>1689139269</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1144594831</t>
+          <t>https://m.place.naver.com/place/1689139269</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2346,39 +2346,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>디몽드네일</t>
+          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>eautorride2@naver.com</t>
+          <t>dritn-nail_a_o@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1392-5341</t>
+          <t>0507-1325-1015</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 수봉남로 1 (용현동)2층</t>
+          <t>인천광역시 미추홀구 장천로 57 1층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://m.themosttimes.co.kr/39655</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2399,17 +2399,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="R21" t="n">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1670918594</t>
+          <t>1166150967</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1670918594</t>
+          <t>https://m.place.naver.com/place/1166150967</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2440,29 +2440,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일미니</t>
+          <t>아르떼네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>snow1blossom@naver.com</t>
+          <t>arte__nail_@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1379-4411</t>
+          <t>0507-1323-0926</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로489번길 107 1층 102호</t>
+          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mi_ni</t>
+          <t>https://blog.naver.com/arte__nail_</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2488,7 +2488,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="Q22" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R22" t="n">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,17 +2512,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1633509740</t>
+          <t>1775601804</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633509740</t>
+          <t>https://m.place.naver.com/place/1775601804</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2534,30 +2534,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일핏</t>
+          <t>네일그리움 주안점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nailfitsl@naver.com</t>
+          <t>cherryjoa_v@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1443-5044</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 311 비젼프라자 2층 206호</t>
+          <t>인천광역시 미추홀구 미추홀대로614번길 42 101호 네일그리움</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FxiNCG</t>
+          <t>https://www.instagram.com/nail_geurium</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2578,7 +2582,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2587,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>932</v>
+        <v>255</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="R23" t="n">
-        <v>944</v>
+        <v>276</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2606,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>718951949</t>
+          <t>1994727673</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/718951949</t>
+          <t>https://m.place.naver.com/place/1994727673</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2624,29 +2628,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>로이네일</t>
+          <t>디두네일 D.do nail studio</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>wlgus1647@naver.com</t>
+          <t>ddonail12@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1350-5396</t>
+          <t>0507-1423-8033</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
+          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vxkKMs/chat</t>
+          <t>http://pf.kakao.com/_Ukxhxmn</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2681,13 +2685,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="Q24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2700,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1765283529</t>
+          <t>2003325308</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765283529</t>
+          <t>https://m.place.naver.com/place/2003325308</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2718,34 +2722,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>제리네일</t>
+          <t>네일구뜨</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>wjdsla91777@naver.com</t>
+          <t>kry198@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1479-5891</t>
+          <t>0507-1376-0963</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 1층 1055호</t>
+          <t>인천광역시 미추홀구 미추홀대로578번길 20 1층 네일구뜨</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j7n._s?igsh=N2UybHpmZjRnbWJz&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_xdxgAXb/chat</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2766,7 +2770,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2775,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>262</v>
+        <v>95</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="R25" t="n">
-        <v>277</v>
+        <v>126</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,17 +2794,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1744004614</t>
+          <t>1674534211</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1744004614</t>
+          <t>https://m.place.naver.com/place/1674534211</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2812,34 +2816,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>홀리네일</t>
+          <t>인블리네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ko3hi@naver.com</t>
+          <t>bbobbolee2@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1409-1716</t>
+          <t>070-7643-2243</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로446번길 7 1층 홀리뷰티</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_holly_nail_0</t>
+          <t>https://pf.kakao.com/_xhUIxmC</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2860,7 +2864,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2869,13 +2873,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>33</v>
+        <v>416</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>1221</v>
       </c>
       <c r="R26" t="n">
-        <v>43</v>
+        <v>1637</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,17 +2888,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1681381393</t>
+          <t>63265483</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681381393</t>
+          <t>https://m.place.naver.com/place/63265483</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2906,39 +2910,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>마이린 네일</t>
+          <t>디몽드네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>myrin_nail@naver.com</t>
+          <t>eautorride2@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1364-9606</t>
+          <t>0507-1392-5341</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
+          <t>인천광역시 미추홀구 수봉남로 1 (용현동)2층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kqfkxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2954,22 +2958,22 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R27" t="n">
-        <v>207</v>
+        <v>154</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,17 +2982,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1373786401</t>
+          <t>1670918594</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373786401</t>
+          <t>https://m.place.naver.com/place/1670918594</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3000,34 +3004,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>드림드로잉</t>
+          <t>끌림네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>powerkorea0505@naver.com</t>
+          <t>cclimnail@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1365-9785</t>
+          <t>032-872-9118</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 7층 7001호 드림드로잉</t>
+          <t>인천광역시 미추홀구 소성로 16 1층 110-2호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d_dnail0818</t>
+          <t>http://pf.kakao.com/_iBxexon</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3048,7 +3052,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3057,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="Q28" t="n">
-        <v>153</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>244</v>
+        <v>128</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,17 +3076,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1887397016</t>
+          <t>2064653044</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1887397016</t>
+          <t>https://m.place.naver.com/place/2064653044</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3094,29 +3098,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>반디인하우스 도화앨리웨이점</t>
+          <t>미다움네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bandinhouse_dohwa@naver.com</t>
+          <t>luna_pic@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1392-8241</t>
+          <t>0507-1442-0506</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
+          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
+          <t>http://instagram.com/me_daoom</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3151,13 +3155,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>341</v>
+        <v>22</v>
       </c>
       <c r="Q29" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="R29" t="n">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,17 +3170,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1485881474</t>
+          <t>1835371224</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485881474</t>
+          <t>https://m.place.naver.com/place/1835371224</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3188,29 +3192,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일로</t>
+          <t>올라운더네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kongdw@naver.com</t>
+          <t>allroundernail@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1378-2633</t>
+          <t>0507-1359-5371</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 4층 4013호</t>
+          <t>인천광역시 미추홀구 주안로 116 1층 103 A호 올라운더네일</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailo.nailstudio?igsh=bnB4MXhpNzF4MjU%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/allroundernail</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3225,7 +3229,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3236,7 +3240,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3245,13 +3249,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,17 +3264,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2019386343</t>
+          <t>1165613309</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019386343</t>
+          <t>https://m.place.naver.com/place/1165613309</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3282,29 +3286,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일도 희</t>
+          <t>네일 해봄</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kimmihee4@naver.com</t>
+          <t>eruriee@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1304-7934</t>
+          <t>0507-1303-4226</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 321-1 1층 101호 네일도, 희</t>
+          <t>인천광역시 미추홀구 토금중로30번길 9 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildo_hee</t>
+          <t>https://www.instagram.com/nail_haebom/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3339,13 +3343,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>296</v>
+        <v>878</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="R31" t="n">
-        <v>303</v>
+        <v>1058</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,17 +3358,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1208564106</t>
+          <t>38301920</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208564106</t>
+          <t>https://m.place.naver.com/place/38301920</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3376,34 +3380,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>걸스네일</t>
+          <t>제로네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ymj11969@naver.com</t>
+          <t>seeat_f@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1410-0304</t>
+          <t>0507-1359-4583</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 133 걸스네일</t>
+          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://link.thinkofyou.kr/girls_nail</t>
+          <t>https://www.instagram.com/zeronail_art</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3424,7 +3428,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3433,13 +3437,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>158</v>
+        <v>334</v>
       </c>
       <c r="Q32" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
-        <v>212</v>
+        <v>339</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3448,17 +3452,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>37257261</t>
+          <t>1613054835</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37257261</t>
+          <t>https://m.place.naver.com/place/1613054835</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3470,34 +3474,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>우니네일</t>
+          <t>예뻐지는네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sseonni51@naver.com</t>
+          <t>ylangylang053@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1390-7191</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 2층 2057호</t>
+          <t>인천광역시 미추홀구 미추홀대로578번길 9 1층(주안동)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ooninail_?igsh=YXc5aDlrOHZoeDh1&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/beautynail_0901</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="R33" t="n">
-        <v>110</v>
+        <v>242</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3542,17 +3542,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1013712359</t>
+          <t>1148534617</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013712359</t>
+          <t>https://m.place.naver.com/place/1148534617</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3564,29 +3564,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
+          <t>네일스하리</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dritn-nail_a_o@naver.com</t>
+          <t>yoollina_@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1325-1015</t>
+          <t>0507-1447-1684</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 장천로 57 1층</t>
+          <t>인천광역시 미추홀구 경원대로864번길 24 여성복지관 내 407호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://m.themosttimes.co.kr/39655</t>
+          <t>http://pf.kakao.com/_rdvxgn</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3612,7 +3612,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3621,13 +3621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="Q34" t="n">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="R34" t="n">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3636,17 +3636,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1166150967</t>
+          <t>2056712513</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166150967</t>
+          <t>https://m.place.naver.com/place/2056712513</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3658,34 +3658,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>하이스타네일</t>
+          <t>네일맑음</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mumu800@naver.com</t>
+          <t>s1514@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1377-6082</t>
+          <t>0507-1489-0530</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 201동 2030호 하이스타네일</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Qxexiqn</t>
+          <t>https://www.instagram.com/yuneungyeong4</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3706,7 +3706,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3715,13 +3715,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>14</v>
+        <v>234</v>
       </c>
       <c r="Q35" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="R35" t="n">
-        <v>57</v>
+        <v>303</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3730,17 +3730,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1591639462</t>
+          <t>1539397163</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591639462</t>
+          <t>https://m.place.naver.com/place/1539397163</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3752,29 +3752,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>뷰티컴트루</t>
+          <t>레푸스 인하대역점 내성발톱 무좀발톱 발각질 문제성발</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>wlsk4075@naver.com</t>
+          <t>hhs3556@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1372-5309</t>
+          <t>0507-1314-9364</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬서로18번길 27-20 1층</t>
+          <t>인천광역시 미추홀구 독배로 309 노블레스 빌딩 10층 1004호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_cometrue</t>
+          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3800,7 +3800,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3809,13 +3809,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>246</v>
+        <v>139</v>
       </c>
       <c r="Q36" t="n">
-        <v>13</v>
+        <v>436</v>
       </c>
       <c r="R36" t="n">
-        <v>259</v>
+        <v>575</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3824,17 +3824,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2001250057</t>
+          <t>1027018171</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001250057</t>
+          <t>https://m.place.naver.com/place/1027018171</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3846,29 +3846,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>수앙뷰티</t>
+          <t>채움네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>m_s_y_0219@naver.com</t>
+          <t>rhdwnsla5656@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1431-2153</t>
+          <t>0507-1326-3123</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 남주길 150 근린생활시설 2동 210호</t>
+          <t>인천광역시 미추홀구 소성로228번길 11 1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soins_beauty_n</t>
+          <t>https://www.instagram.com/chaeum_nail_</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q37" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3918,17 +3918,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2042315946</t>
+          <t>1824103581</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042315946</t>
+          <t>https://m.place.naver.com/place/1824103581</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>소이네일</t>
+          <t>고운손</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bin1549@naver.com</t>
+          <t>ghghrjftm@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3953,17 +3953,17 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 201동 지하1층 B1008호</t>
+          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_mxnTtn/chat</t>
+          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3984,7 +3984,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3993,13 +3993,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="Q38" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2033157749</t>
+          <t>1926481487</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033157749</t>
+          <t>https://m.place.naver.com/place/1926481487</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4030,29 +4030,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일구뜨</t>
+          <t>젤리네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kry198@naver.com</t>
+          <t>mi2013@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1376-0963</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로578번길 20 1층 네일구뜨</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdxgAXb/chat</t>
+          <t>https://open.kakao.com/o/s1SGa70g</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4087,13 +4083,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>95</v>
+        <v>391</v>
       </c>
       <c r="Q39" t="n">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="R39" t="n">
-        <v>126</v>
+        <v>498</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,17 +4098,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1674534211</t>
+          <t>1140244485</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674534211</t>
+          <t>https://m.place.naver.com/place/1140244485</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4124,29 +4120,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일스튜디오 매료</t>
+          <t>네일도 희</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>lnj7205@naver.com</t>
+          <t>kimmihee4@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1440-3488</t>
+          <t>0507-1304-7934</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인에비뉴 2층 2098호 (투썸플레이스 위)</t>
+          <t>인천광역시 미추홀구 소성로 321-1 1층 101호 네일도, 희</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailstudiomeryo/</t>
+          <t>https://www.instagram.com/naildo_hee</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4181,13 +4177,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R40" t="n">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,17 +4192,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1152584583</t>
+          <t>1208564106</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1152584583</t>
+          <t>https://m.place.naver.com/place/1208564106</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4218,29 +4214,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일링</t>
+          <t>모도리 네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>hans6758724@naver.com</t>
+          <t>dbsalwjd88@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1346-3521</t>
+          <t>0507-1330-1268</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 학익로80번길 11 시티오씨엘3단지 메가박스 상가 2층 B-224호</t>
+          <t>인천광역시 미추홀구 독배로382번길 12 1층 모도리네일</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nailing</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4250,7 +4246,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4271,17 +4267,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>229</v>
+        <v>320</v>
       </c>
       <c r="Q41" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,17 +4286,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1351774557</t>
+          <t>1752538431</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1351774557</t>
+          <t>https://m.place.naver.com/place/1752538431</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4312,34 +4308,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>용쥬르샵 인천본점</t>
+          <t>네일 품은 손</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>iiidydwn@naver.com</t>
+          <t>sssh200118@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>032-423-2963</t>
+          <t>0507-1360-1453</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
+          <t>인천광역시 미추홀구 한나루로357번길 5-58 1층 네일품은손</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iiidydwn</t>
+          <t>http://pf.kakao.com/_eQCrb</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4349,7 +4345,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4360,7 +4356,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4369,13 +4365,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>662</v>
+        <v>98</v>
       </c>
       <c r="Q42" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="R42" t="n">
-        <v>717</v>
+        <v>122</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,17 +4380,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1845960167</t>
+          <t>1680001412</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845960167</t>
+          <t>https://m.place.naver.com/place/1680001412</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4406,25 +4402,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>란또 네일&amp;뷰티</t>
+          <t>라보떼 뷰티</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>wealth_8674@naver.com</t>
+          <t>dlatmfrl5824@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1377-9030</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 407 예지빌딩 3층</t>
+          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/randdo24.nail_beauty</t>
+          <t>https://www.instagram.com/labeaute7027__</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4459,13 +4459,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="Q43" t="n">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="R43" t="n">
-        <v>313</v>
+        <v>516</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4474,17 +4474,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1119025988</t>
+          <t>1828605681</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1119025988</t>
+          <t>https://m.place.naver.com/place/1828605681</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4496,29 +4496,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>도화네일</t>
+          <t>네일스튜디오 매료</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>gsqnls2u@naver.com</t>
+          <t>lnj7205@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1373-9131</t>
+          <t>0507-1440-3488</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
+          <t>인천광역시 미추홀구 경인로 372 아인에비뉴 2층 2098호 (투썸플레이스 위)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dohwa_nail_</t>
+          <t>https://www.instagram.com/nailstudiomeryo/</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4553,13 +4553,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>693</v>
+        <v>249</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="R44" t="n">
-        <v>695</v>
+        <v>263</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4568,17 +4568,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1155887763</t>
+          <t>1152584583</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155887763</t>
+          <t>https://m.place.naver.com/place/1152584583</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4590,29 +4590,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일언니</t>
+          <t>부티스튜디오</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>pjh48886@naver.com</t>
+          <t>avecbeaute_@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1360-4886</t>
+          <t>0507-1371-2954</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 97 102 호 네일언니</t>
+          <t>인천광역시 미추홀구 인하로91번길 71 1층일부호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_unni_</t>
+          <t>https://www.instagram.com/buti_studio?igsh=MWJsdzcyNDNobGc0aw==</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>540</v>
+        <v>2</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4662,17 +4662,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>36184234</t>
+          <t>2061859427</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36184234</t>
+          <t>https://m.place.naver.com/place/2061859427</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4684,30 +4684,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>효즈네일&amp;속눈썹&amp;왁싱</t>
+          <t>네일,포슬</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kwoun0303@naver.com</t>
+          <t>r__r_b@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1386-5035</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 67</t>
+          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://instagram.com/hyoz_official</t>
+          <t>https://www.instagram.com/nail_poseul_</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4717,7 +4721,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4737,13 +4741,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1148</v>
+        <v>408</v>
       </c>
       <c r="Q46" t="n">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="R46" t="n">
-        <v>1254</v>
+        <v>449</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4752,17 +4756,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1543447735</t>
+          <t>1050625355</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543447735</t>
+          <t>https://m.place.naver.com/place/1050625355</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4774,34 +4778,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>끌림네일</t>
+          <t>네일플래닛</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>cclimnail@naver.com</t>
+          <t>znzltkfkd123@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>032-872-9118</t>
+          <t>0507-1470-6637</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 16 1층 110-2호</t>
+          <t>인천광역시 미추홀구 경인로 372 포레나 201동(아인여성병원건물) 지상2층 2017호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_iBxexon</t>
+          <t>https://blog.naver.com/znzltkfkd123</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4811,7 +4815,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4822,22 +4826,22 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>122</v>
+        <v>346</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="R47" t="n">
-        <v>125</v>
+        <v>443</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4846,17 +4850,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2064653044</t>
+          <t>1077662255</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064653044</t>
+          <t>https://m.place.naver.com/place/1077662255</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4868,29 +4872,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>메이에르 네일</t>
+          <t>도화네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dmsal6910@naver.com</t>
+          <t>gsqnls2u@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1472-1341</t>
+          <t>0507-1373-9131</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로330번길 23 1층 메이에르네일</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/meyere_nail</t>
+          <t>https://www.instagram.com/dohwa_nail_</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4916,7 +4920,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4925,13 +4929,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>77</v>
+        <v>693</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
-        <v>90</v>
+        <v>695</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4940,17 +4944,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2090344240</t>
+          <t>1155887763</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090344240</t>
+          <t>https://m.place.naver.com/place/1155887763</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4962,29 +4966,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>아무아네일</t>
+          <t>란또 네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>zld9142@naver.com</t>
+          <t>wealth_8674@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1365-1547</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안동로 39 1층</t>
+          <t>인천광역시 미추홀구 매소홀로 407 예지빌딩 3층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://youtube.com/@amouanail_diary?si=mNU7eI9gjC1L4C3W</t>
+          <t>https://www.instagram.com/randdo24.nail_beauty</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5010,7 +5010,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5019,13 +5019,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Q49" t="n">
-        <v>490</v>
+        <v>97</v>
       </c>
       <c r="R49" t="n">
-        <v>701</v>
+        <v>313</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5034,17 +5034,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2098522217</t>
+          <t>1119025988</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098522217</t>
+          <t>https://m.place.naver.com/place/1119025988</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5056,29 +5056,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일혜 도화점</t>
+          <t>착한언니피부네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nailhye_@naver.com</t>
+          <t>u4melive@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1487-9095</t>
+          <t>0507-1368-0680</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
+          <t>인천광역시 미추홀구 낙섬중로 73 1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.hye/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>323</v>
+        <v>383</v>
       </c>
       <c r="Q50" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5128,17 +5128,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1396481559</t>
+          <t>2096439755</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396481559</t>
+          <t>https://m.place.naver.com/place/2096439755</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5150,34 +5150,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>디두네일 D.do nail studio</t>
+          <t>모드니에네일 인천용현점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ddonail12@naver.com</t>
+          <t>wlsk4075@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1423-8033</t>
+          <t>032-888-2430</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
+          <t>인천광역시 미추홀구 낙섬중로 61 1층 101호,102호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Ukxhxmn</t>
+          <t>http://instagram.com/modnie_nail</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5198,7 +5198,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>66</v>
+        <v>773</v>
       </c>
       <c r="Q51" t="n">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="R51" t="n">
-        <v>80</v>
+        <v>876</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5222,17 +5222,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2003325308</t>
+          <t>1031233548</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003325308</t>
+          <t>https://m.place.naver.com/place/1031233548</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5244,34 +5244,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>예뻐진</t>
+          <t>에스네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>tlsguswls81@naver.com</t>
+          <t>snail4324@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1334-0060</t>
+          <t>0507-1406-3132</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 301-2 2층</t>
+          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gFGxbb</t>
+          <t>https://www.instagram.com/snail0070</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5292,7 +5292,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="Q52" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="R52" t="n">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5316,17 +5316,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1366454286</t>
+          <t>38286683</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1366454286</t>
+          <t>https://m.place.naver.com/place/38286683</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5338,29 +5338,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>모드니에네일 인천용현점</t>
+          <t>네일언니</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>wlsk4075@naver.com</t>
+          <t>pjh48886@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>032-888-2430</t>
+          <t>0507-1360-4886</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 61 1층 101호,102호</t>
+          <t>인천광역시 미추홀구 인하로 97 102 호 네일언니</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://instagram.com/modnie_nail</t>
+          <t>https://www.instagram.com/nail_unni_</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5395,13 +5395,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>773</v>
+        <v>499</v>
       </c>
       <c r="Q53" t="n">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="R53" t="n">
-        <v>874</v>
+        <v>540</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5410,17 +5410,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1031233548</t>
+          <t>36184234</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031233548</t>
+          <t>https://m.place.naver.com/place/36184234</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5432,25 +5432,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>고운손</t>
+          <t>네일진</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ghghrjftm@naver.com</t>
+          <t>kng026@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1343-3705</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
+          <t>인천광역시 미추홀구 낙섬중로32번길 22 1층 104호 네일진</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
+          <t>https://www.instagram.com/nail___jin_?igsh=ZHIxemZmNXcxNWtq&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5485,13 +5489,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="Q54" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R54" t="n">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5500,17 +5504,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1926481487</t>
+          <t>1343927659</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926481487</t>
+          <t>https://m.place.naver.com/place/1343927659</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5522,29 +5526,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일스프링</t>
+          <t>네일혜 도화점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>wldus318@naver.com</t>
+          <t>nailhye_@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1465-2797</t>
+          <t>0507-1487-9095</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
+          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___spring</t>
+          <t>https://www.instagram.com/_nail.hye/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5579,13 +5583,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>123</v>
+        <v>325</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R55" t="n">
-        <v>133</v>
+        <v>342</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5594,17 +5598,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2098983836</t>
+          <t>1396481559</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098983836</t>
+          <t>https://m.place.naver.com/place/1396481559</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5616,29 +5620,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일맑음</t>
+          <t>효즈네일&amp;속눈썹&amp;왁싱</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>s1514@naver.com</t>
+          <t>kwoun0303@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1489-0530</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
+          <t>인천광역시 미추홀구 인하로 67</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuneungyeong4</t>
+          <t>http://instagram.com/hyoz_official</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5673,13 +5673,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>234</v>
+        <v>1149</v>
       </c>
       <c r="Q56" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="R56" t="n">
-        <v>303</v>
+        <v>1255</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5688,17 +5688,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1539397163</t>
+          <t>1543447735</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539397163</t>
+          <t>https://m.place.naver.com/place/1543447735</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5710,29 +5710,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일파인</t>
+          <t>루미랑네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>milkysuk@naver.com</t>
+          <t>jine_blog@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1490-7041</t>
+          <t>0507-1371-1706</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로224번길 14 1층 네일파인</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_pine</t>
+          <t>https://www.instagram.com/rumirang_nail</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5758,7 +5758,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>128</v>
+        <v>259</v>
       </c>
       <c r="Q57" t="n">
-        <v>212</v>
+        <v>54</v>
       </c>
       <c r="R57" t="n">
-        <v>340</v>
+        <v>313</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5782,17 +5782,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1679016661</t>
+          <t>1156304078</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679016661</t>
+          <t>https://m.place.naver.com/place/1156304078</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5804,29 +5804,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>부티스튜디오</t>
+          <t>에이풋케어 내성발톱 발톱무좀 발각질 문제성발</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>avecbeaute_@naver.com</t>
+          <t>illbwidu@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1371-2954</t>
+          <t>0507-1378-4114</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로91번길 71 1층일부호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 시티필드 6층 6013호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buti_studio?igsh=MWJsdzcyNDNobGc0aw==</t>
+          <t>https://blog.naver.com/illbwidu</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>485</v>
       </c>
       <c r="R58" t="n">
-        <v>2</v>
+        <v>588</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2061859427</t>
+          <t>1319855180</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061859427</t>
+          <t>https://m.place.naver.com/place/1319855180</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5898,29 +5898,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>착한언니피부네일</t>
+          <t>네일팔레트</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>u4melive@naver.com</t>
+          <t>nail4season@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1368-0680</t>
+          <t>0507-1334-0294</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 73 1층</t>
+          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/palette_nailll</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>383</v>
+        <v>305</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R59" t="n">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5970,17 +5970,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2096439755</t>
+          <t>1167629339</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096439755</t>
+          <t>https://m.place.naver.com/place/1167629339</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5992,29 +5992,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>문제성 손,발 오감네일 도화점</t>
+          <t>네일인더문</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ogam_foot_nail@naver.com</t>
+          <t>beauty_n_nail@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1388-5117</t>
+          <t>0507-1436-0467</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
+          <t>인천광역시 미추홀구 소성로 237 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ogam_foot_nail</t>
+          <t>https://www.instagram.com/nail_inthemoon</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6049,13 +6049,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>663</v>
+        <v>110</v>
       </c>
       <c r="Q60" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="R60" t="n">
-        <v>732</v>
+        <v>162</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1716147754</t>
+          <t>1204881858</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716147754</t>
+          <t>https://m.place.naver.com/place/1204881858</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6086,29 +6086,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일스하리</t>
+          <t>로이네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>yoollina_@naver.com</t>
+          <t>wlgus1647@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1447-1684</t>
+          <t>0507-1350-5396</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로864번길 24 여성복지관 내 407호</t>
+          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rdvxgn</t>
+          <t>http://pf.kakao.com/_vxkKMs/chat</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6143,13 +6143,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="Q61" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="R61" t="n">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6158,17 +6158,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2056712513</t>
+          <t>1765283529</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056712513</t>
+          <t>https://m.place.naver.com/place/1765283529</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6180,29 +6180,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일진</t>
+          <t>메이에르 네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kng026@naver.com</t>
+          <t>dmsal6910@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1343-3705</t>
+          <t>0507-1472-1341</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로32번길 22 1층 104호 네일진</t>
+          <t>인천광역시 미추홀구 인주대로330번길 23 1층 메이에르네일</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___jin_?igsh=ZHIxemZmNXcxNWtq&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/meyere_nail</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6228,7 +6228,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6237,13 +6237,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R62" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6252,17 +6252,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1343927659</t>
+          <t>2090344240</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1343927659</t>
+          <t>https://m.place.naver.com/place/2090344240</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6274,29 +6274,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일,포슬</t>
+          <t>뾰로롱네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>r__r_b@naver.com</t>
+          <t>redberry5@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1386-5035</t>
+          <t>0507-1302-6657</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
+          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_poseul_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6327,17 +6327,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="Q63" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>448</v>
+        <v>83</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6346,17 +6346,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1050625355</t>
+          <t>2058778627</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050625355</t>
+          <t>https://m.place.naver.com/place/2058778627</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6368,39 +6368,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>모도리 네일</t>
+          <t>예뻐진</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>dbsalwjd88@naver.com</t>
+          <t>tlsguswls81@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1330-1268</t>
+          <t>0507-1334-0060</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로382번길 12 1층 모도리네일</t>
+          <t>인천광역시 미추홀구 인하로 301-2 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_gFGxbb</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6416,22 +6416,22 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>319</v>
+        <v>96</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="R64" t="n">
-        <v>321</v>
+        <v>187</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6440,17 +6440,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1752538431</t>
+          <t>1366454286</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1752538431</t>
+          <t>https://m.place.naver.com/place/1366454286</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>레푸스 인하대역점 내성발톱 무좀발톱 발각질 문제성발</t>
+          <t>드림드로잉</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>hhs3556@naver.com</t>
+          <t>powerkorea0505@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1314-9364</t>
+          <t>0507-1365-9785</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 309 노블레스 빌딩 10층 1004호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 7층 7001호 드림드로잉</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
+          <t>https://www.instagram.com/d_dnail0818</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6519,13 +6519,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="Q65" t="n">
-        <v>436</v>
+        <v>153</v>
       </c>
       <c r="R65" t="n">
-        <v>574</v>
+        <v>245</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6534,17 +6534,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1027018171</t>
+          <t>1887397016</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027018171</t>
+          <t>https://m.place.naver.com/place/1887397016</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6556,29 +6556,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>아무르네일</t>
+          <t>네일미니</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>07alsrud@naver.com</t>
+          <t>snow1blossom@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1360-5941</t>
+          <t>0507-1379-4411</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2103호</t>
+          <t>인천광역시 미추홀구 한나루로489번길 107 1층 102호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_mi_ni</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6609,17 +6609,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>102</v>
+        <v>414</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="R66" t="n">
-        <v>110</v>
+        <v>468</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6628,17 +6628,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1701492501</t>
+          <t>1633509740</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701492501</t>
+          <t>https://m.place.naver.com/place/1633509740</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6650,29 +6650,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>하드킴네일</t>
+          <t>수앙뷰티</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>hardkim_nail@naver.com</t>
+          <t>m_s_y_0219@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1386-0240</t>
+          <t>0507-1431-2153</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 학익로80번길 11 312동 2층 B-221호</t>
+          <t>인천광역시 미추홀구 남주길 150 근린생활시설 2동 210호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hardkim_nail</t>
+          <t>https://www.instagram.com/soins_beauty_n</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6707,13 +6707,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>73</v>
+        <v>223</v>
       </c>
       <c r="Q67" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="R67" t="n">
-        <v>115</v>
+        <v>242</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6722,17 +6722,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2095090349</t>
+          <t>2042315946</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095090349</t>
+          <t>https://m.place.naver.com/place/2042315946</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6744,25 +6744,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>예뻐지는네일</t>
+          <t>네일에보</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jisoo851208@naver.com</t>
+          <t>daniya1210@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1311-6332</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로578번길 9 1층(주안동)</t>
+          <t>인천광역시 미추홀구 경인로 372 201동 B2층 2055호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautynail_0901</t>
+          <t>https://www.instagram.com/_nailevo_</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6788,7 +6792,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6797,13 +6801,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>113</v>
+        <v>343</v>
       </c>
       <c r="Q68" t="n">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="R68" t="n">
-        <v>242</v>
+        <v>420</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6812,17 +6816,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1148534617</t>
+          <t>1252060771</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1148534617</t>
+          <t>https://m.place.naver.com/place/1252060771</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6834,29 +6838,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일데이원</t>
+          <t>디어마인샵</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>lisianthus0330@naver.com</t>
+          <t>unthsu@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1337-2867</t>
+          <t>0507-1403-2780</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로834번길 27-12 NS빌딩 2층 203호</t>
+          <t>인천광역시 미추홀구 경인남길30번길 94 1층 디어마인샵</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_dayone</t>
+          <t>http://instagram.com/dear_mine91</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6891,13 +6895,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>237</v>
+        <v>1303</v>
       </c>
       <c r="Q69" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="R69" t="n">
-        <v>240</v>
+        <v>1356</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6906,17 +6910,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1689139269</t>
+          <t>1144594831</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689139269</t>
+          <t>https://m.place.naver.com/place/1144594831</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6928,29 +6932,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일,꽃이피다</t>
+          <t>문제성 손,발 오감네일 도화점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>nail910401@naver.com</t>
+          <t>ogam_foot_nail@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1311-6628</t>
+          <t>0507-1388-5117</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 시티필드 7층 7012호 네일꽃이피다</t>
+          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.bloom__</t>
+          <t>https://blog.naver.com/ogam_foot_nail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6965,7 +6969,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6985,13 +6989,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>172</v>
+        <v>664</v>
       </c>
       <c r="Q70" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="R70" t="n">
-        <v>207</v>
+        <v>733</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7000,17 +7004,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1271233277</t>
+          <t>1716147754</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1271233277</t>
+          <t>https://m.place.naver.com/place/1716147754</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7022,25 +7026,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>젤리네일</t>
+          <t>네일언니</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>mi2013@naver.com</t>
+          <t>555__555@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1315-4886</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
+          <t>인천광역시 미추홀구 독배로 305 102호 네일언니2</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1SGa70g</t>
+          <t>https://www.instagram.com/nailunni_</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7066,7 +7074,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7075,13 +7083,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>391</v>
+        <v>832</v>
       </c>
       <c r="Q71" t="n">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="R71" t="n">
-        <v>498</v>
+        <v>888</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7090,17 +7098,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1140244485</t>
+          <t>1277528071</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140244485</t>
+          <t>https://m.place.naver.com/place/1277528071</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7112,34 +7120,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일언니</t>
+          <t>네일핏</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>555__555@naver.com</t>
+          <t>nailfitsl@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1315-4886</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 305 102호 네일언니2</t>
+          <t>인천광역시 미추홀구 독배로 311 비젼프라자 2층 206호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailunni_</t>
+          <t>http://pf.kakao.com/_FxiNCG</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7160,7 +7164,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7169,13 +7173,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>831</v>
+        <v>934</v>
       </c>
       <c r="Q72" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="R72" t="n">
-        <v>887</v>
+        <v>946</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7184,17 +7188,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1277528071</t>
+          <t>718951949</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1277528071</t>
+          <t>https://m.place.naver.com/place/718951949</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7206,29 +7210,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일팔레트</t>
+          <t>블루진네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>nail4season@naver.com</t>
+          <t>whole4ni@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1334-0294</t>
+          <t>0507-1407-5343</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
+          <t>인천광역시 미추홀구 경원대로897번길 40 상가 1층 101호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palette_nailll</t>
+          <t>https://www.instagram.com/bluejin_nail</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7263,13 +7267,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>304</v>
+        <v>138</v>
       </c>
       <c r="Q73" t="n">
-        <v>6</v>
+        <v>173</v>
       </c>
       <c r="R73" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7278,17 +7282,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1167629339</t>
+          <t>1920868303</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167629339</t>
+          <t>https://m.place.naver.com/place/1920868303</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7300,34 +7304,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>라보떼 뷰티</t>
+          <t>쿄우네일 석바위점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>dlatmfrl5824@naver.com</t>
+          <t>dlthwjd7530@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1377-9030</t>
+          <t>0507-1394-6274</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
+          <t>인천광역시 미추홀구 경원대로 858 3층 일부호 쿄우네일</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/labeaute7027__</t>
+          <t>http://pf.kakao.com/_xdlxjBn</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7348,7 +7352,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7357,13 +7361,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>267</v>
+        <v>181</v>
       </c>
       <c r="Q74" t="n">
-        <v>249</v>
+        <v>38</v>
       </c>
       <c r="R74" t="n">
-        <v>516</v>
+        <v>219</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7372,17 +7376,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1828605681</t>
+          <t>2023963502</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828605681</t>
+          <t>https://m.place.naver.com/place/2023963502</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7394,29 +7398,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일또방</t>
+          <t>네일파인</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>milkysuk@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1378-8088</t>
+          <t>0507-1490-7041</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 665 1층</t>
+          <t>인천광역시 미추홀구 인주대로224번길 14 1층 네일파인</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ddobang/</t>
+          <t>https://www.instagram.com/nail_pine</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7442,7 +7446,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7451,13 +7455,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>634</v>
+        <v>128</v>
       </c>
       <c r="Q75" t="n">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="R75" t="n">
-        <v>656</v>
+        <v>340</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7466,17 +7470,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1177770049</t>
+          <t>1679016661</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1177770049</t>
+          <t>https://m.place.naver.com/place/1679016661</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7488,34 +7492,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>블루진네일</t>
+          <t>마이린 네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>whole4ni@naver.com</t>
+          <t>myrin_nail@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1407-5343</t>
+          <t>0507-1364-9606</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로897번길 40 상가 1층 101호</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bluejin_nail</t>
+          <t>http://pf.kakao.com/_kqfkxj</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7536,7 +7540,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7545,13 +7549,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>138</v>
+        <v>203</v>
       </c>
       <c r="Q76" t="n">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>311</v>
+        <v>207</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7560,17 +7564,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1920868303</t>
+          <t>1373786401</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920868303</t>
+          <t>https://m.place.naver.com/place/1373786401</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/남구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/남구_네일샵.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>뷰티컴트루</t>
+          <t>마이린 네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wlsk4075@naver.com</t>
+          <t>myrin_nail@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1372-5309</t>
+          <t>0507-1364-9606</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬서로18번길 27-20 1층</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_cometrue</t>
+          <t>http://pf.kakao.com/_kqfkxj</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2001250057</t>
+          <t>1373786401</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001250057</t>
+          <t>https://m.place.naver.com/place/1373786401</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일또방</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>hankyuldata@naver.com</t>
-        </is>
-      </c>
+          <t>제로네일</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1378-8088</t>
+          <t>0507-1359-4583</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 665 1층</t>
+          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ddobang/</t>
+          <t>https://www.instagram.com/zeronail_art</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>634</v>
+        <v>335</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>656</v>
+        <v>340</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1177770049</t>
+          <t>1613054835</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1177770049</t>
+          <t>https://m.place.naver.com/place/1613054835</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,34 +748,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>하이스타네일</t>
+          <t>봉구네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mumu800@naver.com</t>
+          <t>94rnrdudal@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1377-6082</t>
+          <t>0507-1320-0380</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 201동 2030호 하이스타네일</t>
+          <t>인천광역시 미추홀구 주안로 86 지하상가 148/173호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Qxexiqn</t>
+          <t>https://www.instagram.com/bonggu_nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,7 +796,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="Q4" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1591639462</t>
+          <t>1965492062</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591639462</t>
+          <t>https://m.place.naver.com/place/1965492062</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +842,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>반디인하우스 도화앨리웨이점</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>bandinhouse_dohwa@naver.com</t>
-        </is>
-      </c>
+          <t>부티스튜디오</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1392-8241</t>
+          <t>0507-1371-2954</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
+          <t>인천광역시 미추홀구 인하로91번길 71 1층일부호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
+          <t>https://www.instagram.com/buti_studio?igsh=MWJsdzcyNDNobGc0aw==</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>420</v>
+        <v>2</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1485881474</t>
+          <t>2061859427</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485881474</t>
+          <t>https://m.place.naver.com/place/2061859427</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +932,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일,꽃이피다</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>nail910401@naver.com</t>
-        </is>
-      </c>
+          <t>고운손</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1311-6628</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 시티필드 7층 7012호 네일꽃이피다</t>
+          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.bloom__</t>
+          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +981,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +996,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1271233277</t>
+          <t>1926481487</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1271233277</t>
+          <t>https://m.place.naver.com/place/1926481487</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1018,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>우니네일</t>
+          <t>오래도록예쁘게 인하대역본점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sseonni51@naver.com</t>
+          <t>oye_beauty@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1390-7191</t>
+          <t>0507-1348-5330</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 2층 2057호</t>
+          <t>인천광역시 미추홀구 용정공원로83번길 43 e편한세상시티 2층 217호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ooninail_?igsh=YXc5aDlrOHZoeDh1&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/o.ye_beauty/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1075,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R7" t="n">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1090,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1013712359</t>
+          <t>1200197583</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013712359</t>
+          <t>https://m.place.naver.com/place/1200197583</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1112,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일오숑</t>
+          <t>예뻐지는네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>ylangylang053@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1141,12 +1125,12 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
+          <t>인천광역시 미추홀구 미추홀대로578번길 9 1층(주안동)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_osyong/</t>
+          <t>https://www.instagram.com/beautynail_0901</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1165,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>260</v>
+        <v>113</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="R8" t="n">
-        <v>279</v>
+        <v>242</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1180,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1518702391</t>
+          <t>1148534617</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1518702391</t>
+          <t>https://m.place.naver.com/place/1148534617</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1202,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일스프링</t>
+          <t>라 폴리쉬드</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wldus318@naver.com</t>
+          <t>wndnjs579@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1465-2797</t>
+          <t>0507-1354-5656</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
+          <t>인천광역시 미추홀구 승학길 28 105호 1층상가 라 폴리쉬드</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___spring</t>
+          <t>https://www.instagram.com/la_polished?igsh=djk3a2lwb3ppdDRk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,13 +1259,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1274,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2098983836</t>
+          <t>2080412833</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098983836</t>
+          <t>https://m.place.naver.com/place/2080412833</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1296,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일로</t>
+          <t>디어마인샵</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>loosetime@naver.com</t>
+          <t>unthsu@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1378-2633</t>
+          <t>0507-1403-2780</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 4층 4013호</t>
+          <t>인천광역시 미추홀구 경인남길30번길 94 1층 디어마인샵</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailo.nailstudio?igsh=bnB4MXhpNzF4MjU%3D&amp;utm_source=qr</t>
+          <t>http://instagram.com/dear_mine91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1360,7 +1344,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1353,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>1299</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="R10" t="n">
-        <v>86</v>
+        <v>1352</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1368,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2019386343</t>
+          <t>1144594831</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019386343</t>
+          <t>https://m.place.naver.com/place/1144594831</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1390,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>미라클뷰티&amp;네일</t>
+          <t>에스네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ssoyoung0318@naver.com</t>
+          <t>snail4324@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1330-3178</t>
+          <t>0507-1406-3132</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 12층1호</t>
+          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miraclebeauty_nail?igsh=MW5nN3NoOHd0OG51dg==</t>
+          <t>https://www.instagram.com/snail0070</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,13 +1447,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="R11" t="n">
-        <v>274</v>
+        <v>146</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1462,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2040709432</t>
+          <t>38286683</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040709432</t>
+          <t>https://m.place.naver.com/place/38286683</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1500,34 +1484,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>라 폴리쉬드</t>
+          <t>네일스하리</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>khw23540@naver.com</t>
+          <t>yoollina_@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1354-5656</t>
+          <t>0507-1447-1684</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 승학길 28 105호 1층상가 라 폴리쉬드</t>
+          <t>인천광역시 미추홀구 경원대로864번길 24 여성복지관 내 407호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/la_polished?igsh=djk3a2lwb3ppdDRk</t>
+          <t>http://pf.kakao.com/_rdvxgn</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1548,7 +1532,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1557,13 +1541,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1556,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2080412833</t>
+          <t>2056712513</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080412833</t>
+          <t>https://m.place.naver.com/place/2056712513</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1578,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일링</t>
+          <t>란또 네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gulgomi@naver.com</t>
+          <t>wealth_8674@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1346-3521</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 학익로80번길 11 시티오씨엘3단지 메가박스 상가 2층 B-224호</t>
+          <t>인천광역시 미추홀구 매소홀로 407 예지빌딩 3층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nailing</t>
+          <t>https://www.instagram.com/randdo24.nail_beauty</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1651,13 +1631,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="Q13" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="R13" t="n">
-        <v>264</v>
+        <v>313</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,17 +1646,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1351774557</t>
+          <t>1119025988</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1351774557</t>
+          <t>https://m.place.naver.com/place/1119025988</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1688,29 +1668,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>아무르네일</t>
+          <t>네일언니</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>07alsrud@naver.com</t>
+          <t>555__555@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1360-5941</t>
+          <t>0507-1315-4886</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2103호</t>
+          <t>인천광역시 미추홀구 독배로 305 102호 네일언니2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailunni_</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1720,7 +1700,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1741,17 +1721,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>102</v>
+        <v>837</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="R14" t="n">
-        <v>110</v>
+        <v>893</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1740,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1701492501</t>
+          <t>1277528071</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701492501</t>
+          <t>https://m.place.naver.com/place/1277528071</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1782,29 +1762,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>제리네일</t>
+          <t>메이에르 네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>wjdsla91777@naver.com</t>
+          <t>dmsal6910@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1479-5891</t>
+          <t>0507-1472-1341</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 1층 1055호</t>
+          <t>인천광역시 미추홀구 인주대로330번길 23 1층 메이에르네일</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j7n._s?igsh=N2UybHpmZjRnbWJz&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/meyere_nail</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1830,7 +1810,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1839,13 +1819,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>278</v>
+        <v>93</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1834,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1744004614</t>
+          <t>2090344240</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1744004614</t>
+          <t>https://m.place.naver.com/place/2090344240</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1876,34 +1856,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>걸스네일</t>
+          <t>네일인더문</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ymj11969@naver.com</t>
+          <t>beauty_n_nail@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1410-0304</t>
+          <t>0507-1436-0467</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 133 걸스네일</t>
+          <t>인천광역시 미추홀구 소성로 237 1층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://link.thinkofyou.kr/girls_nail</t>
+          <t>https://www.instagram.com/nail_inthemoon</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1924,7 +1904,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1933,13 +1913,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="Q16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R16" t="n">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,17 +1928,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>37257261</t>
+          <t>1204881858</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37257261</t>
+          <t>https://m.place.naver.com/place/1204881858</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1970,29 +1950,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>용쥬르샵 인천본점</t>
+          <t>네일,포슬</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iiidydwn@naver.com</t>
+          <t>yonimiao@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>032-423-2963</t>
+          <t>0507-1386-5035</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
+          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iiidydwn</t>
+          <t>https://www.instagram.com/nail_poseul_</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2007,7 +1987,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2027,13 +2007,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>662</v>
+        <v>408</v>
       </c>
       <c r="Q17" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="R17" t="n">
-        <v>717</v>
+        <v>449</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2022,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1845960167</t>
+          <t>1050625355</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845960167</t>
+          <t>https://m.place.naver.com/place/1050625355</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2064,39 +2044,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>아무아네일</t>
+          <t>뾰로롱네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>zld9142@naver.com</t>
+          <t>redberry5@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1365-1547</t>
+          <t>0507-1302-6657</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안동로 39 1층</t>
+          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://youtube.com/@amouanail_diary?si=mNU7eI9gjC1L4C3W</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2112,22 +2092,22 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="Q18" t="n">
-        <v>533</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>743</v>
+        <v>83</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,17 +2116,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2098522217</t>
+          <t>2058778627</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098522217</t>
+          <t>https://m.place.naver.com/place/2058778627</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2158,29 +2138,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>하드킴네일</t>
+          <t>네일피컨트</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hardkim_nail@naver.com</t>
+          <t>edenia_@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1386-0240</t>
+          <t>0507-1368-8328</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 학익로80번길 11 312동 2층 B-221호</t>
+          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2099호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hardkim_nail</t>
+          <t>https://www.instagram.com/nailpiquant</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2195,7 +2175,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2215,13 +2195,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,17 +2210,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2095090349</t>
+          <t>1998009537</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095090349</t>
+          <t>https://m.place.naver.com/place/1998009537</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2252,29 +2232,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일데이원</t>
+          <t>네일,리슬</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>aar422@naver.com</t>
+          <t>lys961206@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1337-2867</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로834번길 27-12 NS빌딩 2층 203호</t>
+          <t>인천광역시 미추홀구 용정공원로83번길 43 2층 207호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_dayone</t>
+          <t>https://www.instagram.com/nail_lee_seul?igsh=ZXQyYzNpbng1aW1y&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2309,13 +2285,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>237</v>
+        <v>35</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>240</v>
+        <v>39</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,17 +2300,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1689139269</t>
+          <t>2009491111</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689139269</t>
+          <t>https://m.place.naver.com/place/2009491111</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2346,34 +2322,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
+          <t>수앙뷰티</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dritn-nail_a_o@naver.com</t>
+          <t>m_s_y_0219@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1325-1015</t>
+          <t>0507-1431-2153</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 장천로 57 1층</t>
+          <t>인천광역시 미추홀구 남주길 150 근린생활시설 2동 210호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://m.themosttimes.co.kr/39655</t>
+          <t>https://www.instagram.com/soins_beauty_n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2403,13 +2379,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>87</v>
+        <v>224</v>
       </c>
       <c r="Q21" t="n">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="R21" t="n">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,17 +2394,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1166150967</t>
+          <t>2042315946</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166150967</t>
+          <t>https://m.place.naver.com/place/2042315946</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2440,29 +2416,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아르떼네일</t>
+          <t>네일,꽃이피다</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>arte__nail_@naver.com</t>
+          <t>nail910401@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1323-0926</t>
+          <t>0507-1311-6628</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 시티필드 7층 7012호 네일꽃이피다</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/arte__nail_</t>
+          <t>https://www.instagram.com/nail.bloom__</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2477,7 +2453,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2488,7 +2464,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2497,13 +2473,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>391</v>
+        <v>172</v>
       </c>
       <c r="Q22" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="R22" t="n">
-        <v>450</v>
+        <v>207</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,17 +2488,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1775601804</t>
+          <t>1271233277</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1775601804</t>
+          <t>https://m.place.naver.com/place/1271233277</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2534,29 +2510,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일그리움 주안점</t>
+          <t>아무르네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>cherryjoa_v@naver.com</t>
+          <t>07alsrud@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1443-5044</t>
+          <t>0507-1360-5941</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로614번길 42 101호 네일그리움</t>
+          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2103호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_geurium</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2566,7 +2542,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2587,17 +2563,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>255</v>
+        <v>102</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>276</v>
+        <v>110</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2606,17 +2582,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1994727673</t>
+          <t>1701492501</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994727673</t>
+          <t>https://m.place.naver.com/place/1701492501</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2628,34 +2604,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>디두네일 D.do nail studio</t>
+          <t>드림드로잉</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ddonail12@naver.com</t>
+          <t>powerkorea0505@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1423-8033</t>
+          <t>0507-1365-9785</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
+          <t>인천광역시 미추홀구 매소홀로 262 7층 7001호 드림드로잉</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Ukxhxmn</t>
+          <t>https://www.instagram.com/d_dnail0818</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2676,7 +2652,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2685,13 +2661,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="R24" t="n">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2700,17 +2676,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2003325308</t>
+          <t>1887397016</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003325308</t>
+          <t>https://m.place.naver.com/place/1887397016</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2722,34 +2698,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>네일구뜨</t>
+          <t>루미랑네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kry198@naver.com</t>
+          <t>jine_blog@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1376-0963</t>
+          <t>0507-1371-1706</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로578번길 20 1층 네일구뜨</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdxgAXb/chat</t>
+          <t>https://www.instagram.com/rumirang_nail</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2770,7 +2746,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2779,13 +2755,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>95</v>
+        <v>261</v>
       </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="R25" t="n">
-        <v>126</v>
+        <v>315</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2794,17 +2770,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1674534211</t>
+          <t>1156304078</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674534211</t>
+          <t>https://m.place.naver.com/place/1156304078</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2816,34 +2792,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>인블리네일</t>
+          <t>네일로</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bbobbolee2@naver.com</t>
+          <t>loosetime@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>070-7643-2243</t>
+          <t>0507-1378-2633</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
+          <t>인천광역시 미추홀구 매소홀로 262 4층 4013호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xhUIxmC</t>
+          <t>https://www.instagram.com/nailo.nailstudio?igsh=bnB4MXhpNzF4MjU%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2873,13 +2849,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>416</v>
+        <v>80</v>
       </c>
       <c r="Q26" t="n">
-        <v>1221</v>
+        <v>6</v>
       </c>
       <c r="R26" t="n">
-        <v>1637</v>
+        <v>86</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2888,17 +2864,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>63265483</t>
+          <t>2019386343</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/63265483</t>
+          <t>https://m.place.naver.com/place/2019386343</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2910,29 +2886,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>디몽드네일</t>
+          <t>네일스프링</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>eautorride2@naver.com</t>
+          <t>wldus318@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1392-5341</t>
+          <t>0507-1465-2797</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 수봉남로 1 (용현동)2층</t>
+          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail___spring</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2942,7 +2918,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2963,17 +2939,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2982,17 +2958,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1670918594</t>
+          <t>2098983836</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1670918594</t>
+          <t>https://m.place.naver.com/place/2098983836</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3004,34 +2980,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>끌림네일</t>
+          <t>블루진네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cclimnail@naver.com</t>
+          <t>whole4ni@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>032-872-9118</t>
+          <t>0507-1407-5343</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 16 1층 110-2호</t>
+          <t>인천광역시 미추홀구 경원대로897번길 40 상가 1층 101호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_iBxexon</t>
+          <t>https://www.instagram.com/bluejin_nail</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3052,7 +3028,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3061,13 +3037,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="R28" t="n">
-        <v>128</v>
+        <v>314</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3076,17 +3052,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2064653044</t>
+          <t>1920868303</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064653044</t>
+          <t>https://m.place.naver.com/place/1920868303</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3098,34 +3074,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>미다움네일</t>
+          <t>쿄우네일 석바위점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>luna_pic@naver.com</t>
+          <t>dlthwjd7530@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1442-0506</t>
+          <t>0507-1394-6274</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
+          <t>인천광역시 미추홀구 경원대로 858 3층 일부호 쿄우네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://instagram.com/me_daoom</t>
+          <t>http://pf.kakao.com/_xdlxjBn</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3146,7 +3122,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3155,13 +3131,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="Q29" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="R29" t="n">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3170,17 +3146,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1835371224</t>
+          <t>2023963502</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835371224</t>
+          <t>https://m.place.naver.com/place/2023963502</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3192,29 +3168,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>올라운더네일</t>
+          <t>네일파인</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>allroundernail@naver.com</t>
+          <t>milkysuk@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1359-5371</t>
+          <t>0507-1490-7041</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 116 1층 103 A호 올라운더네일</t>
+          <t>인천광역시 미추홀구 인주대로224번길 14 1층 네일파인</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/allroundernail</t>
+          <t>https://www.instagram.com/nail_pine</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3229,7 +3205,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3240,7 +3216,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3249,13 +3225,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>212</v>
       </c>
       <c r="R30" t="n">
-        <v>73</v>
+        <v>341</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3264,17 +3240,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1165613309</t>
+          <t>1679016661</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165613309</t>
+          <t>https://m.place.naver.com/place/1679016661</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3286,29 +3262,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일 해봄</t>
+          <t>모도리 네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>eruriee@naver.com</t>
+          <t>dbsalwjd88@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1303-4226</t>
+          <t>0507-1330-1268</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 토금중로30번길 9 1층</t>
+          <t>인천광역시 미추홀구 독배로382번길 12 1층 모도리네일</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_haebom/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3318,7 +3294,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3339,17 +3315,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>878</v>
+        <v>322</v>
       </c>
       <c r="Q31" t="n">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>1058</v>
+        <v>324</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3358,17 +3334,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>38301920</t>
+          <t>1752538431</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38301920</t>
+          <t>https://m.place.naver.com/place/1752538431</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3380,29 +3356,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>제로네일</t>
+          <t>두아네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>seeat_f@naver.com</t>
+          <t>zolongky@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1359-4583</t>
+          <t>0507-1367-8198</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
+          <t>인천광역시 미추홀구 능해길 12 용현대우아파트 상가동 201호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zeronail_art</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3412,7 +3388,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3433,17 +3409,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>334</v>
+        <v>69</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>339</v>
+        <v>70</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3452,17 +3428,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1613054835</t>
+          <t>1806218865</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613054835</t>
+          <t>https://m.place.naver.com/place/1806218865</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3474,25 +3450,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>예뻐지는네일</t>
+          <t>하이스타네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ylangylang053@naver.com</t>
+          <t>mumu800@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1377-6082</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로578번길 9 1층(주안동)</t>
+          <t>인천광역시 미추홀구 경인로 372 201동 2030호 하이스타네일</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautynail_0901</t>
+          <t>http://pf.kakao.com/_Qxexiqn</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3507,7 +3487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3518,7 +3498,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3527,13 +3507,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="Q33" t="n">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="R33" t="n">
-        <v>242</v>
+        <v>57</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3542,17 +3522,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1148534617</t>
+          <t>1591639462</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1148534617</t>
+          <t>https://m.place.naver.com/place/1591639462</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3564,29 +3544,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일스하리</t>
+          <t>인블리네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>yoollina_@naver.com</t>
+          <t>bbobbolee2@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1447-1684</t>
+          <t>070-7643-2243</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로864번길 24 여성복지관 내 407호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rdvxgn</t>
+          <t>https://pf.kakao.com/_xhUIxmC</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3621,13 +3601,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="Q34" t="n">
-        <v>32</v>
+        <v>1221</v>
       </c>
       <c r="R34" t="n">
-        <v>111</v>
+        <v>1637</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3636,17 +3616,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2056712513</t>
+          <t>63265483</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056712513</t>
+          <t>https://m.place.naver.com/place/63265483</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3658,34 +3638,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일맑음</t>
+          <t>네일루아</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>s1514@naver.com</t>
+          <t>wldud0735@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1489-0530</t>
+          <t>0507-1439-8987</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
+          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuneungyeong4</t>
+          <t>http://pf.kakao.com/_yxmDPxj</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3706,7 +3686,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3715,13 +3695,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="Q35" t="n">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>303</v>
+        <v>210</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3730,17 +3710,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1539397163</t>
+          <t>1678699503</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539397163</t>
+          <t>https://m.place.naver.com/place/1678699503</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3752,34 +3732,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>레푸스 인하대역점 내성발톱 무좀발톱 발각질 문제성발</t>
+          <t>로이네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>hhs3556@naver.com</t>
+          <t>wlgus1647@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1314-9364</t>
+          <t>0507-1350-5396</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 309 노블레스 빌딩 10층 1004호</t>
+          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
+          <t>http://pf.kakao.com/_vxkKMs/chat</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3800,7 +3780,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3809,13 +3789,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="Q36" t="n">
-        <v>436</v>
+        <v>17</v>
       </c>
       <c r="R36" t="n">
-        <v>575</v>
+        <v>189</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3824,17 +3804,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1027018171</t>
+          <t>1765283529</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027018171</t>
+          <t>https://m.place.naver.com/place/1765283529</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3908,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3940,25 +3920,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>고운손</t>
+          <t>문제성 손,발 오감네일 도화점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ghghrjftm@naver.com</t>
+          <t>ogam_foot_nail@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1388-5117</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
+          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
+          <t>https://blog.naver.com/ogam_foot_nail</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3973,7 +3957,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3993,13 +3977,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>166</v>
+        <v>665</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="R38" t="n">
-        <v>168</v>
+        <v>734</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,17 +3992,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1926481487</t>
+          <t>1716147754</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926481487</t>
+          <t>https://m.place.naver.com/place/1716147754</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4030,25 +4014,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>젤리네일</t>
+          <t>네일 품은 손</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mi2013@naver.com</t>
+          <t>94105842@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1360-1453</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
+          <t>인천광역시 미추홀구 한나루로357번길 5-58 1층 네일품은손</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1SGa70g</t>
+          <t>http://pf.kakao.com/_eQCrb</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4083,13 +4071,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>391</v>
+        <v>98</v>
       </c>
       <c r="Q39" t="n">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="R39" t="n">
-        <v>498</v>
+        <v>122</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4098,17 +4086,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1140244485</t>
+          <t>1680001412</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140244485</t>
+          <t>https://m.place.naver.com/place/1680001412</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4120,29 +4108,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일도 희</t>
+          <t>레푸스 인하대역점 내성발톱 무좀발톱 발각질 문제성발</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kimmihee4@naver.com</t>
+          <t>hhs3556@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1304-7934</t>
+          <t>0507-1314-9364</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 321-1 1층 101호 네일도, 희</t>
+          <t>인천광역시 미추홀구 독배로 309 노블레스 빌딩 10층 1004호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildo_hee</t>
+          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4177,13 +4165,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>296</v>
+        <v>139</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>435</v>
       </c>
       <c r="R40" t="n">
-        <v>303</v>
+        <v>574</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4192,17 +4180,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1208564106</t>
+          <t>1027018171</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208564106</t>
+          <t>https://m.place.naver.com/place/1027018171</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4214,29 +4202,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>모도리 네일</t>
+          <t>네일그리움 주안점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dbsalwjd88@naver.com</t>
+          <t>cherryjoa_v@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1330-1268</t>
+          <t>0507-1443-5044</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로382번길 12 1층 모도리네일</t>
+          <t>인천광역시 미추홀구 미추홀대로614번길 42 101호 네일그리움</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_geurium</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4246,7 +4234,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4267,17 +4255,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>320</v>
+        <v>258</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="R41" t="n">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4286,17 +4274,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1752538431</t>
+          <t>1994727673</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1752538431</t>
+          <t>https://m.place.naver.com/place/1994727673</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4308,34 +4296,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일 품은 손</t>
+          <t>미다움네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sssh200118@naver.com</t>
+          <t>luna_pic@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1360-1453</t>
+          <t>0507-1442-0506</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로357번길 5-58 1층 네일품은손</t>
+          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_eQCrb</t>
+          <t>http://instagram.com/me_daoom</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4356,7 +4344,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4365,13 +4353,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="R42" t="n">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4380,17 +4368,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1680001412</t>
+          <t>1835371224</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1680001412</t>
+          <t>https://m.place.naver.com/place/1835371224</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4402,29 +4390,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>라보떼 뷰티</t>
+          <t>하드킴네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dlatmfrl5824@naver.com</t>
+          <t>hardkim_nail@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1377-9030</t>
+          <t>0507-1386-0240</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
+          <t>인천광역시 미추홀구 학익로80번길 11 312동 2층 B-221호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/labeaute7027__</t>
+          <t>https://blog.naver.com/hardkim_nail</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4439,7 +4427,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4459,13 +4447,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>267</v>
+        <v>74</v>
       </c>
       <c r="Q43" t="n">
-        <v>249</v>
+        <v>42</v>
       </c>
       <c r="R43" t="n">
-        <v>516</v>
+        <v>116</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4474,17 +4462,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1828605681</t>
+          <t>2095090349</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828605681</t>
+          <t>https://m.place.naver.com/place/2095090349</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4496,29 +4484,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일스튜디오 매료</t>
+          <t>네일미니</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>lnj7205@naver.com</t>
+          <t>snow1blossom@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1440-3488</t>
+          <t>0507-1379-4411</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인에비뉴 2층 2098호 (투썸플레이스 위)</t>
+          <t>인천광역시 미추홀구 한나루로489번길 107 1층 102호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailstudiomeryo/</t>
+          <t>http://www.instagram.com/nail_mi_ni</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4553,13 +4541,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>249</v>
+        <v>413</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="R44" t="n">
-        <v>263</v>
+        <v>467</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4568,17 +4556,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1152584583</t>
+          <t>1633509740</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1152584583</t>
+          <t>https://m.place.naver.com/place/1633509740</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4590,34 +4578,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>부티스튜디오</t>
+          <t>모드니에네일 인천용현점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>avecbeaute_@naver.com</t>
+          <t>wlsk4075@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1371-2954</t>
+          <t>032-888-2430</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로91번길 71 1층일부호</t>
+          <t>인천광역시 미추홀구 낙섬중로 61 1층 101호,102호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buti_studio?igsh=MWJsdzcyNDNobGc0aw==</t>
+          <t>http://instagram.com/modnie_nail</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4627,7 +4615,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4647,13 +4635,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>880</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4662,17 +4650,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2061859427</t>
+          <t>1031233548</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061859427</t>
+          <t>https://m.place.naver.com/place/1031233548</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4684,29 +4672,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일,포슬</t>
+          <t>츄네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>r__r_b@naver.com</t>
+          <t>chuunail@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1386-5035</t>
+          <t>0507-1367-5751</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
+          <t>인천광역시 미추홀구 인주대로 148 효성해링턴타워 2층 205호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_poseul_</t>
+          <t>http://pf.kakao.com/_plZxan/chat</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4721,7 +4709,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4732,7 +4720,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4741,13 +4729,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>408</v>
+        <v>150</v>
       </c>
       <c r="Q46" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>449</v>
+        <v>154</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4756,17 +4744,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1050625355</t>
+          <t>1815885072</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050625355</t>
+          <t>https://m.place.naver.com/place/1815885072</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4778,29 +4766,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일플래닛</t>
+          <t>효즈네일&amp;속눈썹&amp;왁싱</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>znzltkfkd123@naver.com</t>
+          <t>kwoun0303@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0507-1470-6637</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 포레나 201동(아인여성병원건물) 지상2층 2017호</t>
+          <t>인천광역시 미추홀구 인하로 67</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/znzltkfkd123</t>
+          <t>http://instagram.com/hyoz_official</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4815,7 +4799,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4831,17 +4815,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>346</v>
+        <v>1149</v>
       </c>
       <c r="Q47" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="R47" t="n">
-        <v>443</v>
+        <v>1256</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4850,17 +4834,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1077662255</t>
+          <t>1543447735</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077662255</t>
+          <t>https://m.place.naver.com/place/1543447735</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4872,34 +4856,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>도화네일</t>
+          <t>디두네일 D.do nail studio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>gsqnls2u@naver.com</t>
+          <t>ddonail12@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1373-9131</t>
+          <t>0507-1423-8033</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
+          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dohwa_nail_</t>
+          <t>http://pf.kakao.com/_Ukxhxmn</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4920,7 +4904,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4929,13 +4913,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>693</v>
+        <v>68</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="R48" t="n">
-        <v>695</v>
+        <v>82</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4944,17 +4928,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1155887763</t>
+          <t>2003325308</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155887763</t>
+          <t>https://m.place.naver.com/place/2003325308</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4966,25 +4950,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>란또 네일&amp;뷰티</t>
+          <t>디몽드네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>wealth_8674@naver.com</t>
+          <t>eautorride2@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1392-5341</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 407 예지빌딩 3층</t>
+          <t>인천광역시 미추홀구 수봉남로 1 (용현동)2층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/randdo24.nail_beauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4994,7 +4982,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5015,17 +5003,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="Q49" t="n">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="R49" t="n">
-        <v>313</v>
+        <v>154</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5034,17 +5022,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1119025988</t>
+          <t>1670918594</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1119025988</t>
+          <t>https://m.place.naver.com/place/1670918594</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5056,29 +5044,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>착한언니피부네일</t>
+          <t>네일혜 도화점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>u4melive@naver.com</t>
+          <t>nailhye_@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1368-0680</t>
+          <t>0507-1487-9095</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 73 1층</t>
+          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_nail.hye/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5088,7 +5076,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5109,17 +5097,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="Q50" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="R50" t="n">
-        <v>385</v>
+        <v>343</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5128,17 +5116,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2096439755</t>
+          <t>1396481559</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096439755</t>
+          <t>https://m.place.naver.com/place/1396481559</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5150,34 +5138,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>모드니에네일 인천용현점</t>
+          <t>끌림네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>wlsk4075@naver.com</t>
+          <t>cclimnail@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>032-888-2430</t>
+          <t>032-872-9118</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 61 1층 101호,102호</t>
+          <t>인천광역시 미추홀구 소성로 16 1층 110-2호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://instagram.com/modnie_nail</t>
+          <t>http://pf.kakao.com/_iBxexon</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5198,7 +5186,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5207,13 +5195,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>773</v>
+        <v>131</v>
       </c>
       <c r="Q51" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>876</v>
+        <v>134</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5222,17 +5210,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1031233548</t>
+          <t>2064653044</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031233548</t>
+          <t>https://m.place.naver.com/place/2064653044</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5244,29 +5232,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>에스네일</t>
+          <t>용쥬르샵 인천본점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>snail4324@naver.com</t>
+          <t>iiidydwn@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1406-3132</t>
+          <t>032-423-2963</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
+          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snail0070</t>
+          <t>https://blog.naver.com/iiidydwn</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5281,7 +5269,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5301,13 +5289,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>74</v>
+        <v>664</v>
       </c>
       <c r="Q52" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="R52" t="n">
-        <v>146</v>
+        <v>719</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5316,17 +5304,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>38286683</t>
+          <t>1845960167</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38286683</t>
+          <t>https://m.place.naver.com/place/1845960167</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5338,29 +5326,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일언니</t>
+          <t>에이풋케어 내성발톱 발톱무좀 발각질 문제성발</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>pjh48886@naver.com</t>
+          <t>illbwidu@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1360-4886</t>
+          <t>0507-1378-4114</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 97 102 호 네일언니</t>
+          <t>인천광역시 미추홀구 매소홀로 262 시티필드 6층 6013호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_unni_</t>
+          <t>https://blog.naver.com/illbwidu</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5375,7 +5363,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5395,13 +5383,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>499</v>
+        <v>104</v>
       </c>
       <c r="Q53" t="n">
-        <v>41</v>
+        <v>483</v>
       </c>
       <c r="R53" t="n">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5410,17 +5398,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>36184234</t>
+          <t>1319855180</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36184234</t>
+          <t>https://m.place.naver.com/place/1319855180</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5432,29 +5420,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일진</t>
+          <t>네일오숑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kng026@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1343-3705</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로32번길 22 1층 104호 네일진</t>
+          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___jin_?igsh=ZHIxemZmNXcxNWtq&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_osyong/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5489,13 +5473,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>68</v>
+        <v>260</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="R54" t="n">
-        <v>78</v>
+        <v>279</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5504,17 +5488,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1343927659</t>
+          <t>1518702391</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1343927659</t>
+          <t>https://m.place.naver.com/place/1518702391</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5526,29 +5510,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일혜 도화점</t>
+          <t>뷰티컴트루</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>nailhye_@naver.com</t>
+          <t>wlsk4075@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1487-9095</t>
+          <t>0507-1372-5309</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
+          <t>인천광역시 미추홀구 낙섬서로18번길 27-20 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.hye/</t>
+          <t>https://www.instagram.com/beauty_cometrue</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5574,7 +5558,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5583,13 +5567,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>325</v>
+        <v>248</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R55" t="n">
-        <v>342</v>
+        <v>261</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5598,17 +5582,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1396481559</t>
+          <t>2001250057</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396481559</t>
+          <t>https://m.place.naver.com/place/2001250057</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5620,25 +5604,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>효즈네일&amp;속눈썹&amp;왁싱</t>
+          <t>네일맑음</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kwoun0303@naver.com</t>
+          <t>s1514@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1489-0530</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 67</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://instagram.com/hyoz_official</t>
+          <t>https://www.instagram.com/yuneungyeong4</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5673,13 +5661,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1149</v>
+        <v>234</v>
       </c>
       <c r="Q56" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="R56" t="n">
-        <v>1255</v>
+        <v>303</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5688,17 +5676,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1543447735</t>
+          <t>1539397163</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543447735</t>
+          <t>https://m.place.naver.com/place/1539397163</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5710,29 +5698,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>루미랑네일</t>
+          <t>우니네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jine_blog@naver.com</t>
+          <t>sseonni51@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1371-1706</t>
+          <t>0507-1390-7191</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
+          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 2층 2057호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rumirang_nail</t>
+          <t>https://www.instagram.com/ooninail_?igsh=YXc5aDlrOHZoeDh1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5767,13 +5755,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>259</v>
+        <v>93</v>
       </c>
       <c r="Q57" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="R57" t="n">
-        <v>313</v>
+        <v>111</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5782,17 +5770,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1156304078</t>
+          <t>1013712359</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156304078</t>
+          <t>https://m.place.naver.com/place/1013712359</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5804,34 +5792,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>에이풋케어 내성발톱 발톱무좀 발각질 문제성발</t>
+          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>illbwidu@naver.com</t>
+          <t>dritn-nail_a_o@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1378-4114</t>
+          <t>0507-1325-1015</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 시티필드 6층 6013호</t>
+          <t>인천광역시 미추홀구 장천로 57 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/illbwidu</t>
+          <t>https://m.themosttimes.co.kr/39655</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5841,7 +5829,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5861,13 +5849,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="Q58" t="n">
-        <v>485</v>
+        <v>117</v>
       </c>
       <c r="R58" t="n">
-        <v>588</v>
+        <v>204</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5876,17 +5864,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1319855180</t>
+          <t>1166150967</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1319855180</t>
+          <t>https://m.place.naver.com/place/1166150967</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5898,29 +5886,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일팔레트</t>
+          <t>네일스튜디오 매료</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>nail4season@naver.com</t>
+          <t>lnj7205@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1334-0294</t>
+          <t>0507-1440-3488</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
+          <t>인천광역시 미추홀구 경인로 372 아인에비뉴 2층 2098호 (투썸플레이스 위)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palette_nailll</t>
+          <t>https://www.instagram.com/nailstudiomeryo/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5955,13 +5943,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R59" t="n">
-        <v>311</v>
+        <v>264</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5970,17 +5958,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1167629339</t>
+          <t>1152584583</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167629339</t>
+          <t>https://m.place.naver.com/place/1152584583</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5992,34 +5980,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일인더문</t>
+          <t>네일핏</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>beauty_n_nail@naver.com</t>
+          <t>nailfitsl@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1436-0467</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 237 1층</t>
+          <t>인천광역시 미추홀구 독배로 311 비젼프라자 2층 206호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_inthemoon</t>
+          <t>http://pf.kakao.com/_FxiNCG</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6040,7 +6024,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6049,13 +6033,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>110</v>
+        <v>934</v>
       </c>
       <c r="Q60" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="R60" t="n">
-        <v>162</v>
+        <v>946</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6064,17 +6048,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1204881858</t>
+          <t>718951949</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204881858</t>
+          <t>https://m.place.naver.com/place/718951949</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6086,34 +6070,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>로이네일</t>
+          <t>비비드네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>wlgus1647@naver.com</t>
+          <t>minimouse24@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1350-5396</t>
+          <t>0507-1327-5012</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
+          <t>인천광역시 미추홀구 낙섬서로50번길 17 1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vxkKMs/chat</t>
+          <t>http://www.instagram.com/VIVID__NAIL</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6134,7 +6118,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6143,13 +6127,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>172</v>
+        <v>386</v>
       </c>
       <c r="Q61" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R61" t="n">
-        <v>189</v>
+        <v>399</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6158,17 +6142,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1765283529</t>
+          <t>1191911505</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765283529</t>
+          <t>https://m.place.naver.com/place/1191911505</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6180,29 +6164,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>메이에르 네일</t>
+          <t>도화네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>dmsal6910@naver.com</t>
+          <t>gsqnls2u@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1472-1341</t>
+          <t>0507-1373-9131</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로330번길 23 1층 메이에르네일</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/meyere_nail</t>
+          <t>https://www.instagram.com/dohwa_nail_</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6228,7 +6212,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6237,13 +6221,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>78</v>
+        <v>695</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>91</v>
+        <v>697</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6252,17 +6236,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2090344240</t>
+          <t>1155887763</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090344240</t>
+          <t>https://m.place.naver.com/place/1155887763</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6274,29 +6258,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>뾰로롱네일</t>
+          <t>반디인하우스 도화앨리웨이점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>redberry5@naver.com</t>
+          <t>bandinhouse_dohwa@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1302-6657</t>
+          <t>0507-1392-8241</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
+          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6306,7 +6290,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6327,17 +6311,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="R63" t="n">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6346,17 +6330,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2058778627</t>
+          <t>1485881474</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058778627</t>
+          <t>https://m.place.naver.com/place/1485881474</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6368,34 +6352,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>예뻐진</t>
+          <t>네일만나</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>tlsguswls81@naver.com</t>
+          <t>oppue91@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1334-0060</t>
+          <t>0507-1439-6889</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 301-2 2층</t>
+          <t>인천광역시 미추홀구 아암대로45번길 135 온누리테마라인 1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gFGxbb</t>
+          <t>https://www.instagram.com/nail_manna__</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6416,7 +6400,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6425,13 +6409,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="R64" t="n">
-        <v>187</v>
+        <v>14</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6440,17 +6424,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1366454286</t>
+          <t>1019634096</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1366454286</t>
+          <t>https://m.place.naver.com/place/1019634096</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6462,29 +6446,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>드림드로잉</t>
+          <t>네일진</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>powerkorea0505@naver.com</t>
+          <t>kng026@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1365-9785</t>
+          <t>0507-1343-3705</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 7층 7001호 드림드로잉</t>
+          <t>인천광역시 미추홀구 낙섬중로32번길 22 1층 104호 네일진</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d_dnail0818</t>
+          <t>https://www.instagram.com/nail___jin_?igsh=ZHIxemZmNXcxNWtq&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6519,13 +6503,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="Q65" t="n">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="R65" t="n">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6534,17 +6518,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1887397016</t>
+          <t>1343927659</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1887397016</t>
+          <t>https://m.place.naver.com/place/1343927659</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6556,29 +6540,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일미니</t>
+          <t>미라클뷰티&amp;네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>snow1blossom@naver.com</t>
+          <t>pyk20012001@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1379-4411</t>
+          <t>0507-1330-3178</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로489번길 107 1층 102호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 12층1호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mi_ni</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6588,7 +6572,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6613,13 +6597,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>414</v>
+        <v>195</v>
       </c>
       <c r="Q66" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="R66" t="n">
-        <v>468</v>
+        <v>275</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6628,17 +6612,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1633509740</t>
+          <t>2040709432</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633509740</t>
+          <t>https://m.place.naver.com/place/2040709432</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6650,29 +6634,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>수앙뷰티</t>
+          <t>네일도 희</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>m_s_y_0219@naver.com</t>
+          <t>kimmihee4@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1431-2153</t>
+          <t>0507-1304-7934</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 남주길 150 근린생활시설 2동 210호</t>
+          <t>인천광역시 미추홀구 소성로 321-1 1층 101호 네일도, 희</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soins_beauty_n</t>
+          <t>https://www.instagram.com/naildo_hee</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6707,13 +6691,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>223</v>
+        <v>296</v>
       </c>
       <c r="Q67" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="R67" t="n">
-        <v>242</v>
+        <v>303</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6722,17 +6706,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2042315946</t>
+          <t>1208564106</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042315946</t>
+          <t>https://m.place.naver.com/place/1208564106</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6810,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6838,34 +6822,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>디어마인샵</t>
+          <t>걸스네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>unthsu@naver.com</t>
+          <t>ymj11969@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1403-2780</t>
+          <t>0507-1410-0304</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인남길30번길 94 1층 디어마인샵</t>
+          <t>인천광역시 미추홀구 소성로 133 걸스네일</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://instagram.com/dear_mine91</t>
+          <t>https://link.thinkofyou.kr/girls_nail</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6886,7 +6870,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6895,13 +6879,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1303</v>
+        <v>159</v>
       </c>
       <c r="Q69" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R69" t="n">
-        <v>1356</v>
+        <v>213</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6910,17 +6894,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1144594831</t>
+          <t>37257261</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1144594831</t>
+          <t>https://m.place.naver.com/place/37257261</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6932,29 +6916,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>문제성 손,발 오감네일 도화점</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ogam_foot_nail@naver.com</t>
-        </is>
-      </c>
+          <t>라보떼 뷰티</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1388-5117</t>
+          <t>0507-1377-9030</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
+          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ogam_foot_nail</t>
+          <t>https://www.instagram.com/labeaute7027__</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6969,7 +6949,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6989,13 +6969,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>664</v>
+        <v>267</v>
       </c>
       <c r="Q70" t="n">
-        <v>69</v>
+        <v>252</v>
       </c>
       <c r="R70" t="n">
-        <v>733</v>
+        <v>519</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7004,17 +6984,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1716147754</t>
+          <t>1828605681</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716147754</t>
+          <t>https://m.place.naver.com/place/1828605681</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7026,34 +7006,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일언니</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>555__555@naver.com</t>
-        </is>
-      </c>
+          <t>아무아네일</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1315-4886</t>
+          <t>0507-1365-1547</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 305 102호 네일언니2</t>
+          <t>인천광역시 미추홀구 주안동로 39 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailunni_</t>
+          <t>https://youtube.com/@amouanail_diary?si=mNU7eI9gjC1L4C3W</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7074,7 +7050,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7083,13 +7059,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>832</v>
+        <v>208</v>
       </c>
       <c r="Q71" t="n">
-        <v>56</v>
+        <v>577</v>
       </c>
       <c r="R71" t="n">
-        <v>888</v>
+        <v>785</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7098,17 +7074,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1277528071</t>
+          <t>2098522217</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1277528071</t>
+          <t>https://m.place.naver.com/place/2098522217</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7120,30 +7096,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일핏</t>
+          <t>네일팔레트</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>nailfitsl@naver.com</t>
+          <t>nail4season@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1334-0294</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 311 비젼프라자 2층 206호</t>
+          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FxiNCG</t>
+          <t>https://www.instagram.com/palette_nailll</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7164,7 +7144,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7173,13 +7153,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>934</v>
+        <v>305</v>
       </c>
       <c r="Q72" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R72" t="n">
-        <v>946</v>
+        <v>311</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7188,17 +7168,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>718951949</t>
+          <t>1167629339</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/718951949</t>
+          <t>https://m.place.naver.com/place/1167629339</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7210,34 +7190,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>블루진네일</t>
+          <t>젤리네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>whole4ni@naver.com</t>
+          <t>mi2013@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0507-1407-5343</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로897번길 40 상가 1층 101호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bluejin_nail</t>
+          <t>https://open.kakao.com/o/s1SGa70g</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7258,7 +7234,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7267,13 +7243,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>138</v>
+        <v>391</v>
       </c>
       <c r="Q73" t="n">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="R73" t="n">
-        <v>311</v>
+        <v>498</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7282,17 +7258,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1920868303</t>
+          <t>1140244485</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920868303</t>
+          <t>https://m.place.naver.com/place/1140244485</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7304,34 +7280,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>쿄우네일 석바위점</t>
+          <t>제리네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>dlthwjd7530@naver.com</t>
+          <t>wjdsla91777@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1394-6274</t>
+          <t>0507-1479-5891</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로 858 3층 일부호 쿄우네일</t>
+          <t>인천광역시 미추홀구 매소홀로 262 1층 1055호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdlxjBn</t>
+          <t>https://www.instagram.com/j7n._s?igsh=N2UybHpmZjRnbWJz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7352,7 +7328,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7361,13 +7337,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="Q74" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="R74" t="n">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7376,17 +7352,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2023963502</t>
+          <t>1744004614</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023963502</t>
+          <t>https://m.place.naver.com/place/1744004614</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7398,29 +7374,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일파인</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>milkysuk@naver.com</t>
-        </is>
-      </c>
+          <t>네일 해봄</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1490-7041</t>
+          <t>0507-1303-4226</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로224번길 14 1층 네일파인</t>
+          <t>인천광역시 미추홀구 토금중로30번길 9 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_pine</t>
+          <t>https://www.instagram.com/nail_haebom/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7446,7 +7418,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7455,13 +7427,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>128</v>
+        <v>881</v>
       </c>
       <c r="Q75" t="n">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="R75" t="n">
-        <v>340</v>
+        <v>1061</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7470,17 +7442,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1679016661</t>
+          <t>38301920</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679016661</t>
+          <t>https://m.place.naver.com/place/38301920</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7492,29 +7464,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>마이린 네일</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>myrin_nail@naver.com</t>
-        </is>
-      </c>
+          <t>네일구뜨</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1364-9606</t>
+          <t>0507-1376-0963</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
+          <t>인천광역시 미추홀구 미추홀대로578번길 20 1층 네일구뜨</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kqfkxj</t>
+          <t>http://pf.kakao.com/_xdxgAXb/chat</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7549,13 +7517,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>203</v>
+        <v>95</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="R76" t="n">
-        <v>207</v>
+        <v>126</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7564,17 +7532,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1373786401</t>
+          <t>1674534211</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373786401</t>
+          <t>https://m.place.naver.com/place/1674534211</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/남구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/남구_네일샵.xlsx
@@ -661,7 +661,11 @@
           <t>제로네일</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>seeat_f@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,7 +849,11 @@
           <t>부티스튜디오</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>avecbeaute_@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
@@ -935,7 +943,11 @@
           <t>고운손</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ghghrjftm@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -1207,7 +1219,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wndnjs579@naver.com</t>
+          <t>1jigu@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1450,10 +1462,10 @@
         <v>74</v>
       </c>
       <c r="Q11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R11" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1767,7 +1779,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dmsal6910@naver.com</t>
+          <t>tlsdmsal1910@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2232,25 +2244,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일,리슬</t>
+          <t>네일언니</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lys961206@naver.com</t>
+          <t>pjh48886@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1360-4886</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용정공원로83번길 43 2층 207호</t>
+          <t>인천광역시 미추홀구 인하로 97 102 호 네일언니</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lee_seul?igsh=ZXQyYzNpbng1aW1y&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_unni_</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2285,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>35</v>
+        <v>500</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
-        <v>39</v>
+        <v>541</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2300,12 +2316,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2009491111</t>
+          <t>36184234</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009491111</t>
+          <t>https://m.place.naver.com/place/36184234</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2322,29 +2338,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>수앙뷰티</t>
+          <t>네일,리슬</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>m_s_y_0219@naver.com</t>
+          <t>lys961206@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1431-2153</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 남주길 150 근린생활시설 2동 210호</t>
+          <t>인천광역시 미추홀구 용정공원로83번길 43 2층 207호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soins_beauty_n</t>
+          <t>https://www.instagram.com/nail_lee_seul?igsh=ZXQyYzNpbng1aW1y&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,13 +2391,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>224</v>
+        <v>35</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>243</v>
+        <v>39</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2394,12 +2406,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2042315946</t>
+          <t>2009491111</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042315946</t>
+          <t>https://m.place.naver.com/place/2009491111</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2416,29 +2428,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일,꽃이피다</t>
+          <t>수앙뷰티</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nail910401@naver.com</t>
+          <t>m_s_y_0219@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1311-6628</t>
+          <t>0507-1431-2153</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 시티필드 7층 7012호 네일꽃이피다</t>
+          <t>인천광역시 미추홀구 남주길 150 근린생활시설 2동 210호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.bloom__</t>
+          <t>https://www.instagram.com/soins_beauty_n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2473,13 +2485,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="Q22" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2488,12 +2500,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1271233277</t>
+          <t>2042315946</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1271233277</t>
+          <t>https://m.place.naver.com/place/2042315946</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2510,29 +2522,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>아무르네일</t>
+          <t>네일,꽃이피다</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>07alsrud@naver.com</t>
+          <t>nail910401@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1360-5941</t>
+          <t>0507-1311-6628</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2103호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 시티필드 7층 7012호 네일꽃이피다</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.bloom__</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2542,7 +2554,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2563,17 +2575,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>102</v>
+        <v>172</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="R23" t="n">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2582,12 +2594,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1701492501</t>
+          <t>1271233277</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701492501</t>
+          <t>https://m.place.naver.com/place/1271233277</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2604,29 +2616,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>드림드로잉</t>
+          <t>아무르네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>powerkorea0505@naver.com</t>
+          <t>07alsrud@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1365-9785</t>
+          <t>0507-1360-5941</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 7층 7001호 드림드로잉</t>
+          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2103호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d_dnail0818</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2636,7 +2648,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2657,17 +2669,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="Q24" t="n">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>247</v>
+        <v>110</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2676,12 +2688,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1887397016</t>
+          <t>1701492501</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1887397016</t>
+          <t>https://m.place.naver.com/place/1701492501</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2698,29 +2710,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>루미랑네일</t>
+          <t>드림드로잉</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jine_blog@naver.com</t>
+          <t>powerkorea0505@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1371-1706</t>
+          <t>0507-1365-9785</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 7층 7001호 드림드로잉</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rumirang_nail</t>
+          <t>https://www.instagram.com/d_dnail0818</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2755,13 +2767,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>261</v>
+        <v>92</v>
       </c>
       <c r="Q25" t="n">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="R25" t="n">
-        <v>315</v>
+        <v>247</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2770,12 +2782,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1156304078</t>
+          <t>1887397016</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156304078</t>
+          <t>https://m.place.naver.com/place/1887397016</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2792,29 +2804,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일로</t>
+          <t>루미랑네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>loosetime@naver.com</t>
+          <t>jine_blog@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1378-2633</t>
+          <t>0507-1371-1706</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 4층 4013호</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailo.nailstudio?igsh=bnB4MXhpNzF4MjU%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/rumirang_nail</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2840,7 +2852,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2849,13 +2861,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>80</v>
+        <v>261</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="R26" t="n">
-        <v>86</v>
+        <v>315</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2864,12 +2876,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2019386343</t>
+          <t>1156304078</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019386343</t>
+          <t>https://m.place.naver.com/place/1156304078</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2886,29 +2898,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일스프링</t>
+          <t>네일로</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>wldus318@naver.com</t>
+          <t>kongdw@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1465-2797</t>
+          <t>0507-1378-2633</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
+          <t>인천광역시 미추홀구 매소홀로 262 4층 4013호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___spring</t>
+          <t>https://www.instagram.com/nailo.nailstudio?igsh=bnB4MXhpNzF4MjU%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2934,7 +2946,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2943,13 +2955,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2958,12 +2970,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2098983836</t>
+          <t>2019386343</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098983836</t>
+          <t>https://m.place.naver.com/place/2019386343</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2980,29 +2992,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>블루진네일</t>
+          <t>네일스프링</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>whole4ni@naver.com</t>
+          <t>wldus318@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1407-5343</t>
+          <t>0507-1465-2797</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로897번길 40 상가 1층 101호</t>
+          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bluejin_nail</t>
+          <t>https://www.instagram.com/nail___spring</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3037,13 +3049,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="Q28" t="n">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="R28" t="n">
-        <v>314</v>
+        <v>136</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3052,12 +3064,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1920868303</t>
+          <t>2098983836</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920868303</t>
+          <t>https://m.place.naver.com/place/2098983836</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3074,34 +3086,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>쿄우네일 석바위점</t>
+          <t>블루진네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dlthwjd7530@naver.com</t>
+          <t>whole4ni@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1394-6274</t>
+          <t>0507-1407-5343</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로 858 3층 일부호 쿄우네일</t>
+          <t>인천광역시 미추홀구 경원대로897번길 40 상가 1층 101호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdlxjBn</t>
+          <t>https://www.instagram.com/bluejin_nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3122,7 +3134,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3131,13 +3143,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="Q29" t="n">
-        <v>38</v>
+        <v>173</v>
       </c>
       <c r="R29" t="n">
-        <v>221</v>
+        <v>314</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3146,12 +3158,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2023963502</t>
+          <t>1920868303</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023963502</t>
+          <t>https://m.place.naver.com/place/1920868303</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3168,34 +3180,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일파인</t>
+          <t>쿄우네일 석바위점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>milkysuk@naver.com</t>
+          <t>dlthwjd7530@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1490-7041</t>
+          <t>0507-1394-6274</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로224번길 14 1층 네일파인</t>
+          <t>인천광역시 미추홀구 경원대로 858 3층 일부호 쿄우네일</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_pine</t>
+          <t>http://pf.kakao.com/_xdlxjBn</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3225,13 +3237,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="Q30" t="n">
-        <v>212</v>
+        <v>38</v>
       </c>
       <c r="R30" t="n">
-        <v>341</v>
+        <v>221</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,12 +3252,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1679016661</t>
+          <t>2023963502</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679016661</t>
+          <t>https://m.place.naver.com/place/2023963502</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -4014,34 +4026,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일 품은 손</t>
+          <t>레푸스 인하대역점 내성발톱 무좀발톱 발각질 문제성발</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>94105842@naver.com</t>
+          <t>hhs3556@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1360-1453</t>
+          <t>0507-1314-9364</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로357번길 5-58 1층 네일품은손</t>
+          <t>인천광역시 미추홀구 독배로 309 노블레스 빌딩 10층 1004호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_eQCrb</t>
+          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4062,7 +4074,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4071,13 +4083,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="Q39" t="n">
-        <v>24</v>
+        <v>435</v>
       </c>
       <c r="R39" t="n">
-        <v>122</v>
+        <v>574</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,12 +4098,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1680001412</t>
+          <t>1027018171</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1680001412</t>
+          <t>https://m.place.naver.com/place/1027018171</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4108,29 +4120,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>레푸스 인하대역점 내성발톱 무좀발톱 발각질 문제성발</t>
+          <t>네일그리움 주안점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>hhs3556@naver.com</t>
+          <t>cherryjoa_v@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1314-9364</t>
+          <t>0507-1443-5044</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 309 노블레스 빌딩 10층 1004호</t>
+          <t>인천광역시 미추홀구 미추홀대로614번길 42 101호 네일그리움</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
+          <t>https://www.instagram.com/nail_geurium</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4165,13 +4177,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>139</v>
+        <v>258</v>
       </c>
       <c r="Q40" t="n">
-        <v>435</v>
+        <v>21</v>
       </c>
       <c r="R40" t="n">
-        <v>574</v>
+        <v>279</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,12 +4192,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1027018171</t>
+          <t>1994727673</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027018171</t>
+          <t>https://m.place.naver.com/place/1994727673</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4202,29 +4214,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일그리움 주안점</t>
+          <t>미다움네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>cherryjoa_v@naver.com</t>
+          <t>luna_pic@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1443-5044</t>
+          <t>0507-1442-0506</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로614번길 42 101호 네일그리움</t>
+          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_geurium</t>
+          <t>http://instagram.com/me_daoom</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4259,13 +4271,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>258</v>
+        <v>22</v>
       </c>
       <c r="Q41" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="R41" t="n">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,12 +4286,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1994727673</t>
+          <t>1835371224</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994727673</t>
+          <t>https://m.place.naver.com/place/1835371224</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4296,29 +4308,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>미다움네일</t>
+          <t>하드킴네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>luna_pic@naver.com</t>
+          <t>hardkim_nail@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1442-0506</t>
+          <t>0507-1386-0240</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
+          <t>인천광역시 미추홀구 학익로80번길 11 312동 2층 B-221호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://instagram.com/me_daoom</t>
+          <t>https://blog.naver.com/hardkim_nail</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4333,7 +4345,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4353,13 +4365,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="Q42" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="R42" t="n">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4368,12 +4380,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1835371224</t>
+          <t>2095090349</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835371224</t>
+          <t>https://m.place.naver.com/place/2095090349</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4390,29 +4402,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>하드킴네일</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>hardkim_nail@naver.com</t>
-        </is>
-      </c>
+          <t>네일미니</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1386-0240</t>
+          <t>0507-1379-4411</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 학익로80번길 11 312동 2층 B-221호</t>
+          <t>인천광역시 미추홀구 한나루로489번길 107 1층 102호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hardkim_nail</t>
+          <t>http://www.instagram.com/nail_mi_ni</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4427,7 +4435,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4447,13 +4455,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>74</v>
+        <v>413</v>
       </c>
       <c r="Q43" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="R43" t="n">
-        <v>116</v>
+        <v>467</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4462,12 +4470,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2095090349</t>
+          <t>1633509740</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095090349</t>
+          <t>https://m.place.naver.com/place/1633509740</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4484,29 +4492,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일미니</t>
+          <t>모드니에네일 인천용현점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>snow1blossom@naver.com</t>
+          <t>wlsk4075@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1379-4411</t>
+          <t>032-888-2430</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로489번길 107 1층 102호</t>
+          <t>인천광역시 미추홀구 낙섬중로 61 1층 101호,102호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mi_ni</t>
+          <t>http://instagram.com/modnie_nail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4541,13 +4549,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>413</v>
+        <v>778</v>
       </c>
       <c r="Q44" t="n">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="R44" t="n">
-        <v>467</v>
+        <v>881</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,12 +4564,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1633509740</t>
+          <t>1031233548</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633509740</t>
+          <t>https://m.place.naver.com/place/1031233548</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4578,29 +4586,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>모드니에네일 인천용현점</t>
+          <t>츄네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>wlsk4075@naver.com</t>
+          <t>chuunail@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>032-888-2430</t>
+          <t>0507-1367-5751</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 61 1층 101호,102호</t>
+          <t>인천광역시 미추홀구 인주대로 148 효성해링턴타워 2층 205호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://instagram.com/modnie_nail</t>
+          <t>http://pf.kakao.com/_plZxan/chat</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4615,7 +4623,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4626,7 +4634,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4635,13 +4643,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>777</v>
+        <v>150</v>
       </c>
       <c r="Q45" t="n">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>880</v>
+        <v>154</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,12 +4658,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1031233548</t>
+          <t>1815885072</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031233548</t>
+          <t>https://m.place.naver.com/place/1815885072</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4672,34 +4680,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>츄네일</t>
+          <t>효즈네일&amp;속눈썹&amp;왁싱</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>chuunail@naver.com</t>
+          <t>kwoun0303@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1367-5751</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 148 효성해링턴타워 2층 205호</t>
+          <t>인천광역시 미추홀구 인하로 67</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_plZxan/chat</t>
+          <t>http://instagram.com/hyoz_official</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4720,7 +4724,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4729,13 +4733,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>150</v>
+        <v>1149</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="R46" t="n">
-        <v>154</v>
+        <v>1256</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4744,12 +4748,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1815885072</t>
+          <t>1543447735</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1815885072</t>
+          <t>https://m.place.naver.com/place/1543447735</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4766,30 +4770,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>효즈네일&amp;속눈썹&amp;왁싱</t>
+          <t>디두네일 D.do nail studio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kwoun0303@naver.com</t>
+          <t>ddonail12@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1423-8033</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 67</t>
+          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://instagram.com/hyoz_official</t>
+          <t>http://pf.kakao.com/_Ukxhxmn</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4810,7 +4818,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4819,13 +4827,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1149</v>
+        <v>68</v>
       </c>
       <c r="Q47" t="n">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="R47" t="n">
-        <v>1256</v>
+        <v>82</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4834,12 +4842,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1543447735</t>
+          <t>2003325308</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543447735</t>
+          <t>https://m.place.naver.com/place/2003325308</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4856,39 +4864,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>디두네일 D.do nail studio</t>
+          <t>디몽드네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ddonail12@naver.com</t>
+          <t>eautorride2@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1423-8033</t>
+          <t>0507-1392-5341</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
+          <t>인천광역시 미추홀구 수봉남로 1 (용현동)2층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Ukxhxmn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4904,22 +4912,22 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>68</v>
+        <v>143</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R48" t="n">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4928,12 +4936,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2003325308</t>
+          <t>1670918594</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003325308</t>
+          <t>https://m.place.naver.com/place/1670918594</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4950,29 +4958,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>디몽드네일</t>
+          <t>네일혜 도화점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>eautorride2@naver.com</t>
+          <t>nailhye_@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1392-5341</t>
+          <t>0507-1487-9095</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 수봉남로 1 (용현동)2층</t>
+          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_nail.hye/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4982,7 +4990,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5003,17 +5011,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>143</v>
+        <v>326</v>
       </c>
       <c r="Q49" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R49" t="n">
-        <v>154</v>
+        <v>343</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5022,12 +5030,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1670918594</t>
+          <t>1396481559</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1670918594</t>
+          <t>https://m.place.naver.com/place/1396481559</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5044,34 +5052,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일혜 도화점</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>nailhye_@naver.com</t>
-        </is>
-      </c>
+          <t>끌림네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1487-9095</t>
+          <t>032-872-9118</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
+          <t>인천광역시 미추홀구 소성로 16 1층 110-2호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.hye/</t>
+          <t>http://pf.kakao.com/_iBxexon</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5092,7 +5096,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5101,13 +5105,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>326</v>
+        <v>132</v>
       </c>
       <c r="Q50" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="R50" t="n">
-        <v>343</v>
+        <v>135</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5116,12 +5120,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1396481559</t>
+          <t>2064653044</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396481559</t>
+          <t>https://m.place.naver.com/place/2064653044</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5138,34 +5142,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>끌림네일</t>
+          <t>용쥬르샵 인천본점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>cclimnail@naver.com</t>
+          <t>iiidydwn@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>032-872-9118</t>
+          <t>032-423-2963</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 16 1층 110-2호</t>
+          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_iBxexon</t>
+          <t>https://blog.naver.com/iiidydwn</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5175,7 +5179,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5186,7 +5190,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5195,13 +5199,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>131</v>
+        <v>664</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="R51" t="n">
-        <v>134</v>
+        <v>719</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5210,12 +5214,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2064653044</t>
+          <t>1845960167</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064653044</t>
+          <t>https://m.place.naver.com/place/1845960167</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5232,29 +5236,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>용쥬르샵 인천본점</t>
+          <t>에이풋케어 내성발톱 발톱무좀 발각질 문제성발</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>iiidydwn@naver.com</t>
+          <t>illbwidu@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>032-423-2963</t>
+          <t>0507-1378-4114</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
+          <t>인천광역시 미추홀구 매소홀로 262 시티필드 6층 6013호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iiidydwn</t>
+          <t>https://blog.naver.com/illbwidu</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5289,13 +5293,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>664</v>
+        <v>104</v>
       </c>
       <c r="Q52" t="n">
-        <v>55</v>
+        <v>483</v>
       </c>
       <c r="R52" t="n">
-        <v>719</v>
+        <v>587</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5304,12 +5308,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1845960167</t>
+          <t>1319855180</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845960167</t>
+          <t>https://m.place.naver.com/place/1319855180</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5326,29 +5330,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>에이풋케어 내성발톱 발톱무좀 발각질 문제성발</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>illbwidu@naver.com</t>
-        </is>
-      </c>
+          <t>네일오숑</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1378-4114</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 시티필드 6층 6013호</t>
+          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/illbwidu</t>
+          <t>https://www.instagram.com/nail_osyong/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5363,7 +5359,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5383,13 +5379,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>104</v>
+        <v>260</v>
       </c>
       <c r="Q53" t="n">
-        <v>483</v>
+        <v>19</v>
       </c>
       <c r="R53" t="n">
-        <v>587</v>
+        <v>279</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5398,12 +5394,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1319855180</t>
+          <t>1518702391</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1319855180</t>
+          <t>https://m.place.naver.com/place/1518702391</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5420,25 +5416,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일오숑</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>dong_fcpae@naver.com</t>
-        </is>
-      </c>
+          <t>뷰티컴트루</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1372-5309</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
+          <t>인천광역시 미추홀구 낙섬서로18번길 27-20 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_osyong/</t>
+          <t>https://www.instagram.com/beauty_cometrue</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5464,7 +5460,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5473,13 +5469,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R54" t="n">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5488,12 +5484,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1518702391</t>
+          <t>2001250057</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1518702391</t>
+          <t>https://m.place.naver.com/place/2001250057</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5510,29 +5506,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>뷰티컴트루</t>
+          <t>네일맑음</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>wlsk4075@naver.com</t>
+          <t>s1514@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1372-5309</t>
+          <t>0507-1489-0530</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬서로18번길 27-20 1층</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_cometrue</t>
+          <t>https://www.instagram.com/yuneungyeong4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5558,7 +5554,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5567,13 +5563,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="Q55" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="R55" t="n">
-        <v>261</v>
+        <v>303</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5582,12 +5578,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2001250057</t>
+          <t>1539397163</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001250057</t>
+          <t>https://m.place.naver.com/place/1539397163</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5604,29 +5600,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일맑음</t>
+          <t>우니네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>s1514@naver.com</t>
+          <t>sseonni51@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1489-0530</t>
+          <t>0507-1390-7191</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
+          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 2층 2057호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuneungyeong4</t>
+          <t>https://www.instagram.com/ooninail_?igsh=YXc5aDlrOHZoeDh1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5661,13 +5657,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>234</v>
+        <v>93</v>
       </c>
       <c r="Q56" t="n">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="R56" t="n">
-        <v>303</v>
+        <v>111</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5676,12 +5672,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1539397163</t>
+          <t>1013712359</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539397163</t>
+          <t>https://m.place.naver.com/place/1013712359</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5698,29 +5694,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>우니네일</t>
+          <t>라예샵</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sseonni51@naver.com</t>
+          <t>mh124510@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1390-7191</t>
+          <t>0507-1329-0164</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 2층 2057호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 16 1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ooninail_?igsh=YXc5aDlrOHZoeDh1&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/mh124510</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5735,7 +5731,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5755,13 +5751,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R57" t="n">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5770,12 +5766,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1013712359</t>
+          <t>1698965767</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013712359</t>
+          <t>https://m.place.naver.com/place/1698965767</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6562,7 +6558,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/miraclebeauty_nail?igsh=MW5nN3NoOHd0OG51dg==</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6572,7 +6568,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6634,29 +6630,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일도 희</t>
+          <t>네일에보</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kimmihee4@naver.com</t>
+          <t>daniya1210@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1304-7934</t>
+          <t>0507-1311-6332</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 321-1 1층 101호 네일도, 희</t>
+          <t>인천광역시 미추홀구 경인로 372 201동 B2층 2055호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildo_hee</t>
+          <t>https://www.instagram.com/_nailevo_</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6682,7 +6678,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6691,13 +6687,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>296</v>
+        <v>343</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="R67" t="n">
-        <v>303</v>
+        <v>420</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6706,12 +6702,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1208564106</t>
+          <t>1252060771</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208564106</t>
+          <t>https://m.place.naver.com/place/1252060771</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6728,34 +6724,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일에보</t>
+          <t>걸스네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>daniya1210@naver.com</t>
+          <t>ymj11969@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1311-6332</t>
+          <t>0507-1410-0304</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 201동 B2층 2055호</t>
+          <t>인천광역시 미추홀구 소성로 133 걸스네일</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailevo_</t>
+          <t>https://link.thinkofyou.kr/girls_nail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6785,13 +6781,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>343</v>
+        <v>159</v>
       </c>
       <c r="Q68" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="R68" t="n">
-        <v>420</v>
+        <v>213</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6800,12 +6796,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1252060771</t>
+          <t>37257261</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252060771</t>
+          <t>https://m.place.naver.com/place/37257261</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6822,34 +6818,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>걸스네일</t>
+          <t>라보떼 뷰티</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ymj11969@naver.com</t>
+          <t>dlatmfrl5824@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1410-0304</t>
+          <t>0507-1377-9030</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 133 걸스네일</t>
+          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://link.thinkofyou.kr/girls_nail</t>
+          <t>https://www.instagram.com/labeaute7027__</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6870,7 +6866,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6879,13 +6875,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>159</v>
+        <v>267</v>
       </c>
       <c r="Q69" t="n">
-        <v>54</v>
+        <v>253</v>
       </c>
       <c r="R69" t="n">
-        <v>213</v>
+        <v>520</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6894,12 +6890,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>37257261</t>
+          <t>1828605681</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37257261</t>
+          <t>https://m.place.naver.com/place/1828605681</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6916,25 +6912,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>라보떼 뷰티</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>아무아네일</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>zld9142@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1377-9030</t>
+          <t>0507-1365-1547</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
+          <t>인천광역시 미추홀구 주안동로 39 1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/labeaute7027__</t>
+          <t>https://youtube.com/@amouanail_diary?si=mNU7eI9gjC1L4C3W</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6960,7 +6960,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="Q70" t="n">
-        <v>252</v>
+        <v>575</v>
       </c>
       <c r="R70" t="n">
-        <v>519</v>
+        <v>783</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1828605681</t>
+          <t>2098522217</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828605681</t>
+          <t>https://m.place.naver.com/place/2098522217</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7006,30 +7006,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>아무아네일</t>
+          <t>네일팔레트</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1365-1547</t>
+          <t>0507-1334-0294</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안동로 39 1층</t>
+          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://youtube.com/@amouanail_diary?si=mNU7eI9gjC1L4C3W</t>
+          <t>https://www.instagram.com/palette_nailll</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7050,7 +7050,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7059,13 +7059,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="Q71" t="n">
-        <v>577</v>
+        <v>6</v>
       </c>
       <c r="R71" t="n">
-        <v>785</v>
+        <v>311</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2098522217</t>
+          <t>1167629339</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098522217</t>
+          <t>https://m.place.naver.com/place/1167629339</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7096,29 +7096,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일팔레트</t>
+          <t>젤리네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>nail4season@naver.com</t>
+          <t>mi2013@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1334-0294</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palette_nailll</t>
+          <t>https://open.kakao.com/o/s1SGa70g</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7144,7 +7140,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7153,13 +7149,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>305</v>
+        <v>391</v>
       </c>
       <c r="Q72" t="n">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="R72" t="n">
-        <v>311</v>
+        <v>498</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7168,12 +7164,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1167629339</t>
+          <t>1140244485</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167629339</t>
+          <t>https://m.place.naver.com/place/1140244485</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7190,35 +7186,35 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>젤리네일</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>mi2013@naver.com</t>
-        </is>
-      </c>
+          <t>착한언니피부네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1368-0680</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
+          <t>인천광역시 미추홀구 낙섬중로 73 1층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1SGa70g</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7234,22 +7230,22 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="Q73" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>498</v>
+        <v>386</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7258,12 +7254,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1140244485</t>
+          <t>2096439755</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140244485</t>
+          <t>https://m.place.naver.com/place/2096439755</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7377,7 +7373,11 @@
           <t>네일 해봄</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>eruriee@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
@@ -7467,7 +7467,11 @@
           <t>네일구뜨</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>kry198@naver.com</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_nail/남구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/남구_네일샵.xlsx
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>마이린 네일</t>
+          <t>에이풋케어 내성발톱 발톱무좀 발각질 문제성발</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>myrin_nail@naver.com</t>
+          <t>illbwidu@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1364-9606</t>
+          <t>0507-1378-4114</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 시티필드 6층 6013호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kqfkxj</t>
+          <t>https://blog.naver.com/illbwidu</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>203</v>
+        <v>104</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>483</v>
       </c>
       <c r="R2" t="n">
-        <v>207</v>
+        <v>587</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1373786401</t>
+          <t>1319855180</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373786401</t>
+          <t>https://m.place.naver.com/place/1319855180</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>제로네일</t>
+          <t>비비드네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>seeat_f@naver.com</t>
+          <t>vividnailart@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1359-4583</t>
+          <t>0507-1327-5012</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
+          <t>인천광역시 미추홀구 낙섬서로50번길 17 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zeronail_art</t>
+          <t>http://www.instagram.com/VIVID__NAIL</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
-        <v>340</v>
+        <v>398</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1613054835</t>
+          <t>1191911505</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613054835</t>
+          <t>https://m.place.naver.com/place/1191911505</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>봉구네일</t>
+          <t>네일 해봄</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>94rnrdudal@naver.com</t>
+          <t>eruriee@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1320-0380</t>
+          <t>0507-1303-4226</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86 지하상가 148/173호</t>
+          <t>인천광역시 미추홀구 토금중로30번길 9 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bonggu_nail</t>
+          <t>https://www.instagram.com/nail_haebom/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>102</v>
+        <v>882</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="R4" t="n">
-        <v>132</v>
+        <v>1062</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1965492062</t>
+          <t>38301920</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965492062</t>
+          <t>https://m.place.naver.com/place/38301920</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>부티스튜디오</t>
+          <t>메이에르 네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>avecbeaute_@naver.com</t>
+          <t>tlsdmsal1910@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1371-2954</t>
+          <t>0507-1472-1341</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로91번길 71 1층일부호</t>
+          <t>인천광역시 미추홀구 인주대로330번길 23 1층 메이에르네일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buti_studio?igsh=MWJsdzcyNDNobGc0aw==</t>
+          <t>https://www.instagram.com/meyere_nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2061859427</t>
+          <t>2090344240</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061859427</t>
+          <t>https://m.place.naver.com/place/2090344240</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,25 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>고운손</t>
+          <t>에스네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ghghrjftm@naver.com</t>
+          <t>snail4324@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1406-3132</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
+          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
+          <t>https://www.instagram.com/snail0070</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="R6" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1926481487</t>
+          <t>38286683</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926481487</t>
+          <t>https://m.place.naver.com/place/38286683</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오래도록예쁘게 인하대역본점</t>
+          <t>제리네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oye_beauty@naver.com</t>
+          <t>wjdsla91777@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1348-5330</t>
+          <t>0507-1479-5891</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용정공원로83번길 43 e편한세상시티 2층 217호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 1층 1055호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/o.ye_beauty/</t>
+          <t>https://www.instagram.com/j7n._s?igsh=N2UybHpmZjRnbWJz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>171</v>
+        <v>278</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1200197583</t>
+          <t>1744004614</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200197583</t>
+          <t>https://m.place.naver.com/place/1744004614</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1124,25 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>예뻐지는네일</t>
+          <t>문제성 손,발 오감네일 도화점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ylangylang053@naver.com</t>
+          <t>ogam_foot_nail@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1388-5117</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로578번길 9 1층(주안동)</t>
+          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautynail_0901</t>
+          <t>https://blog.naver.com/ogam_foot_nail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1157,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1177,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>113</v>
+        <v>664</v>
       </c>
       <c r="Q8" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="R8" t="n">
-        <v>242</v>
+        <v>733</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1148534617</t>
+          <t>1716147754</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1148534617</t>
+          <t>https://m.place.naver.com/place/1716147754</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>라 폴리쉬드</t>
+          <t>채움네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1jigu@naver.com</t>
+          <t>rhdwnsla5656@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1354-5656</t>
+          <t>0507-1326-3123</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 승학길 28 105호 1층상가 라 폴리쉬드</t>
+          <t>인천광역시 미추홀구 소성로228번길 11 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/la_polished?igsh=djk3a2lwb3ppdDRk</t>
+          <t>https://www.instagram.com/chaeum_nail_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1271,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>76</v>
+        <v>222</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2080412833</t>
+          <t>1824103581</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080412833</t>
+          <t>https://m.place.naver.com/place/1824103581</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>디어마인샵</t>
+          <t>봉구네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unthsu@naver.com</t>
+          <t>94rnrdudal@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1403-2780</t>
+          <t>0507-1320-0380</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인남길30번길 94 1층 디어마인샵</t>
+          <t>인천광역시 미추홀구 주안로 86 지하상가 148/173호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://instagram.com/dear_mine91</t>
+          <t>https://www.instagram.com/bonggu_nail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1299</v>
+        <v>103</v>
       </c>
       <c r="Q10" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="R10" t="n">
-        <v>1352</v>
+        <v>133</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1144594831</t>
+          <t>1965492062</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1144594831</t>
+          <t>https://m.place.naver.com/place/1965492062</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1402,34 +1410,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에스네일</t>
+          <t>로이네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>snail4324@naver.com</t>
+          <t>charming9827@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1406-3132</t>
+          <t>0507-1350-5396</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
+          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snail0070</t>
+          <t>http://pf.kakao.com/_vxkKMs/chat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1450,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="Q11" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38286683</t>
+          <t>1765283529</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38286683</t>
+          <t>https://m.place.naver.com/place/1765283529</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일스하리</t>
+          <t>쿄우네일 석바위점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>yoollina_@naver.com</t>
+          <t>dlthwjd7530@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1447-1684</t>
+          <t>0507-1394-6274</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로864번길 24 여성복지관 내 407호</t>
+          <t>인천광역시 미추홀구 경원대로 858 3층 일부호 쿄우네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rdvxgn</t>
+          <t>http://pf.kakao.com/_xdlxjBn</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="Q12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R12" t="n">
-        <v>111</v>
+        <v>223</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2056712513</t>
+          <t>2023963502</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056712513</t>
+          <t>https://m.place.naver.com/place/2023963502</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1590,25 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>란또 네일&amp;뷰티</t>
+          <t>네일언니</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>wealth_8674@naver.com</t>
+          <t>pjh48886@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1360-4886</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 407 예지빌딩 3층</t>
+          <t>인천광역시 미추홀구 인하로 97 102 호 네일언니</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/randdo24.nail_beauty</t>
+          <t>https://www.instagram.com/nail_unni_</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1643,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>216</v>
+        <v>497</v>
       </c>
       <c r="Q13" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="R13" t="n">
-        <v>313</v>
+        <v>538</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1670,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1119025988</t>
+          <t>36184234</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1119025988</t>
+          <t>https://m.place.naver.com/place/36184234</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1680,29 +1692,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일언니</t>
+          <t>바나나뷰티</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>555__555@naver.com</t>
+          <t>ik0726@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1315-4886</t>
+          <t>0507-1416-0533</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 305 102호 네일언니2</t>
+          <t>인천광역시 미추홀구 구월남로 8 101호 바나나뷰티</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailunni_</t>
+          <t>http://instagram.com/banana_nail_</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1737,13 +1749,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>837</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>893</v>
+        <v>18</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,17 +1764,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1277528071</t>
+          <t>38403688</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1277528071</t>
+          <t>https://m.place.naver.com/place/38403688</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1774,29 +1786,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>메이에르 네일</t>
+          <t>레푸스 인하대역점 내성발톱 무좀발톱 발각질 문제성발</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tlsdmsal1910@naver.com</t>
+          <t>hhs3556@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1472-1341</t>
+          <t>0507-1314-9364</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로330번길 23 1층 메이에르네일</t>
+          <t>인천광역시 미추홀구 독배로 309 노블레스 빌딩 10층 1004호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/meyere_nail</t>
+          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1822,7 +1834,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1831,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>435</v>
       </c>
       <c r="R15" t="n">
-        <v>93</v>
+        <v>574</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1858,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2090344240</t>
+          <t>1027018171</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090344240</t>
+          <t>https://m.place.naver.com/place/1027018171</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1868,29 +1880,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일인더문</t>
+          <t>네일,리슬</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>beauty_n_nail@naver.com</t>
+          <t>lys961206@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1436-0467</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 237 1층</t>
+          <t>인천광역시 미추홀구 용정공원로83번길 43 2층 207호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_inthemoon</t>
+          <t>https://www.instagram.com/nail_lee_seul?igsh=ZXQyYzNpbng1aW1y&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1925,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="Q16" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>162</v>
+        <v>39</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1204881858</t>
+          <t>2009491111</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204881858</t>
+          <t>https://m.place.naver.com/place/2009491111</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1962,34 +1970,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일,포슬</t>
+          <t>하이스타네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>yonimiao@naver.com</t>
+          <t>mumu800@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1386-5035</t>
+          <t>0507-1377-6082</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
+          <t>인천광역시 미추홀구 경인로 372 201동 2030호 하이스타네일</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_poseul_</t>
+          <t>http://pf.kakao.com/_Qxexiqn</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2010,7 +2018,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2019,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>408</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R17" t="n">
-        <v>449</v>
+        <v>57</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1050625355</t>
+          <t>1591639462</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050625355</t>
+          <t>https://m.place.naver.com/place/1591639462</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2056,29 +2064,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>뾰로롱네일</t>
+          <t>루미랑네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>redberry5@naver.com</t>
+          <t>jine_blog@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1302-6657</t>
+          <t>0507-1371-1706</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/rumirang_nail</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2088,7 +2096,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2109,17 +2117,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="R18" t="n">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2058778627</t>
+          <t>1156304078</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058778627</t>
+          <t>https://m.place.naver.com/place/1156304078</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2150,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네일피컨트</t>
+          <t>네일그리움 주안점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>edenia_@naver.com</t>
+          <t>cherryjoa_v@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1368-8328</t>
+          <t>0507-1443-5044</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2099호</t>
+          <t>인천광역시 미추홀구 미추홀대로614번길 42 101호 네일그리움</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailpiquant</t>
+          <t>https://www.instagram.com/nail_geurium</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2207,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>113</v>
+        <v>261</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>119</v>
+        <v>282</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2230,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1998009537</t>
+          <t>1994727673</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1998009537</t>
+          <t>https://m.place.naver.com/place/1994727673</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2244,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일언니</t>
+          <t>네일인더문</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pjh48886@naver.com</t>
+          <t>beauty_n_nail@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1360-4886</t>
+          <t>0507-1436-0467</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 97 102 호 네일언니</t>
+          <t>인천광역시 미추홀구 소성로 237 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_unni_</t>
+          <t>https://www.instagram.com/nail_inthemoon</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2301,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="Q20" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="R20" t="n">
-        <v>541</v>
+        <v>162</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2324,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>36184234</t>
+          <t>1204881858</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36184234</t>
+          <t>https://m.place.naver.com/place/1204881858</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2338,25 +2346,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일,리슬</t>
+          <t>우니네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>lys961206@naver.com</t>
+          <t>sseonni51@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1390-7191</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용정공원로83번길 43 2층 207호</t>
+          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 2층 2057호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lee_seul?igsh=ZXQyYzNpbng1aW1y&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/ooninail_?igsh=YXc5aDlrOHZoeDh1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2391,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R21" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,17 +2418,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2009491111</t>
+          <t>1013712359</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009491111</t>
+          <t>https://m.place.naver.com/place/1013712359</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2428,29 +2440,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>수앙뷰티</t>
+          <t>라 폴리쉬드</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>m_s_y_0219@naver.com</t>
+          <t>1jigu@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1431-2153</t>
+          <t>0507-1354-5656</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 남주길 150 근린생활시설 2동 210호</t>
+          <t>인천광역시 미추홀구 승학길 28 105호 1층상가 라 폴리쉬드</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soins_beauty_n</t>
+          <t>https://www.instagram.com/la_polished?igsh=djk3a2lwb3ppdDRk</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2485,13 +2497,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
-        <v>243</v>
+        <v>85</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,17 +2512,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2042315946</t>
+          <t>2080412833</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042315946</t>
+          <t>https://m.place.naver.com/place/2080412833</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2522,29 +2534,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일,꽃이피다</t>
+          <t>제로네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nail910401@naver.com</t>
+          <t>seeat_f@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1311-6628</t>
+          <t>0507-1359-4583</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 시티필드 7층 7012호 네일꽃이피다</t>
+          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.bloom__</t>
+          <t>https://www.instagram.com/zeronail_art</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2579,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>172</v>
+        <v>335</v>
       </c>
       <c r="Q23" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>207</v>
+        <v>340</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2594,17 +2606,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1271233277</t>
+          <t>1613054835</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1271233277</t>
+          <t>https://m.place.naver.com/place/1613054835</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2616,29 +2628,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아무르네일</t>
+          <t>블루진네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>07alsrud@naver.com</t>
+          <t>whole4ni@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1360-5941</t>
+          <t>0507-1407-5343</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2103호</t>
+          <t>인천광역시 미추홀구 경원대로897번길 40 상가 1층 101호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bluejin_nail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2648,7 +2660,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2669,17 +2681,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="R24" t="n">
-        <v>110</v>
+        <v>314</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,17 +2700,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1701492501</t>
+          <t>1920868303</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701492501</t>
+          <t>https://m.place.naver.com/place/1920868303</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2710,29 +2722,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>드림드로잉</t>
+          <t>네일진</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>powerkorea0505@naver.com</t>
+          <t>kng026@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1365-9785</t>
+          <t>0507-1343-3705</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 7층 7001호 드림드로잉</t>
+          <t>인천광역시 미추홀구 낙섬중로32번길 22 1층 104호 네일진</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d_dnail0818</t>
+          <t>https://www.instagram.com/nail___jin_?igsh=ZHIxemZmNXcxNWtq&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2767,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="Q25" t="n">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="R25" t="n">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2794,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1887397016</t>
+          <t>1343927659</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1887397016</t>
+          <t>https://m.place.naver.com/place/1343927659</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2804,34 +2816,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>루미랑네일</t>
+          <t>네일핏</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jine_blog@naver.com</t>
+          <t>nailfitsl@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1371-1706</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
+          <t>인천광역시 미추홀구 독배로 311 비젼프라자 2층 206호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rumirang_nail</t>
+          <t>http://pf.kakao.com/_FxiNCG</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2852,7 +2860,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2861,13 +2869,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>261</v>
+        <v>935</v>
       </c>
       <c r="Q26" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="R26" t="n">
-        <v>315</v>
+        <v>947</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2884,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1156304078</t>
+          <t>718951949</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156304078</t>
+          <t>https://m.place.naver.com/place/718951949</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2906,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일로</t>
+          <t>네일언니</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kongdw@naver.com</t>
+          <t>555__555@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1378-2633</t>
+          <t>0507-1315-4886</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 4층 4013호</t>
+          <t>인천광역시 미추홀구 독배로 305 102호 네일언니2</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailo.nailstudio?igsh=bnB4MXhpNzF4MjU%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nailunni_</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2946,7 +2954,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2955,13 +2963,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>80</v>
+        <v>839</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="R27" t="n">
-        <v>86</v>
+        <v>895</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +2978,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2019386343</t>
+          <t>1277528071</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019386343</t>
+          <t>https://m.place.naver.com/place/1277528071</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2992,29 +3000,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일스프링</t>
+          <t>네일피컨트</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wldus318@naver.com</t>
+          <t>edenia_@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1465-2797</t>
+          <t>0507-1368-8328</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
+          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2099호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___spring</t>
+          <t>https://www.instagram.com/nailpiquant</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3049,13 +3057,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3072,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2098983836</t>
+          <t>1998009537</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098983836</t>
+          <t>https://m.place.naver.com/place/1998009537</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3086,29 +3094,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>블루진네일</t>
+          <t>디어마인샵</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>whole4ni@naver.com</t>
+          <t>unthsu@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1407-5343</t>
+          <t>0507-1403-2780</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로897번길 40 상가 1층 101호</t>
+          <t>인천광역시 미추홀구 경인남길30번길 94 1층 디어마인샵</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bluejin_nail</t>
+          <t>http://instagram.com/dear_mine91</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3143,13 +3151,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>141</v>
+        <v>1302</v>
       </c>
       <c r="Q29" t="n">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="R29" t="n">
-        <v>314</v>
+        <v>1355</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3158,17 +3166,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1920868303</t>
+          <t>1144594831</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920868303</t>
+          <t>https://m.place.naver.com/place/1144594831</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3180,34 +3188,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>쿄우네일 석바위점</t>
+          <t>예뻐지는네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dlthwjd7530@naver.com</t>
+          <t>ylangylang053@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1394-6274</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로 858 3층 일부호 쿄우네일</t>
+          <t>인천광역시 미추홀구 미추홀대로578번길 9 1층(주안동)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdlxjBn</t>
+          <t>https://www.instagram.com/beautynail_0901</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3228,7 +3232,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3237,13 +3241,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>183</v>
+        <v>113</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="R30" t="n">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3252,17 +3256,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2023963502</t>
+          <t>1148534617</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023963502</t>
+          <t>https://m.place.naver.com/place/1148534617</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3274,29 +3278,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>모도리 네일</t>
+          <t>네일,포슬</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dbsalwjd88@naver.com</t>
+          <t>yonimiao@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1330-1268</t>
+          <t>0507-1386-5035</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로382번길 12 1층 모도리네일</t>
+          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_poseul_</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3306,7 +3310,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3327,17 +3331,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>322</v>
+        <v>408</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="R31" t="n">
-        <v>324</v>
+        <v>449</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3346,17 +3350,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1752538431</t>
+          <t>1050625355</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1752538431</t>
+          <t>https://m.place.naver.com/place/1050625355</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3368,29 +3372,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>두아네일</t>
+          <t>젤리네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>zolongky@naver.com</t>
+          <t>mi2013@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1367-8198</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 능해길 12 용현대우아파트 상가동 201호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/s1SGa70g</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3416,22 +3416,22 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>69</v>
+        <v>392</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="R32" t="n">
-        <v>70</v>
+        <v>499</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,17 +3440,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1806218865</t>
+          <t>1140244485</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806218865</t>
+          <t>https://m.place.naver.com/place/1140244485</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3462,34 +3462,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>하이스타네일</t>
+          <t>란또 네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mumu800@naver.com</t>
+          <t>wealth_8674@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1377-6082</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 201동 2030호 하이스타네일</t>
+          <t>인천광역시 미추홀구 매소홀로 407 예지빌딩 3층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Qxexiqn</t>
+          <t>https://www.instagram.com/randdo24.nail_beauty</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3510,7 +3506,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3519,13 +3515,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>14</v>
+        <v>216</v>
       </c>
       <c r="Q33" t="n">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="R33" t="n">
-        <v>57</v>
+        <v>313</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,17 +3530,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1591639462</t>
+          <t>1119025988</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591639462</t>
+          <t>https://m.place.naver.com/place/1119025988</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3556,34 +3552,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>인블리네일</t>
+          <t>네일스튜디오 매료</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>bbobbolee2@naver.com</t>
+          <t>lnj7205@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>070-7643-2243</t>
+          <t>0507-1440-3488</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
+          <t>인천광역시 미추홀구 경인로 372 아인에비뉴 2층 2098호 (투썸플레이스 위)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xhUIxmC</t>
+          <t>https://www.instagram.com/nailstudiomeryo/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3604,7 +3600,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3613,13 +3609,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>416</v>
+        <v>250</v>
       </c>
       <c r="Q34" t="n">
-        <v>1221</v>
+        <v>14</v>
       </c>
       <c r="R34" t="n">
-        <v>1637</v>
+        <v>264</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,17 +3624,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>63265483</t>
+          <t>1152584583</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/63265483</t>
+          <t>https://m.place.naver.com/place/1152584583</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3650,39 +3646,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일루아</t>
+          <t>디몽드네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>wldud0735@naver.com</t>
+          <t>eautorride2@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1439-8987</t>
+          <t>0507-1392-5341</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
+          <t>인천광역시 미추홀구 수봉남로 1 (용현동)2층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxmDPxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3698,22 +3694,22 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R35" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,17 +3718,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1678699503</t>
+          <t>1670918594</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1678699503</t>
+          <t>https://m.place.naver.com/place/1670918594</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3744,34 +3740,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>로이네일</t>
+          <t>네일로</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>wlgus1647@naver.com</t>
+          <t>sungunara226@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1350-5396</t>
+          <t>0507-1378-2633</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
+          <t>인천광역시 미추홀구 매소홀로 262 4층 4013호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vxkKMs/chat</t>
+          <t>https://www.instagram.com/nailo.nailstudio?igsh=bnB4MXhpNzF4MjU%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3801,13 +3797,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="Q36" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="R36" t="n">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3816,17 +3812,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1765283529</t>
+          <t>2019386343</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765283529</t>
+          <t>https://m.place.naver.com/place/2019386343</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3838,29 +3834,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>채움네일</t>
+          <t>네일스프링</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>rhdwnsla5656@naver.com</t>
+          <t>wldus318@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1326-3123</t>
+          <t>0507-1465-2797</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로228번길 11 1층</t>
+          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaeum_nail_</t>
+          <t>https://www.instagram.com/nail___spring</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3895,13 +3891,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>223</v>
+        <v>126</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="R37" t="n">
-        <v>262</v>
+        <v>136</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3910,17 +3906,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1824103581</t>
+          <t>2098983836</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824103581</t>
+          <t>https://m.place.naver.com/place/2098983836</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3932,29 +3928,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>문제성 손,발 오감네일 도화점</t>
+          <t>뾰로롱네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ogam_foot_nail@naver.com</t>
+          <t>redberry5@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1388-5117</t>
+          <t>0507-1302-6657</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
+          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ogam_foot_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3964,12 +3960,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3985,17 +3981,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>665</v>
+        <v>82</v>
       </c>
       <c r="Q38" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>734</v>
+        <v>83</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4004,17 +4000,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1716147754</t>
+          <t>2058778627</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716147754</t>
+          <t>https://m.place.naver.com/place/2058778627</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4026,29 +4022,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>레푸스 인하대역점 내성발톱 무좀발톱 발각질 문제성발</t>
+          <t>네일만나</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>hhs3556@naver.com</t>
+          <t>oppue91@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1314-9364</t>
+          <t>0507-1439-6889</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 309 노블레스 빌딩 10층 1004호</t>
+          <t>인천광역시 미추홀구 아암대로45번길 135 온누리테마라인 1층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
+          <t>https://www.instagram.com/nail_manna__</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4083,13 +4079,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>435</v>
+        <v>12</v>
       </c>
       <c r="R39" t="n">
-        <v>574</v>
+        <v>14</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4098,17 +4094,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1027018171</t>
+          <t>1019634096</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027018171</t>
+          <t>https://m.place.naver.com/place/1019634096</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4120,29 +4116,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일그리움 주안점</t>
+          <t>용쥬르샵 인천본점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>cherryjoa_v@naver.com</t>
+          <t>iiidydwn@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1443-5044</t>
+          <t>032-423-2963</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로614번길 42 101호 네일그리움</t>
+          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_geurium</t>
+          <t>https://blog.naver.com/iiidydwn</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4157,7 +4153,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4177,13 +4173,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>258</v>
+        <v>664</v>
       </c>
       <c r="Q40" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="R40" t="n">
-        <v>279</v>
+        <v>719</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4192,17 +4188,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1994727673</t>
+          <t>1845960167</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994727673</t>
+          <t>https://m.place.naver.com/place/1845960167</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4214,29 +4210,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>미다움네일</t>
+          <t>반디인하우스 도화앨리웨이점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>luna_pic@naver.com</t>
+          <t>bandinhouse_dohwa@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1442-0506</t>
+          <t>0507-1392-8241</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
+          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://instagram.com/me_daoom</t>
+          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4271,13 +4267,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>22</v>
+        <v>341</v>
       </c>
       <c r="Q41" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="R41" t="n">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4286,17 +4282,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1835371224</t>
+          <t>1485881474</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835371224</t>
+          <t>https://m.place.naver.com/place/1485881474</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4308,34 +4304,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>하드킴네일</t>
+          <t>네일스하리</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hardkim_nail@naver.com</t>
+          <t>yoollina_@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1386-0240</t>
+          <t>0507-1447-1684</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 학익로80번길 11 312동 2층 B-221호</t>
+          <t>인천광역시 미추홀구 경원대로864번길 24 여성복지관 내 407호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hardkim_nail</t>
+          <t>http://pf.kakao.com/_rdvxgn</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4345,7 +4341,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4356,7 +4352,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4365,13 +4361,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q42" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R42" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4380,17 +4376,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2095090349</t>
+          <t>2056712513</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095090349</t>
+          <t>https://m.place.naver.com/place/2056712513</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4402,30 +4398,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일미니</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>dritn-nail_a_o@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1379-4411</t>
+          <t>0507-1325-1015</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로489번길 107 1층 102호</t>
+          <t>인천광역시 미추홀구 장천로 57 1층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mi_ni</t>
+          <t>https://m.themosttimes.co.kr/39655</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>413</v>
+        <v>87</v>
       </c>
       <c r="Q43" t="n">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="R43" t="n">
-        <v>467</v>
+        <v>204</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4470,17 +4470,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1633509740</t>
+          <t>1166150967</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633509740</t>
+          <t>https://m.place.naver.com/place/1166150967</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4492,29 +4492,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>모드니에네일 인천용현점</t>
+          <t>미다움네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>wlsk4075@naver.com</t>
+          <t>luna_pic@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>032-888-2430</t>
+          <t>0507-1442-0506</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 61 1층 101호,102호</t>
+          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://instagram.com/modnie_nail</t>
+          <t>http://instagram.com/me_daoom</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4549,13 +4549,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>778</v>
+        <v>22</v>
       </c>
       <c r="Q44" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="R44" t="n">
-        <v>881</v>
+        <v>80</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4564,17 +4564,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1031233548</t>
+          <t>1835371224</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031233548</t>
+          <t>https://m.place.naver.com/place/1835371224</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4586,29 +4586,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>츄네일</t>
+          <t>네일루아</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>chuunail@naver.com</t>
+          <t>wldud0735@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1367-5751</t>
+          <t>0507-1439-8987</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 148 효성해링턴타워 2층 205호</t>
+          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_plZxan/chat</t>
+          <t>http://pf.kakao.com/_yxmDPxj</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4643,13 +4643,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="Q45" t="n">
         <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4658,17 +4658,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1815885072</t>
+          <t>1678699503</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1815885072</t>
+          <t>https://m.place.naver.com/place/1678699503</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4680,25 +4680,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>효즈네일&amp;속눈썹&amp;왁싱</t>
+          <t>네일팔레트</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kwoun0303@naver.com</t>
+          <t>gkdisgmlwo@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1334-0294</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 67</t>
+          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://instagram.com/hyoz_official</t>
+          <t>https://www.instagram.com/palette_nailll</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4733,13 +4737,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1149</v>
+        <v>305</v>
       </c>
       <c r="Q46" t="n">
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="R46" t="n">
-        <v>1256</v>
+        <v>311</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4748,17 +4752,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1543447735</t>
+          <t>1167629339</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543447735</t>
+          <t>https://m.place.naver.com/place/1167629339</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4770,34 +4774,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>디두네일 D.do nail studio</t>
+          <t>네일에보</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ddonail12@naver.com</t>
+          <t>daniya1210@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1423-8033</t>
+          <t>0507-1311-6332</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
+          <t>인천광역시 미추홀구 경인로 372 201동 B2층 2055호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Ukxhxmn</t>
+          <t>https://www.instagram.com/_nailevo_</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4827,13 +4831,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>68</v>
+        <v>343</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="R47" t="n">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4842,17 +4846,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2003325308</t>
+          <t>1252060771</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003325308</t>
+          <t>https://m.place.naver.com/place/1252060771</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4864,39 +4868,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>디몽드네일</t>
+          <t>디두네일 D.do nail studio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>eautorride2@naver.com</t>
+          <t>ddonail12@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1392-5341</t>
+          <t>0507-1423-8033</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 수봉남로 1 (용현동)2층</t>
+          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_Ukxhxmn</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4912,22 +4916,22 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="Q48" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R48" t="n">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4936,17 +4940,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1670918594</t>
+          <t>2003325308</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1670918594</t>
+          <t>https://m.place.naver.com/place/2003325308</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4958,29 +4962,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일혜 도화점</t>
+          <t>뷰티컴트루</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>nailhye_@naver.com</t>
+          <t>wlsk4075@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1487-9095</t>
+          <t>0507-1372-5309</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
+          <t>인천광역시 미추홀구 낙섬서로18번길 27-20 1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.hye/</t>
+          <t>https://www.instagram.com/beauty_cometrue</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5006,7 +5010,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5015,13 +5019,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>326</v>
+        <v>248</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R49" t="n">
-        <v>343</v>
+        <v>261</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,17 +5034,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1396481559</t>
+          <t>2001250057</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396481559</t>
+          <t>https://m.place.naver.com/place/2001250057</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5052,30 +5056,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>끌림네일</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>고운손</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ghghrjftm@naver.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>032-872-9118</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 16 1층 110-2호</t>
+          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_iBxexon</t>
+          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5096,7 +5100,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5105,13 +5109,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="Q50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5120,17 +5124,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2064653044</t>
+          <t>1926481487</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064653044</t>
+          <t>https://m.place.naver.com/place/1926481487</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5142,29 +5146,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>용쥬르샵 인천본점</t>
+          <t>미라클뷰티&amp;네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>iiidydwn@naver.com</t>
+          <t>pyk20012001@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>032-423-2963</t>
+          <t>0507-1330-3178</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
+          <t>인천광역시 미추홀구 매소홀로 262 12층1호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iiidydwn</t>
+          <t>https://www.instagram.com/miraclebeauty_nail?igsh=MW5nN3NoOHd0OG51dg==</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5179,7 +5183,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5199,13 +5203,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>664</v>
+        <v>196</v>
       </c>
       <c r="Q51" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="R51" t="n">
-        <v>719</v>
+        <v>276</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5214,17 +5218,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1845960167</t>
+          <t>2040709432</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845960167</t>
+          <t>https://m.place.naver.com/place/2040709432</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5236,34 +5240,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>에이풋케어 내성발톱 발톱무좀 발각질 문제성발</t>
+          <t>인블리네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>illbwidu@naver.com</t>
+          <t>bbobbolee2@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1378-4114</t>
+          <t>070-7643-2243</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 시티필드 6층 6013호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/illbwidu</t>
+          <t>https://pf.kakao.com/_xhUIxmC</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5273,7 +5277,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5284,7 +5288,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5293,13 +5297,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>104</v>
+        <v>417</v>
       </c>
       <c r="Q52" t="n">
-        <v>483</v>
+        <v>1221</v>
       </c>
       <c r="R52" t="n">
-        <v>587</v>
+        <v>1638</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5308,17 +5312,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1319855180</t>
+          <t>63265483</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1319855180</t>
+          <t>https://m.place.naver.com/place/63265483</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5330,21 +5334,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일오숑</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>착한언니피부네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>u4melive@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1368-0680</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
+          <t>인천광역시 미추홀구 낙섬중로 73 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_osyong/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5354,7 +5366,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5375,17 +5387,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>260</v>
+        <v>384</v>
       </c>
       <c r="Q53" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>279</v>
+        <v>386</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5394,17 +5406,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1518702391</t>
+          <t>2096439755</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1518702391</t>
+          <t>https://m.place.naver.com/place/2096439755</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5416,25 +5428,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>뷰티컴트루</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>네일,꽃이피다</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>nail910401@naver.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1372-5309</t>
+          <t>0507-1311-6628</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬서로18번길 27-20 1층</t>
+          <t>인천광역시 미추홀구 매소홀로 262 시티필드 7층 7012호 네일꽃이피다</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_cometrue</t>
+          <t>https://www.instagram.com/nail.bloom__</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5460,7 +5476,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5469,13 +5485,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>248</v>
+        <v>172</v>
       </c>
       <c r="Q54" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="R54" t="n">
-        <v>261</v>
+        <v>207</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5484,17 +5500,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2001250057</t>
+          <t>1271233277</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001250057</t>
+          <t>https://m.place.naver.com/place/1271233277</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5506,29 +5522,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일맑음</t>
+          <t>아무아네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>s1514@naver.com</t>
+          <t>jujuhehe6466@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1489-0530</t>
+          <t>0507-1365-1547</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
+          <t>인천광역시 미추홀구 주안동로 39 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuneungyeong4</t>
+          <t>https://youtube.com/@amouanail_diary?si=mNU7eI9gjC1L4C3W</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5554,7 +5570,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5563,13 +5579,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="Q55" t="n">
-        <v>69</v>
+        <v>593</v>
       </c>
       <c r="R55" t="n">
-        <v>303</v>
+        <v>803</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5578,17 +5594,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1539397163</t>
+          <t>2098522217</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539397163</t>
+          <t>https://m.place.naver.com/place/2098522217</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5600,29 +5616,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>우니네일</t>
+          <t>드림드로잉</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sseonni51@naver.com</t>
+          <t>powerkorea0505@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1390-7191</t>
+          <t>0507-1365-9785</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 2층 2057호</t>
+          <t>인천광역시 미추홀구 매소홀로 262 7층 7001호 드림드로잉</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ooninail_?igsh=YXc5aDlrOHZoeDh1&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/d_dnail0818</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5657,13 +5673,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q56" t="n">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="R56" t="n">
-        <v>111</v>
+        <v>247</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5672,17 +5688,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1013712359</t>
+          <t>1887397016</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013712359</t>
+          <t>https://m.place.naver.com/place/1887397016</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5694,29 +5710,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>라예샵</t>
+          <t>네일미니</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mh124510@naver.com</t>
+          <t>snow1blossom@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1329-0164</t>
+          <t>0507-1379-4411</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 16 1층</t>
+          <t>인천광역시 미추홀구 한나루로489번길 107 1층 102호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mh124510</t>
+          <t>http://www.instagram.com/nail_mi_ni</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5731,7 +5747,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5751,13 +5767,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>180</v>
+        <v>413</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="R57" t="n">
-        <v>188</v>
+        <v>467</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5766,17 +5782,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1698965767</t>
+          <t>1633509740</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698965767</t>
+          <t>https://m.place.naver.com/place/1633509740</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5788,34 +5804,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
+          <t>네일혜 도화점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>dritn-nail_a_o@naver.com</t>
+          <t>nailhye_@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1325-1015</t>
+          <t>0507-1487-9095</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 장천로 57 1층</t>
+          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://m.themosttimes.co.kr/39655</t>
+          <t>https://www.instagram.com/_nail.hye/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5845,13 +5861,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>87</v>
+        <v>328</v>
       </c>
       <c r="Q58" t="n">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="R58" t="n">
-        <v>204</v>
+        <v>345</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5860,17 +5876,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1166150967</t>
+          <t>1396481559</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166150967</t>
+          <t>https://m.place.naver.com/place/1396481559</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5882,29 +5898,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일스튜디오 매료</t>
+          <t>수앙뷰티</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>lnj7205@naver.com</t>
+          <t>m_s_y_0219@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1440-3488</t>
+          <t>0507-1431-2153</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인에비뉴 2층 2098호 (투썸플레이스 위)</t>
+          <t>인천광역시 미추홀구 남주길 150 근린생활시설 2동 210호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailstudiomeryo/</t>
+          <t>https://www.instagram.com/soins_beauty_n</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5939,13 +5955,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="Q59" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R59" t="n">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,17 +5970,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1152584583</t>
+          <t>2042315946</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1152584583</t>
+          <t>https://m.place.naver.com/place/2042315946</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5976,35 +5992,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일핏</t>
+          <t>모도리 네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>nailfitsl@naver.com</t>
+          <t>handart4@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1330-1268</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 311 비젼프라자 2층 206호</t>
+          <t>인천광역시 미추홀구 독배로382번길 12 1층 모도리네일</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FxiNCG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6020,22 +6040,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>934</v>
+        <v>322</v>
       </c>
       <c r="Q60" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>946</v>
+        <v>324</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6044,17 +6064,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>718951949</t>
+          <t>1752538431</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/718951949</t>
+          <t>https://m.place.naver.com/place/1752538431</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6066,34 +6086,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>비비드네일</t>
+          <t>네일구뜨</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>minimouse24@naver.com</t>
+          <t>ssuj2728@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1327-5012</t>
+          <t>0507-1376-0963</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬서로50번길 17 1층</t>
+          <t>인천광역시 미추홀구 미추홀대로578번길 20 1층 네일구뜨</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/VIVID__NAIL</t>
+          <t>http://pf.kakao.com/_xdxgAXb/chat</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6114,7 +6134,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6123,13 +6143,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>386</v>
+        <v>95</v>
       </c>
       <c r="Q61" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="R61" t="n">
-        <v>399</v>
+        <v>126</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,17 +6158,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1191911505</t>
+          <t>1674534211</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1191911505</t>
+          <t>https://m.place.naver.com/place/1674534211</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6160,34 +6180,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>도화네일</t>
+          <t>끌림네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>gsqnls2u@naver.com</t>
+          <t>cclimnail@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1373-9131</t>
+          <t>032-872-9118</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
+          <t>인천광역시 미추홀구 소성로 16 1층 110-2호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dohwa_nail_</t>
+          <t>http://pf.kakao.com/_iBxexon</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6208,7 +6228,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6217,13 +6237,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>695</v>
+        <v>135</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R62" t="n">
-        <v>697</v>
+        <v>138</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6232,17 +6252,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1155887763</t>
+          <t>2064653044</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155887763</t>
+          <t>https://m.place.naver.com/place/2064653044</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6254,29 +6274,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>반디인하우스 도화앨리웨이점</t>
+          <t>라보떼 뷰티</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>bandinhouse_dohwa@naver.com</t>
+          <t>dlatmfrl5824@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1392-8241</t>
+          <t>0507-1377-9030</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
+          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
+          <t>https://www.instagram.com/labeaute7027__</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6311,13 +6331,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>341</v>
+        <v>268</v>
       </c>
       <c r="Q63" t="n">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="R63" t="n">
-        <v>420</v>
+        <v>523</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,17 +6346,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1485881474</t>
+          <t>1828605681</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485881474</t>
+          <t>https://m.place.naver.com/place/1828605681</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6348,34 +6368,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일만나</t>
+          <t>걸스네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>oppue91@naver.com</t>
+          <t>ymj11969@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1439-6889</t>
+          <t>0507-1410-0304</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 아암대로45번길 135 온누리테마라인 1층</t>
+          <t>인천광역시 미추홀구 소성로 133 걸스네일</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_manna__</t>
+          <t>https://link.thinkofyou.kr/girls_nail</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6396,7 +6416,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6405,13 +6425,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="R64" t="n">
-        <v>14</v>
+        <v>213</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6420,17 +6440,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1019634096</t>
+          <t>37257261</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1019634096</t>
+          <t>https://m.place.naver.com/place/37257261</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6442,29 +6462,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일진</t>
+          <t>효즈네일&amp;속눈썹&amp;왁싱</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kng026@naver.com</t>
+          <t>kwoun0303@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0507-1343-3705</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로32번길 22 1층 104호 네일진</t>
+          <t>인천광역시 미추홀구 인하로 67</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___jin_?igsh=ZHIxemZmNXcxNWtq&amp;utm_source=qr</t>
+          <t>http://instagram.com/hyoz_official</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6499,13 +6515,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>68</v>
+        <v>1149</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="R65" t="n">
-        <v>78</v>
+        <v>1256</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6514,17 +6530,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1343927659</t>
+          <t>1543447735</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1343927659</t>
+          <t>https://m.place.naver.com/place/1543447735</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6536,29 +6552,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>미라클뷰티&amp;네일</t>
+          <t>오래도록예쁘게 인하대역본점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>pyk20012001@naver.com</t>
+          <t>oye_beauty@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1330-3178</t>
+          <t>0507-1348-5330</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 12층1호</t>
+          <t>인천광역시 미추홀구 용정공원로83번길 43 e편한세상시티 2층 217호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miraclebeauty_nail?igsh=MW5nN3NoOHd0OG51dg==</t>
+          <t>https://www.instagram.com/o.ye_beauty/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6593,13 +6609,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="Q66" t="n">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="R66" t="n">
-        <v>275</v>
+        <v>171</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6608,17 +6624,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2040709432</t>
+          <t>1200197583</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040709432</t>
+          <t>https://m.place.naver.com/place/1200197583</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6630,34 +6646,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일에보</t>
+          <t>마이린 네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>daniya1210@naver.com</t>
+          <t>myrin_nail@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1311-6332</t>
+          <t>0507-1364-9606</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 201동 B2층 2055호</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailevo_</t>
+          <t>http://pf.kakao.com/_kqfkxj</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6687,13 +6703,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>343</v>
+        <v>203</v>
       </c>
       <c r="Q67" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="R67" t="n">
-        <v>420</v>
+        <v>207</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6702,17 +6718,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1252060771</t>
+          <t>1373786401</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252060771</t>
+          <t>https://m.place.naver.com/place/1373786401</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6724,34 +6740,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>걸스네일</t>
+          <t>네일맑음</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ymj11969@naver.com</t>
+          <t>s1514@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1410-0304</t>
+          <t>0507-1489-0530</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 133 걸스네일</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://link.thinkofyou.kr/girls_nail</t>
+          <t>https://www.instagram.com/yuneungyeong4</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6772,7 +6788,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6781,13 +6797,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>159</v>
+        <v>234</v>
       </c>
       <c r="Q68" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="R68" t="n">
-        <v>213</v>
+        <v>303</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6796,17 +6812,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>37257261</t>
+          <t>1539397163</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37257261</t>
+          <t>https://m.place.naver.com/place/1539397163</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6818,29 +6834,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>라보떼 뷰티</t>
+          <t>하드킴네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>dlatmfrl5824@naver.com</t>
+          <t>hardkim_nail@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1377-9030</t>
+          <t>0507-1386-0240</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
+          <t>인천광역시 미추홀구 학익로80번길 11 312동 2층 B-221호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/labeaute7027__</t>
+          <t>https://blog.naver.com/hardkim_nail</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6855,7 +6871,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6875,13 +6891,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>267</v>
+        <v>74</v>
       </c>
       <c r="Q69" t="n">
-        <v>253</v>
+        <v>42</v>
       </c>
       <c r="R69" t="n">
-        <v>520</v>
+        <v>116</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6890,17 +6906,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1828605681</t>
+          <t>2095090349</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828605681</t>
+          <t>https://m.place.naver.com/place/2095090349</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6912,29 +6928,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>아무아네일</t>
+          <t>도화네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>zld9142@naver.com</t>
+          <t>gsqnls2u@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1365-1547</t>
+          <t>0507-1373-9131</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안동로 39 1층</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://youtube.com/@amouanail_diary?si=mNU7eI9gjC1L4C3W</t>
+          <t>https://www.instagram.com/dohwa_nail_</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6960,7 +6976,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6969,13 +6985,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>208</v>
+        <v>695</v>
       </c>
       <c r="Q70" t="n">
-        <v>575</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>783</v>
+        <v>697</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6984,17 +7000,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2098522217</t>
+          <t>1155887763</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098522217</t>
+          <t>https://m.place.naver.com/place/1155887763</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7006,25 +7022,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일팔레트</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>아무르네일</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>07alsrud@naver.com</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1334-0294</t>
+          <t>0507-1360-5941</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
+          <t>인천광역시 미추홀구 경인로 372 미추홀포레나 아인애비뉴 2층 2103호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palette_nailll</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7034,7 +7054,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7055,17 +7075,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>305</v>
+        <v>102</v>
       </c>
       <c r="Q71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R71" t="n">
-        <v>311</v>
+        <v>110</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7074,17 +7094,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1167629339</t>
+          <t>1701492501</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167629339</t>
+          <t>https://m.place.naver.com/place/1701492501</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7096,30 +7116,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>젤리네일</t>
+          <t>츄네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>mi2013@naver.com</t>
+          <t>ekffo1202@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1367-5751</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
+          <t>인천광역시 미추홀구 인주대로 148 효성해링턴타워 2층 205호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1SGa70g</t>
+          <t>http://pf.kakao.com/_plZxan/chat</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7149,13 +7173,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>391</v>
+        <v>150</v>
       </c>
       <c r="Q72" t="n">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>498</v>
+        <v>154</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7164,17 +7188,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1140244485</t>
+          <t>1815885072</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140244485</t>
+          <t>https://m.place.naver.com/place/1815885072</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7186,35 +7210,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>착한언니피부네일</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>예뻐진</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>tlsguswls81@naver.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1368-0680</t>
+          <t>0507-1334-0060</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 73 1층</t>
+          <t>인천광역시 미추홀구 인하로 301-2 2층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_gFGxbb</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7230,22 +7258,22 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>384</v>
+        <v>97</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="R73" t="n">
-        <v>386</v>
+        <v>188</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7254,17 +7282,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2096439755</t>
+          <t>1366454286</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096439755</t>
+          <t>https://m.place.naver.com/place/1366454286</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7276,29 +7304,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>제리네일</t>
+          <t>부티스튜디오</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>wjdsla91777@naver.com</t>
+          <t>avecbeaute_@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1479-5891</t>
+          <t>0507-1371-2954</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 262 1층 1055호</t>
+          <t>인천광역시 미추홀구 인하로91번길 71 1층일부호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j7n._s?igsh=N2UybHpmZjRnbWJz&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/buti_studio?igsh=MWJsdzcyNDNobGc0aw==</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7333,13 +7361,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>278</v>
+        <v>2</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7348,17 +7376,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1744004614</t>
+          <t>2061859427</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1744004614</t>
+          <t>https://m.place.naver.com/place/2061859427</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7370,29 +7398,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일 해봄</t>
+          <t>두아네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>eruriee@naver.com</t>
+          <t>zolongky@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1303-4226</t>
+          <t>0507-1367-8198</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 토금중로30번길 9 1층</t>
+          <t>인천광역시 미추홀구 능해길 12 용현대우아파트 상가동 201호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_haebom/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7402,7 +7430,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7423,17 +7451,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>881</v>
+        <v>69</v>
       </c>
       <c r="Q75" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>1061</v>
+        <v>70</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7442,17 +7470,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>38301920</t>
+          <t>1806218865</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38301920</t>
+          <t>https://m.place.naver.com/place/1806218865</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7464,34 +7492,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일구뜨</t>
+          <t>모드니에네일 인천용현점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kry198@naver.com</t>
+          <t>wlsk4075@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1376-0963</t>
+          <t>032-888-2430</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로578번길 20 1층 네일구뜨</t>
+          <t>인천광역시 미추홀구 낙섬중로 61 1층 101호,102호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdxgAXb/chat</t>
+          <t>http://instagram.com/modnie_nail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7512,7 +7540,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7521,13 +7549,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>95</v>
+        <v>781</v>
       </c>
       <c r="Q76" t="n">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="R76" t="n">
-        <v>126</v>
+        <v>884</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7536,17 +7564,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1674534211</t>
+          <t>1031233548</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674534211</t>
+          <t>https://m.place.naver.com/place/1031233548</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
